--- a/data/exports/optimization/uk49s_genetic_optimizer_results.xlsx
+++ b/data/exports/optimization/uk49s_genetic_optimizer_results.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R75"/>
+  <dimension ref="A1:R72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -532,7 +532,7 @@
         <v>49</v>
       </c>
       <c r="H2" t="n">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="I2" t="n">
         <v>148</v>
@@ -556,7 +556,7 @@
         <v>14.7051</v>
       </c>
       <c r="P2" t="n">
-        <v>200.2028</v>
+        <v>200.8628</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -565,7 +565,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:20</t>
+          <t>2026-05-24 05:37:07</t>
         </is>
       </c>
     </row>
@@ -592,7 +592,7 @@
         <v>49</v>
       </c>
       <c r="H3" t="n">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="I3" t="n">
         <v>148</v>
@@ -616,7 +616,7 @@
         <v>14.7051</v>
       </c>
       <c r="P3" t="n">
-        <v>200.2028</v>
+        <v>200.8628</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -625,7 +625,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:20</t>
+          <t>2026-05-24 05:37:07</t>
         </is>
       </c>
     </row>
@@ -676,7 +676,7 @@
         <v>14.7051</v>
       </c>
       <c r="P4" t="n">
-        <v>200.2028</v>
+        <v>200.8628</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -685,7 +685,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:20</t>
+          <t>2026-05-24 05:37:07</t>
         </is>
       </c>
     </row>
@@ -712,7 +712,7 @@
         <v>49</v>
       </c>
       <c r="H5" t="n">
-        <v>10</v>
+        <v>38</v>
       </c>
       <c r="I5" t="n">
         <v>148</v>
@@ -736,7 +736,7 @@
         <v>14.7051</v>
       </c>
       <c r="P5" t="n">
-        <v>200.2028</v>
+        <v>200.8628</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -745,7 +745,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:20</t>
+          <t>2026-05-24 05:37:07</t>
         </is>
       </c>
     </row>
@@ -772,7 +772,7 @@
         <v>49</v>
       </c>
       <c r="H6" t="n">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="I6" t="n">
         <v>148</v>
@@ -796,7 +796,7 @@
         <v>14.7051</v>
       </c>
       <c r="P6" t="n">
-        <v>200.2028</v>
+        <v>200.8628</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -805,7 +805,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:20</t>
+          <t>2026-05-24 05:37:07</t>
         </is>
       </c>
     </row>
@@ -832,7 +832,7 @@
         <v>49</v>
       </c>
       <c r="H7" t="n">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="I7" t="n">
         <v>148</v>
@@ -856,7 +856,7 @@
         <v>14.7051</v>
       </c>
       <c r="P7" t="n">
-        <v>200.2028</v>
+        <v>200.8628</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
@@ -865,7 +865,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:20</t>
+          <t>2026-05-24 05:37:07</t>
         </is>
       </c>
     </row>
@@ -892,7 +892,7 @@
         <v>49</v>
       </c>
       <c r="H8" t="n">
-        <v>48</v>
+        <v>9</v>
       </c>
       <c r="I8" t="n">
         <v>148</v>
@@ -916,7 +916,7 @@
         <v>14.7051</v>
       </c>
       <c r="P8" t="n">
-        <v>200.2028</v>
+        <v>200.8628</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:20</t>
+          <t>2026-05-24 05:37:07</t>
         </is>
       </c>
     </row>
@@ -952,7 +952,7 @@
         <v>49</v>
       </c>
       <c r="H9" t="n">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="I9" t="n">
         <v>148</v>
@@ -976,7 +976,7 @@
         <v>14.7051</v>
       </c>
       <c r="P9" t="n">
-        <v>200.2028</v>
+        <v>200.8628</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
@@ -985,7 +985,7 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:20</t>
+          <t>2026-05-24 05:37:07</t>
         </is>
       </c>
     </row>
@@ -1012,7 +1012,7 @@
         <v>49</v>
       </c>
       <c r="H10" t="n">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="I10" t="n">
         <v>148</v>
@@ -1036,7 +1036,7 @@
         <v>14.7051</v>
       </c>
       <c r="P10" t="n">
-        <v>200.2028</v>
+        <v>200.8628</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
@@ -1045,7 +1045,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:20</t>
+          <t>2026-05-24 05:37:07</t>
         </is>
       </c>
     </row>
@@ -1072,7 +1072,7 @@
         <v>49</v>
       </c>
       <c r="H11" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="I11" t="n">
         <v>148</v>
@@ -1096,7 +1096,7 @@
         <v>14.7051</v>
       </c>
       <c r="P11" t="n">
-        <v>200.2028</v>
+        <v>200.8628</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
@@ -1105,7 +1105,7 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:20</t>
+          <t>2026-05-24 05:37:07</t>
         </is>
       </c>
     </row>
@@ -1132,7 +1132,7 @@
         <v>49</v>
       </c>
       <c r="H12" t="n">
-        <v>43</v>
+        <v>4</v>
       </c>
       <c r="I12" t="n">
         <v>148</v>
@@ -1156,7 +1156,7 @@
         <v>14.7051</v>
       </c>
       <c r="P12" t="n">
-        <v>200.2028</v>
+        <v>200.8628</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
@@ -1165,7 +1165,7 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:20</t>
+          <t>2026-05-24 05:37:07</t>
         </is>
       </c>
     </row>
@@ -1192,7 +1192,7 @@
         <v>49</v>
       </c>
       <c r="H13" t="n">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="I13" t="n">
         <v>148</v>
@@ -1216,7 +1216,7 @@
         <v>14.7051</v>
       </c>
       <c r="P13" t="n">
-        <v>200.2028</v>
+        <v>200.8628</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
@@ -1225,7 +1225,7 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:20</t>
+          <t>2026-05-24 05:37:07</t>
         </is>
       </c>
     </row>
@@ -1252,7 +1252,7 @@
         <v>49</v>
       </c>
       <c r="H14" t="n">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="I14" t="n">
         <v>148</v>
@@ -1276,7 +1276,7 @@
         <v>14.7051</v>
       </c>
       <c r="P14" t="n">
-        <v>200.2028</v>
+        <v>200.8628</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
@@ -1285,7 +1285,7 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:20</t>
+          <t>2026-05-24 05:37:07</t>
         </is>
       </c>
     </row>
@@ -1312,7 +1312,7 @@
         <v>49</v>
       </c>
       <c r="H15" t="n">
-        <v>18</v>
+        <v>48</v>
       </c>
       <c r="I15" t="n">
         <v>148</v>
@@ -1336,7 +1336,7 @@
         <v>14.7051</v>
       </c>
       <c r="P15" t="n">
-        <v>200.2028</v>
+        <v>200.8628</v>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
@@ -1345,7 +1345,7 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:20</t>
+          <t>2026-05-24 05:37:07</t>
         </is>
       </c>
     </row>
@@ -1372,7 +1372,7 @@
         <v>49</v>
       </c>
       <c r="H16" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="I16" t="n">
         <v>148</v>
@@ -1396,7 +1396,7 @@
         <v>14.7051</v>
       </c>
       <c r="P16" t="n">
-        <v>200.2028</v>
+        <v>200.8628</v>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
@@ -1405,7 +1405,7 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:20</t>
+          <t>2026-05-24 05:37:07</t>
         </is>
       </c>
     </row>
@@ -1432,7 +1432,7 @@
         <v>49</v>
       </c>
       <c r="H17" t="n">
-        <v>33</v>
+        <v>11</v>
       </c>
       <c r="I17" t="n">
         <v>148</v>
@@ -1456,7 +1456,7 @@
         <v>14.7051</v>
       </c>
       <c r="P17" t="n">
-        <v>200.2028</v>
+        <v>200.8628</v>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
@@ -1465,7 +1465,7 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:20</t>
+          <t>2026-05-24 05:37:07</t>
         </is>
       </c>
     </row>
@@ -1492,7 +1492,7 @@
         <v>49</v>
       </c>
       <c r="H18" t="n">
-        <v>30</v>
+        <v>7</v>
       </c>
       <c r="I18" t="n">
         <v>148</v>
@@ -1516,7 +1516,7 @@
         <v>14.7051</v>
       </c>
       <c r="P18" t="n">
-        <v>200.2028</v>
+        <v>200.8628</v>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
@@ -1525,7 +1525,7 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:20</t>
+          <t>2026-05-24 05:37:07</t>
         </is>
       </c>
     </row>
@@ -1552,7 +1552,7 @@
         <v>49</v>
       </c>
       <c r="H19" t="n">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="I19" t="n">
         <v>148</v>
@@ -1576,7 +1576,7 @@
         <v>14.7051</v>
       </c>
       <c r="P19" t="n">
-        <v>200.2028</v>
+        <v>200.8628</v>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
@@ -1585,7 +1585,7 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:20</t>
+          <t>2026-05-24 05:37:07</t>
         </is>
       </c>
     </row>
@@ -1612,7 +1612,7 @@
         <v>49</v>
       </c>
       <c r="H20" t="n">
-        <v>31</v>
+        <v>17</v>
       </c>
       <c r="I20" t="n">
         <v>148</v>
@@ -1636,7 +1636,7 @@
         <v>14.7051</v>
       </c>
       <c r="P20" t="n">
-        <v>200.2028</v>
+        <v>200.8628</v>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
@@ -1645,7 +1645,7 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:20</t>
+          <t>2026-05-24 05:37:07</t>
         </is>
       </c>
     </row>
@@ -1672,7 +1672,7 @@
         <v>49</v>
       </c>
       <c r="H21" t="n">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="I21" t="n">
         <v>148</v>
@@ -1696,7 +1696,7 @@
         <v>14.7051</v>
       </c>
       <c r="P21" t="n">
-        <v>200.2028</v>
+        <v>200.8628</v>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
@@ -1705,7 +1705,7 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:20</t>
+          <t>2026-05-24 05:37:07</t>
         </is>
       </c>
     </row>
@@ -1732,7 +1732,7 @@
         <v>49</v>
       </c>
       <c r="H22" t="n">
-        <v>47</v>
+        <v>15</v>
       </c>
       <c r="I22" t="n">
         <v>148</v>
@@ -1756,7 +1756,7 @@
         <v>14.7051</v>
       </c>
       <c r="P22" t="n">
-        <v>200.2028</v>
+        <v>200.8628</v>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
@@ -1765,7 +1765,7 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:20</t>
+          <t>2026-05-24 05:37:07</t>
         </is>
       </c>
     </row>
@@ -1792,7 +1792,7 @@
         <v>49</v>
       </c>
       <c r="H23" t="n">
-        <v>14</v>
+        <v>47</v>
       </c>
       <c r="I23" t="n">
         <v>148</v>
@@ -1816,7 +1816,7 @@
         <v>14.7051</v>
       </c>
       <c r="P23" t="n">
-        <v>200.2028</v>
+        <v>200.8628</v>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
@@ -1825,7 +1825,7 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:20</t>
+          <t>2026-05-24 05:37:07</t>
         </is>
       </c>
     </row>
@@ -1852,7 +1852,7 @@
         <v>49</v>
       </c>
       <c r="H24" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I24" t="n">
         <v>148</v>
@@ -1876,7 +1876,7 @@
         <v>14.7051</v>
       </c>
       <c r="P24" t="n">
-        <v>200.2028</v>
+        <v>200.8628</v>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
@@ -1885,7 +1885,7 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:20</t>
+          <t>2026-05-24 05:37:07</t>
         </is>
       </c>
     </row>
@@ -1936,7 +1936,7 @@
         <v>14.7051</v>
       </c>
       <c r="P25" t="n">
-        <v>200.2028</v>
+        <v>200.8628</v>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
@@ -1945,7 +1945,7 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:20</t>
+          <t>2026-05-24 05:37:07</t>
         </is>
       </c>
     </row>
@@ -1996,7 +1996,7 @@
         <v>14.7051</v>
       </c>
       <c r="P26" t="n">
-        <v>200.2028</v>
+        <v>200.8628</v>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
@@ -2005,7 +2005,7 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:20</t>
+          <t>2026-05-24 05:37:07</t>
         </is>
       </c>
     </row>
@@ -2056,7 +2056,7 @@
         <v>14.7051</v>
       </c>
       <c r="P27" t="n">
-        <v>200.2028</v>
+        <v>200.8628</v>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
@@ -2065,7 +2065,7 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:20</t>
+          <t>2026-05-24 05:37:07</t>
         </is>
       </c>
     </row>
@@ -2116,7 +2116,7 @@
         <v>14.7051</v>
       </c>
       <c r="P28" t="n">
-        <v>200.2028</v>
+        <v>200.8628</v>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
@@ -2125,7 +2125,7 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:20</t>
+          <t>2026-05-24 05:37:07</t>
         </is>
       </c>
     </row>
@@ -2176,7 +2176,7 @@
         <v>14.7051</v>
       </c>
       <c r="P29" t="n">
-        <v>200.2028</v>
+        <v>200.8628</v>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
@@ -2185,7 +2185,7 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:20</t>
+          <t>2026-05-24 05:37:07</t>
         </is>
       </c>
     </row>
@@ -2212,7 +2212,7 @@
         <v>49</v>
       </c>
       <c r="H30" t="n">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="I30" t="n">
         <v>148</v>
@@ -2236,7 +2236,7 @@
         <v>14.7051</v>
       </c>
       <c r="P30" t="n">
-        <v>200.2028</v>
+        <v>200.8628</v>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
@@ -2245,7 +2245,7 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:20</t>
+          <t>2026-05-24 05:37:07</t>
         </is>
       </c>
     </row>
@@ -2272,7 +2272,7 @@
         <v>49</v>
       </c>
       <c r="H31" t="n">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="I31" t="n">
         <v>187</v>
@@ -2296,7 +2296,7 @@
         <v>13.7201</v>
       </c>
       <c r="P31" t="n">
-        <v>197.2601</v>
+        <v>197.6001</v>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
@@ -2305,7 +2305,7 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:20</t>
+          <t>2026-05-24 05:37:07</t>
         </is>
       </c>
     </row>
@@ -2332,7 +2332,7 @@
         <v>49</v>
       </c>
       <c r="H32" t="n">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="I32" t="n">
         <v>149</v>
@@ -2356,7 +2356,7 @@
         <v>14.8135</v>
       </c>
       <c r="P32" t="n">
-        <v>196.6338</v>
+        <v>197.1138</v>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
@@ -2365,7 +2365,7 @@
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:20</t>
+          <t>2026-05-24 05:37:07</t>
         </is>
       </c>
     </row>
@@ -2374,7 +2374,7 @@
         <v>32</v>
       </c>
       <c r="B33" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C33" t="n">
         <v>3</v>
@@ -2383,40 +2383,40 @@
         <v>5</v>
       </c>
       <c r="E33" t="n">
-        <v>44</v>
+        <v>8</v>
       </c>
       <c r="F33" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="G33" t="n">
         <v>49</v>
       </c>
       <c r="H33" t="n">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="I33" t="n">
-        <v>149</v>
+        <v>110</v>
       </c>
       <c r="J33" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K33" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L33" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M33" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O33" t="n">
-        <v>14.8135</v>
+        <v>13.2454</v>
       </c>
       <c r="P33" t="n">
-        <v>196.6338</v>
+        <v>196.2934</v>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
@@ -2425,7 +2425,7 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:20</t>
+          <t>2026-05-24 05:37:07</t>
         </is>
       </c>
     </row>
@@ -2443,7 +2443,7 @@
         <v>5</v>
       </c>
       <c r="E34" t="n">
-        <v>8</v>
+        <v>40</v>
       </c>
       <c r="F34" t="n">
         <v>44</v>
@@ -2452,16 +2452,16 @@
         <v>49</v>
       </c>
       <c r="H34" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="I34" t="n">
-        <v>110</v>
+        <v>142</v>
       </c>
       <c r="J34" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K34" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L34" t="n">
         <v>4</v>
@@ -2473,10 +2473,10 @@
         <v>0</v>
       </c>
       <c r="O34" t="n">
-        <v>13.2454</v>
+        <v>12.753</v>
       </c>
       <c r="P34" t="n">
-        <v>195.7734</v>
+        <v>196.0826</v>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
@@ -2485,7 +2485,7 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:20</t>
+          <t>2026-05-24 05:37:07</t>
         </is>
       </c>
     </row>
@@ -2500,22 +2500,22 @@
         <v>3</v>
       </c>
       <c r="D35" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E35" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="F35" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="G35" t="n">
         <v>49</v>
       </c>
       <c r="H35" t="n">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="I35" t="n">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="J35" t="n">
         <v>3</v>
@@ -2524,19 +2524,19 @@
         <v>3</v>
       </c>
       <c r="L35" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M35" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O35" t="n">
-        <v>12.753</v>
+        <v>15.2132</v>
       </c>
       <c r="P35" t="n">
-        <v>195.7426</v>
+        <v>195.6929</v>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
@@ -2545,7 +2545,7 @@
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:20</t>
+          <t>2026-05-24 05:37:07</t>
         </is>
       </c>
     </row>
@@ -2557,10 +2557,10 @@
         <v>1</v>
       </c>
       <c r="C36" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D36" t="n">
-        <v>40</v>
+        <v>3</v>
       </c>
       <c r="E36" t="n">
         <v>44</v>
@@ -2572,16 +2572,16 @@
         <v>49</v>
       </c>
       <c r="H36" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I36" t="n">
-        <v>183</v>
+        <v>145</v>
       </c>
       <c r="J36" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K36" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L36" t="n">
         <v>3</v>
@@ -2590,13 +2590,13 @@
         <v>3</v>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O36" t="n">
-        <v>13.7201</v>
+        <v>15.7175</v>
       </c>
       <c r="P36" t="n">
-        <v>195.6401</v>
+        <v>195.0938</v>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
@@ -2605,7 +2605,7 @@
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:20</t>
+          <t>2026-05-24 05:37:07</t>
         </is>
       </c>
     </row>
@@ -2620,10 +2620,10 @@
         <v>3</v>
       </c>
       <c r="D37" t="n">
-        <v>4</v>
+        <v>44</v>
       </c>
       <c r="E37" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F37" t="n">
         <v>46</v>
@@ -2632,31 +2632,31 @@
         <v>49</v>
       </c>
       <c r="H37" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="I37" t="n">
-        <v>147</v>
+        <v>188</v>
       </c>
       <c r="J37" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K37" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L37" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M37" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N37" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O37" t="n">
-        <v>15.2132</v>
+        <v>15.7175</v>
       </c>
       <c r="P37" t="n">
-        <v>195.0329</v>
+        <v>194.9938</v>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
@@ -2665,7 +2665,7 @@
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:20</t>
+          <t>2026-05-24 05:37:07</t>
         </is>
       </c>
     </row>
@@ -2677,46 +2677,46 @@
         <v>1</v>
       </c>
       <c r="C38" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D38" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E38" t="n">
-        <v>44</v>
+        <v>9</v>
       </c>
       <c r="F38" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="G38" t="n">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="H38" t="n">
-        <v>32</v>
+        <v>6</v>
       </c>
       <c r="I38" t="n">
-        <v>145</v>
+        <v>108</v>
       </c>
       <c r="J38" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K38" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L38" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M38" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N38" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O38" t="n">
-        <v>15.7175</v>
+        <v>13.0231</v>
       </c>
       <c r="P38" t="n">
-        <v>194.4338</v>
+        <v>194.9576</v>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
@@ -2725,7 +2725,7 @@
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:20</t>
+          <t>2026-05-24 05:37:07</t>
         </is>
       </c>
     </row>
@@ -2734,16 +2734,16 @@
         <v>38</v>
       </c>
       <c r="B39" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C39" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D39" t="n">
-        <v>44</v>
+        <v>6</v>
       </c>
       <c r="E39" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F39" t="n">
         <v>46</v>
@@ -2752,31 +2752,31 @@
         <v>49</v>
       </c>
       <c r="H39" t="n">
-        <v>38</v>
+        <v>2</v>
       </c>
       <c r="I39" t="n">
-        <v>188</v>
+        <v>153</v>
       </c>
       <c r="J39" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K39" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L39" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M39" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N39" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O39" t="n">
-        <v>15.7175</v>
+        <v>14.4139</v>
       </c>
       <c r="P39" t="n">
-        <v>194.3338</v>
+        <v>194.7547</v>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
@@ -2785,7 +2785,7 @@
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:20</t>
+          <t>2026-05-24 05:37:07</t>
         </is>
       </c>
     </row>
@@ -2794,28 +2794,28 @@
         <v>39</v>
       </c>
       <c r="B40" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C40" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D40" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E40" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F40" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="G40" t="n">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="H40" t="n">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="I40" t="n">
-        <v>153</v>
+        <v>142</v>
       </c>
       <c r="J40" t="n">
         <v>3</v>
@@ -2824,19 +2824,19 @@
         <v>3</v>
       </c>
       <c r="L40" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M40" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N40" t="n">
         <v>1</v>
       </c>
       <c r="O40" t="n">
-        <v>14.4139</v>
+        <v>14.5052</v>
       </c>
       <c r="P40" t="n">
-        <v>194.2747</v>
+        <v>194.5229</v>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
@@ -2845,7 +2845,7 @@
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:20</t>
+          <t>2026-05-24 05:37:07</t>
         </is>
       </c>
     </row>
@@ -2857,31 +2857,31 @@
         <v>1</v>
       </c>
       <c r="C41" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D41" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E41" t="n">
-        <v>9</v>
+        <v>44</v>
       </c>
       <c r="F41" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="G41" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="H41" t="n">
-        <v>26</v>
+        <v>6</v>
       </c>
       <c r="I41" t="n">
-        <v>108</v>
+        <v>154</v>
       </c>
       <c r="J41" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K41" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L41" t="n">
         <v>4</v>
@@ -2893,10 +2893,10 @@
         <v>0</v>
       </c>
       <c r="O41" t="n">
-        <v>13.0231</v>
+        <v>12.7216</v>
       </c>
       <c r="P41" t="n">
-        <v>194.1176</v>
+        <v>194.4441</v>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
@@ -2905,7 +2905,7 @@
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:20</t>
+          <t>2026-05-24 05:37:07</t>
         </is>
       </c>
     </row>
@@ -2917,46 +2917,46 @@
         <v>1</v>
       </c>
       <c r="C42" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D42" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E42" t="n">
-        <v>44</v>
+        <v>6</v>
       </c>
       <c r="F42" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="G42" t="n">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="H42" t="n">
-        <v>6</v>
+        <v>38</v>
       </c>
       <c r="I42" t="n">
-        <v>154</v>
+        <v>105</v>
       </c>
       <c r="J42" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K42" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L42" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M42" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O42" t="n">
-        <v>12.7216</v>
+        <v>14.5052</v>
       </c>
       <c r="P42" t="n">
-        <v>193.9641</v>
+        <v>194.1829</v>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
@@ -2965,7 +2965,7 @@
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:20</t>
+          <t>2026-05-24 05:37:07</t>
         </is>
       </c>
     </row>
@@ -2977,31 +2977,31 @@
         <v>1</v>
       </c>
       <c r="C43" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D43" t="n">
-        <v>5</v>
+        <v>43</v>
       </c>
       <c r="E43" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F43" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="G43" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="H43" t="n">
-        <v>11</v>
+        <v>38</v>
       </c>
       <c r="I43" t="n">
-        <v>142</v>
+        <v>188</v>
       </c>
       <c r="J43" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K43" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L43" t="n">
         <v>4</v>
@@ -3013,10 +3013,10 @@
         <v>1</v>
       </c>
       <c r="O43" t="n">
-        <v>14.5052</v>
+        <v>14.2352</v>
       </c>
       <c r="P43" t="n">
-        <v>193.6829</v>
+        <v>193.8079</v>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
@@ -3025,7 +3025,7 @@
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:20</t>
+          <t>2026-05-24 05:37:07</t>
         </is>
       </c>
     </row>
@@ -3034,34 +3034,34 @@
         <v>43</v>
       </c>
       <c r="B44" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C44" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D44" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E44" t="n">
-        <v>6</v>
+        <v>44</v>
       </c>
       <c r="F44" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="G44" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="H44" t="n">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="I44" t="n">
-        <v>105</v>
+        <v>157</v>
       </c>
       <c r="J44" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K44" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L44" t="n">
         <v>3</v>
@@ -3070,13 +3070,13 @@
         <v>3</v>
       </c>
       <c r="N44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O44" t="n">
-        <v>14.5052</v>
+        <v>12.4483</v>
       </c>
       <c r="P44" t="n">
-        <v>193.5229</v>
+        <v>193.1807</v>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
@@ -3085,7 +3085,7 @@
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:20</t>
+          <t>2026-05-24 05:37:07</t>
         </is>
       </c>
     </row>
@@ -3097,46 +3097,46 @@
         <v>1</v>
       </c>
       <c r="C45" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D45" t="n">
-        <v>43</v>
+        <v>5</v>
       </c>
       <c r="E45" t="n">
-        <v>44</v>
+        <v>10</v>
       </c>
       <c r="F45" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="G45" t="n">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="H45" t="n">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="I45" t="n">
-        <v>188</v>
+        <v>109</v>
       </c>
       <c r="J45" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K45" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L45" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M45" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O45" t="n">
-        <v>14.2352</v>
+        <v>12.5539</v>
       </c>
       <c r="P45" t="n">
-        <v>193.3279</v>
+        <v>192.7247</v>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
@@ -3145,7 +3145,7 @@
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:20</t>
+          <t>2026-05-24 05:37:07</t>
         </is>
       </c>
     </row>
@@ -3154,28 +3154,28 @@
         <v>45</v>
       </c>
       <c r="B46" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C46" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D46" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E46" t="n">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="F46" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="G46" t="n">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="H46" t="n">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="I46" t="n">
-        <v>157</v>
+        <v>137</v>
       </c>
       <c r="J46" t="n">
         <v>3</v>
@@ -3193,10 +3193,10 @@
         <v>0</v>
       </c>
       <c r="O46" t="n">
-        <v>12.4483</v>
+        <v>12.0996</v>
       </c>
       <c r="P46" t="n">
-        <v>192.7007</v>
+        <v>192.709</v>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
@@ -3205,7 +3205,7 @@
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:20</t>
+          <t>2026-05-24 05:37:07</t>
         </is>
       </c>
     </row>
@@ -3217,13 +3217,13 @@
         <v>1</v>
       </c>
       <c r="C47" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D47" t="n">
-        <v>39</v>
+        <v>5</v>
       </c>
       <c r="E47" t="n">
-        <v>44</v>
+        <v>12</v>
       </c>
       <c r="F47" t="n">
         <v>46</v>
@@ -3232,16 +3232,16 @@
         <v>49</v>
       </c>
       <c r="H47" t="n">
-        <v>26</v>
+        <v>2</v>
       </c>
       <c r="I47" t="n">
-        <v>184</v>
+        <v>116</v>
       </c>
       <c r="J47" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K47" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L47" t="n">
         <v>4</v>
@@ -3253,10 +3253,10 @@
         <v>0</v>
       </c>
       <c r="O47" t="n">
-        <v>12.2409</v>
+        <v>12.3386</v>
       </c>
       <c r="P47" t="n">
-        <v>192.2823</v>
+        <v>192.6064</v>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
@@ -3265,7 +3265,7 @@
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:20</t>
+          <t>2026-05-24 05:37:07</t>
         </is>
       </c>
     </row>
@@ -3280,43 +3280,43 @@
         <v>3</v>
       </c>
       <c r="D48" t="n">
-        <v>5</v>
+        <v>37</v>
       </c>
       <c r="E48" t="n">
-        <v>10</v>
+        <v>44</v>
       </c>
       <c r="F48" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="G48" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="H48" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="I48" t="n">
-        <v>109</v>
+        <v>180</v>
       </c>
       <c r="J48" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K48" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L48" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M48" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N48" t="n">
         <v>0</v>
       </c>
       <c r="O48" t="n">
-        <v>12.5539</v>
+        <v>12.3386</v>
       </c>
       <c r="P48" t="n">
-        <v>192.0647</v>
+        <v>192.3864</v>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
@@ -3325,7 +3325,7 @@
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:20</t>
+          <t>2026-05-24 05:37:07</t>
         </is>
       </c>
     </row>
@@ -3337,25 +3337,25 @@
         <v>1</v>
       </c>
       <c r="C49" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D49" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E49" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="F49" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="G49" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="H49" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="I49" t="n">
-        <v>137</v>
+        <v>155</v>
       </c>
       <c r="J49" t="n">
         <v>3</v>
@@ -3373,10 +3373,10 @@
         <v>0</v>
       </c>
       <c r="O49" t="n">
-        <v>12.0996</v>
+        <v>12.2409</v>
       </c>
       <c r="P49" t="n">
-        <v>192.049</v>
+        <v>191.7423</v>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
@@ -3385,7 +3385,7 @@
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:20</t>
+          <t>2026-05-24 05:37:07</t>
         </is>
       </c>
     </row>
@@ -3400,28 +3400,28 @@
         <v>3</v>
       </c>
       <c r="D50" t="n">
-        <v>37</v>
+        <v>5</v>
       </c>
       <c r="E50" t="n">
-        <v>44</v>
+        <v>14</v>
       </c>
       <c r="F50" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="G50" t="n">
         <v>49</v>
       </c>
       <c r="H50" t="n">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="I50" t="n">
-        <v>180</v>
+        <v>116</v>
       </c>
       <c r="J50" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K50" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L50" t="n">
         <v>4</v>
@@ -3433,10 +3433,10 @@
         <v>0</v>
       </c>
       <c r="O50" t="n">
-        <v>12.3386</v>
+        <v>10.5186</v>
       </c>
       <c r="P50" t="n">
-        <v>191.7264</v>
+        <v>191.6964</v>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
@@ -3445,7 +3445,7 @@
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:20</t>
+          <t>2026-05-24 05:37:07</t>
         </is>
       </c>
     </row>
@@ -3463,40 +3463,40 @@
         <v>5</v>
       </c>
       <c r="E51" t="n">
-        <v>12</v>
+        <v>44</v>
       </c>
       <c r="F51" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G51" t="n">
         <v>49</v>
       </c>
       <c r="H51" t="n">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="I51" t="n">
-        <v>116</v>
+        <v>147</v>
       </c>
       <c r="J51" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K51" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L51" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M51" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O51" t="n">
-        <v>12.3386</v>
+        <v>14.7323</v>
       </c>
       <c r="P51" t="n">
-        <v>191.7264</v>
+        <v>191.5707</v>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
@@ -3505,7 +3505,7 @@
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:20</t>
+          <t>2026-05-24 05:37:07</t>
         </is>
       </c>
     </row>
@@ -3517,25 +3517,25 @@
         <v>1</v>
       </c>
       <c r="C52" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D52" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E52" t="n">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="F52" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="G52" t="n">
         <v>49</v>
       </c>
       <c r="H52" t="n">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="I52" t="n">
-        <v>155</v>
+        <v>136</v>
       </c>
       <c r="J52" t="n">
         <v>3</v>
@@ -3544,19 +3544,19 @@
         <v>3</v>
       </c>
       <c r="L52" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M52" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N52" t="n">
         <v>0</v>
       </c>
       <c r="O52" t="n">
-        <v>12.2409</v>
+        <v>10.1311</v>
       </c>
       <c r="P52" t="n">
-        <v>191.4023</v>
+        <v>191.3679</v>
       </c>
       <c r="Q52" t="inlineStr">
         <is>
@@ -3565,7 +3565,7 @@
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:20</t>
+          <t>2026-05-24 05:37:07</t>
         </is>
       </c>
     </row>
@@ -3583,19 +3583,19 @@
         <v>5</v>
       </c>
       <c r="E53" t="n">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="F53" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="G53" t="n">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="H53" t="n">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="I53" t="n">
-        <v>147</v>
+        <v>136</v>
       </c>
       <c r="J53" t="n">
         <v>3</v>
@@ -3604,19 +3604,19 @@
         <v>3</v>
       </c>
       <c r="L53" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M53" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O53" t="n">
-        <v>14.7323</v>
+        <v>11.6619</v>
       </c>
       <c r="P53" t="n">
-        <v>191.2307</v>
+        <v>190.0548</v>
       </c>
       <c r="Q53" t="inlineStr">
         <is>
@@ -3625,7 +3625,7 @@
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:20</t>
+          <t>2026-05-24 05:37:07</t>
         </is>
       </c>
     </row>
@@ -3640,28 +3640,28 @@
         <v>3</v>
       </c>
       <c r="D54" t="n">
-        <v>5</v>
+        <v>31</v>
       </c>
       <c r="E54" t="n">
-        <v>14</v>
+        <v>44</v>
       </c>
       <c r="F54" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="G54" t="n">
         <v>49</v>
       </c>
       <c r="H54" t="n">
-        <v>29</v>
+        <v>9</v>
       </c>
       <c r="I54" t="n">
-        <v>116</v>
+        <v>174</v>
       </c>
       <c r="J54" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K54" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L54" t="n">
         <v>4</v>
@@ -3673,10 +3673,10 @@
         <v>0</v>
       </c>
       <c r="O54" t="n">
-        <v>10.5186</v>
+        <v>10.0916</v>
       </c>
       <c r="P54" t="n">
-        <v>191.2164</v>
+        <v>189.249</v>
       </c>
       <c r="Q54" t="inlineStr">
         <is>
@@ -3685,7 +3685,7 @@
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:20</t>
+          <t>2026-05-24 05:37:07</t>
         </is>
       </c>
     </row>
@@ -3703,19 +3703,19 @@
         <v>5</v>
       </c>
       <c r="E55" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F55" t="n">
         <v>44</v>
       </c>
       <c r="G55" t="n">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="H55" t="n">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="I55" t="n">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="J55" t="n">
         <v>3</v>
@@ -3724,19 +3724,19 @@
         <v>3</v>
       </c>
       <c r="L55" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M55" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N55" t="n">
         <v>0</v>
       </c>
       <c r="O55" t="n">
-        <v>10.1311</v>
+        <v>11.2428</v>
       </c>
       <c r="P55" t="n">
-        <v>191.0279</v>
+        <v>188.2469</v>
       </c>
       <c r="Q55" t="inlineStr">
         <is>
@@ -3745,7 +3745,7 @@
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:20</t>
+          <t>2026-05-24 05:37:07</t>
         </is>
       </c>
     </row>
@@ -3763,16 +3763,16 @@
         <v>5</v>
       </c>
       <c r="E56" t="n">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="F56" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="G56" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="H56" t="n">
-        <v>48</v>
+        <v>15</v>
       </c>
       <c r="I56" t="n">
         <v>136</v>
@@ -3793,10 +3793,10 @@
         <v>0</v>
       </c>
       <c r="O56" t="n">
-        <v>11.6619</v>
+        <v>9.8102</v>
       </c>
       <c r="P56" t="n">
-        <v>189.3948</v>
+        <v>188.2255</v>
       </c>
       <c r="Q56" t="inlineStr">
         <is>
@@ -3805,7 +3805,7 @@
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:20</t>
+          <t>2026-05-24 05:37:07</t>
         </is>
       </c>
     </row>
@@ -3820,7 +3820,7 @@
         <v>3</v>
       </c>
       <c r="D57" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E57" t="n">
         <v>44</v>
@@ -3832,10 +3832,10 @@
         <v>49</v>
       </c>
       <c r="H57" t="n">
-        <v>21</v>
+        <v>38</v>
       </c>
       <c r="I57" t="n">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="J57" t="n">
         <v>4</v>
@@ -3853,10 +3853,10 @@
         <v>0</v>
       </c>
       <c r="O57" t="n">
-        <v>10.0916</v>
+        <v>10.7443</v>
       </c>
       <c r="P57" t="n">
-        <v>188.589</v>
+        <v>187.9808</v>
       </c>
       <c r="Q57" t="inlineStr">
         <is>
@@ -3865,7 +3865,7 @@
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:20</t>
+          <t>2026-05-24 05:37:07</t>
         </is>
       </c>
     </row>
@@ -3874,49 +3874,49 @@
         <v>57</v>
       </c>
       <c r="B58" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C58" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D58" t="n">
-        <v>5</v>
+        <v>44</v>
       </c>
       <c r="E58" t="n">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="F58" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="G58" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="H58" t="n">
-        <v>32</v>
+        <v>6</v>
       </c>
       <c r="I58" t="n">
-        <v>135</v>
+        <v>192</v>
       </c>
       <c r="J58" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K58" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L58" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M58" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N58" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O58" t="n">
-        <v>11.2428</v>
+        <v>14.9184</v>
       </c>
       <c r="P58" t="n">
-        <v>187.5869</v>
+        <v>187.1961</v>
       </c>
       <c r="Q58" t="inlineStr">
         <is>
@@ -3925,7 +3925,7 @@
       </c>
       <c r="R58" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:20</t>
+          <t>2026-05-24 05:37:07</t>
         </is>
       </c>
     </row>
@@ -3943,7 +3943,7 @@
         <v>5</v>
       </c>
       <c r="E59" t="n">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="F59" t="n">
         <v>46</v>
@@ -3952,10 +3952,10 @@
         <v>49</v>
       </c>
       <c r="H59" t="n">
-        <v>15</v>
+        <v>38</v>
       </c>
       <c r="I59" t="n">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="J59" t="n">
         <v>3</v>
@@ -3964,19 +3964,19 @@
         <v>3</v>
       </c>
       <c r="L59" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M59" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N59" t="n">
         <v>0</v>
       </c>
       <c r="O59" t="n">
-        <v>9.8102</v>
+        <v>12.3386</v>
       </c>
       <c r="P59" t="n">
-        <v>187.3855</v>
+        <v>187.1264</v>
       </c>
       <c r="Q59" t="inlineStr">
         <is>
@@ -3985,7 +3985,7 @@
       </c>
       <c r="R59" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:20</t>
+          <t>2026-05-24 05:37:07</t>
         </is>
       </c>
     </row>
@@ -4000,28 +4000,28 @@
         <v>3</v>
       </c>
       <c r="D60" t="n">
-        <v>33</v>
+        <v>5</v>
       </c>
       <c r="E60" t="n">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="F60" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="G60" t="n">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="H60" t="n">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="I60" t="n">
-        <v>176</v>
+        <v>134</v>
       </c>
       <c r="J60" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K60" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L60" t="n">
         <v>4</v>
@@ -4033,10 +4033,10 @@
         <v>0</v>
       </c>
       <c r="O60" t="n">
-        <v>10.7443</v>
+        <v>10.8444</v>
       </c>
       <c r="P60" t="n">
-        <v>187.3208</v>
+        <v>187.0909</v>
       </c>
       <c r="Q60" t="inlineStr">
         <is>
@@ -4045,7 +4045,7 @@
       </c>
       <c r="R60" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:20</t>
+          <t>2026-05-24 05:37:07</t>
         </is>
       </c>
     </row>
@@ -4054,49 +4054,49 @@
         <v>60</v>
       </c>
       <c r="B61" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C61" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D61" t="n">
-        <v>44</v>
+        <v>5</v>
       </c>
       <c r="E61" t="n">
-        <v>45</v>
+        <v>24</v>
       </c>
       <c r="F61" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="G61" t="n">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="H61" t="n">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="I61" t="n">
-        <v>192</v>
+        <v>123</v>
       </c>
       <c r="J61" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K61" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L61" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M61" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N61" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O61" t="n">
-        <v>14.9184</v>
+        <v>8.579000000000001</v>
       </c>
       <c r="P61" t="n">
-        <v>186.7161</v>
+        <v>185.9076</v>
       </c>
       <c r="Q61" t="inlineStr">
         <is>
@@ -4105,7 +4105,7 @@
       </c>
       <c r="R61" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:20</t>
+          <t>2026-05-24 05:37:07</t>
         </is>
       </c>
     </row>
@@ -4120,10 +4120,10 @@
         <v>3</v>
       </c>
       <c r="D62" t="n">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="E62" t="n">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="F62" t="n">
         <v>46</v>
@@ -4132,10 +4132,10 @@
         <v>49</v>
       </c>
       <c r="H62" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="I62" t="n">
-        <v>143</v>
+        <v>164</v>
       </c>
       <c r="J62" t="n">
         <v>3</v>
@@ -4144,19 +4144,19 @@
         <v>3</v>
       </c>
       <c r="L62" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M62" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N62" t="n">
         <v>0</v>
       </c>
       <c r="O62" t="n">
-        <v>12.3386</v>
+        <v>9.0465</v>
       </c>
       <c r="P62" t="n">
-        <v>186.4664</v>
+        <v>185.2164</v>
       </c>
       <c r="Q62" t="inlineStr">
         <is>
@@ -4165,7 +4165,7 @@
       </c>
       <c r="R62" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:20</t>
+          <t>2026-05-24 05:37:07</t>
         </is>
       </c>
     </row>
@@ -4183,7 +4183,7 @@
         <v>5</v>
       </c>
       <c r="E63" t="n">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="F63" t="n">
         <v>44</v>
@@ -4192,16 +4192,16 @@
         <v>46</v>
       </c>
       <c r="H63" t="n">
-        <v>40</v>
+        <v>2</v>
       </c>
       <c r="I63" t="n">
-        <v>134</v>
+        <v>120</v>
       </c>
       <c r="J63" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K63" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L63" t="n">
         <v>4</v>
@@ -4213,10 +4213,10 @@
         <v>0</v>
       </c>
       <c r="O63" t="n">
-        <v>10.8444</v>
+        <v>8.8544</v>
       </c>
       <c r="P63" t="n">
-        <v>186.4309</v>
+        <v>184.4559</v>
       </c>
       <c r="Q63" t="inlineStr">
         <is>
@@ -4225,7 +4225,7 @@
       </c>
       <c r="R63" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:20</t>
+          <t>2026-05-24 05:37:07</t>
         </is>
       </c>
     </row>
@@ -4234,34 +4234,34 @@
         <v>63</v>
       </c>
       <c r="B64" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C64" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D64" t="n">
-        <v>5</v>
+        <v>28</v>
       </c>
       <c r="E64" t="n">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="F64" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="G64" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="H64" t="n">
-        <v>48</v>
+        <v>16</v>
       </c>
       <c r="I64" t="n">
-        <v>123</v>
+        <v>175</v>
       </c>
       <c r="J64" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K64" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L64" t="n">
         <v>3</v>
@@ -4273,10 +4273,10 @@
         <v>0</v>
       </c>
       <c r="O64" t="n">
-        <v>8.579000000000001</v>
+        <v>8.704000000000001</v>
       </c>
       <c r="P64" t="n">
-        <v>185.2476</v>
+        <v>184.1001</v>
       </c>
       <c r="Q64" t="inlineStr">
         <is>
@@ -4285,7 +4285,7 @@
       </c>
       <c r="R64" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:20</t>
+          <t>2026-05-24 05:37:07</t>
         </is>
       </c>
     </row>
@@ -4294,13 +4294,13 @@
         <v>64</v>
       </c>
       <c r="B65" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C65" t="n">
         <v>5</v>
       </c>
       <c r="D65" t="n">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="E65" t="n">
         <v>44</v>
@@ -4312,31 +4312,31 @@
         <v>49</v>
       </c>
       <c r="H65" t="n">
-        <v>48</v>
+        <v>2</v>
       </c>
       <c r="I65" t="n">
-        <v>168</v>
+        <v>175</v>
       </c>
       <c r="J65" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K65" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L65" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M65" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N65" t="n">
         <v>0</v>
       </c>
       <c r="O65" t="n">
-        <v>8.704000000000001</v>
+        <v>8.822699999999999</v>
       </c>
       <c r="P65" t="n">
-        <v>184.3601</v>
+        <v>183.8567</v>
       </c>
       <c r="Q65" t="inlineStr">
         <is>
@@ -4345,7 +4345,7 @@
       </c>
       <c r="R65" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:20</t>
+          <t>2026-05-24 05:37:07</t>
         </is>
       </c>
     </row>
@@ -4363,7 +4363,7 @@
         <v>5</v>
       </c>
       <c r="E66" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="F66" t="n">
         <v>44</v>
@@ -4372,22 +4372,22 @@
         <v>46</v>
       </c>
       <c r="H66" t="n">
-        <v>29</v>
+        <v>49</v>
       </c>
       <c r="I66" t="n">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="J66" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K66" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L66" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M66" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N66" t="n">
         <v>0</v>
@@ -4396,7 +4396,7 @@
         <v>8.8544</v>
       </c>
       <c r="P66" t="n">
-        <v>183.7959</v>
+        <v>183.6359</v>
       </c>
       <c r="Q66" t="inlineStr">
         <is>
@@ -4405,7 +4405,7 @@
       </c>
       <c r="R66" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:20</t>
+          <t>2026-05-24 05:37:07</t>
         </is>
       </c>
     </row>
@@ -4414,13 +4414,13 @@
         <v>66</v>
       </c>
       <c r="B67" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C67" t="n">
         <v>5</v>
       </c>
       <c r="D67" t="n">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="E67" t="n">
         <v>44</v>
@@ -4432,31 +4432,31 @@
         <v>49</v>
       </c>
       <c r="H67" t="n">
-        <v>21</v>
+        <v>38</v>
       </c>
       <c r="I67" t="n">
-        <v>175</v>
+        <v>166</v>
       </c>
       <c r="J67" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K67" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L67" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M67" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N67" t="n">
         <v>0</v>
       </c>
       <c r="O67" t="n">
-        <v>8.704000000000001</v>
+        <v>8.4048</v>
       </c>
       <c r="P67" t="n">
-        <v>183.6201</v>
+        <v>183.2119</v>
       </c>
       <c r="Q67" t="inlineStr">
         <is>
@@ -4465,7 +4465,7 @@
       </c>
       <c r="R67" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:20</t>
+          <t>2026-05-24 05:37:07</t>
         </is>
       </c>
     </row>
@@ -4477,46 +4477,46 @@
         <v>1</v>
       </c>
       <c r="C68" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D68" t="n">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="E68" t="n">
-        <v>44</v>
+        <v>27</v>
       </c>
       <c r="F68" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="G68" t="n">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="H68" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I68" t="n">
-        <v>175</v>
+        <v>126</v>
       </c>
       <c r="J68" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K68" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L68" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M68" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N68" t="n">
         <v>0</v>
       </c>
       <c r="O68" t="n">
-        <v>8.822699999999999</v>
+        <v>8.7178</v>
       </c>
       <c r="P68" t="n">
-        <v>183.5167</v>
+        <v>181.5945</v>
       </c>
       <c r="Q68" t="inlineStr">
         <is>
@@ -4525,7 +4525,7 @@
       </c>
       <c r="R68" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:20</t>
+          <t>2026-05-24 05:37:07</t>
         </is>
       </c>
     </row>
@@ -4537,46 +4537,46 @@
         <v>1</v>
       </c>
       <c r="C69" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D69" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="E69" t="n">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="F69" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="G69" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="H69" t="n">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="I69" t="n">
-        <v>127</v>
+        <v>170</v>
       </c>
       <c r="J69" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K69" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L69" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M69" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N69" t="n">
         <v>0</v>
       </c>
       <c r="O69" t="n">
-        <v>8.8544</v>
+        <v>8.1142</v>
       </c>
       <c r="P69" t="n">
-        <v>182.9759</v>
+        <v>181.2455</v>
       </c>
       <c r="Q69" t="inlineStr">
         <is>
@@ -4585,7 +4585,7 @@
       </c>
       <c r="R69" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:20</t>
+          <t>2026-05-24 05:37:07</t>
         </is>
       </c>
     </row>
@@ -4597,13 +4597,13 @@
         <v>1</v>
       </c>
       <c r="C70" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D70" t="n">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="E70" t="n">
-        <v>44</v>
+        <v>31</v>
       </c>
       <c r="F70" t="n">
         <v>46</v>
@@ -4612,10 +4612,10 @@
         <v>49</v>
       </c>
       <c r="H70" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="I70" t="n">
-        <v>166</v>
+        <v>135</v>
       </c>
       <c r="J70" t="n">
         <v>3</v>
@@ -4624,19 +4624,19 @@
         <v>3</v>
       </c>
       <c r="L70" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M70" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N70" t="n">
         <v>0</v>
       </c>
       <c r="O70" t="n">
-        <v>8.4048</v>
+        <v>9.5624</v>
       </c>
       <c r="P70" t="n">
-        <v>182.8719</v>
+        <v>181.2261</v>
       </c>
       <c r="Q70" t="inlineStr">
         <is>
@@ -4645,7 +4645,7 @@
       </c>
       <c r="R70" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:20</t>
+          <t>2026-05-24 05:37:07</t>
         </is>
       </c>
     </row>
@@ -4657,31 +4657,31 @@
         <v>1</v>
       </c>
       <c r="C71" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D71" t="n">
-        <v>5</v>
+        <v>27</v>
       </c>
       <c r="E71" t="n">
-        <v>27</v>
+        <v>44</v>
       </c>
       <c r="F71" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="G71" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="H71" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I71" t="n">
-        <v>126</v>
+        <v>172</v>
       </c>
       <c r="J71" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K71" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L71" t="n">
         <v>4</v>
@@ -4693,10 +4693,10 @@
         <v>0</v>
       </c>
       <c r="O71" t="n">
-        <v>8.7178</v>
+        <v>8.2608</v>
       </c>
       <c r="P71" t="n">
-        <v>180.9345</v>
+        <v>180.1719</v>
       </c>
       <c r="Q71" t="inlineStr">
         <is>
@@ -4705,7 +4705,7 @@
       </c>
       <c r="R71" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:20</t>
+          <t>2026-05-24 05:37:07</t>
         </is>
       </c>
     </row>
@@ -4717,13 +4717,13 @@
         <v>1</v>
       </c>
       <c r="C72" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D72" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="E72" t="n">
-        <v>44</v>
+        <v>23</v>
       </c>
       <c r="F72" t="n">
         <v>46</v>
@@ -4732,31 +4732,31 @@
         <v>49</v>
       </c>
       <c r="H72" t="n">
-        <v>29</v>
+        <v>6</v>
       </c>
       <c r="I72" t="n">
-        <v>170</v>
+        <v>127</v>
       </c>
       <c r="J72" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K72" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L72" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M72" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N72" t="n">
         <v>0</v>
       </c>
       <c r="O72" t="n">
-        <v>8.1142</v>
+        <v>9.0465</v>
       </c>
       <c r="P72" t="n">
-        <v>180.9055</v>
+        <v>177.8364</v>
       </c>
       <c r="Q72" t="inlineStr">
         <is>
@@ -4765,187 +4765,7 @@
       </c>
       <c r="R72" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:20</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="n">
-        <v>72</v>
-      </c>
-      <c r="B73" t="n">
-        <v>1</v>
-      </c>
-      <c r="C73" t="n">
-        <v>3</v>
-      </c>
-      <c r="D73" t="n">
-        <v>5</v>
-      </c>
-      <c r="E73" t="n">
-        <v>31</v>
-      </c>
-      <c r="F73" t="n">
-        <v>46</v>
-      </c>
-      <c r="G73" t="n">
-        <v>49</v>
-      </c>
-      <c r="H73" t="n">
-        <v>19</v>
-      </c>
-      <c r="I73" t="n">
-        <v>135</v>
-      </c>
-      <c r="J73" t="n">
-        <v>3</v>
-      </c>
-      <c r="K73" t="n">
-        <v>3</v>
-      </c>
-      <c r="L73" t="n">
-        <v>5</v>
-      </c>
-      <c r="M73" t="n">
-        <v>1</v>
-      </c>
-      <c r="N73" t="n">
-        <v>0</v>
-      </c>
-      <c r="O73" t="n">
-        <v>9.5624</v>
-      </c>
-      <c r="P73" t="n">
-        <v>180.5661</v>
-      </c>
-      <c r="Q73" t="inlineStr">
-        <is>
-          <t>UK49sGeneticOptimizer_v1</t>
-        </is>
-      </c>
-      <c r="R73" t="inlineStr">
-        <is>
-          <t>2026-05-23 08:33:20</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="n">
-        <v>73</v>
-      </c>
-      <c r="B74" t="n">
-        <v>1</v>
-      </c>
-      <c r="C74" t="n">
-        <v>5</v>
-      </c>
-      <c r="D74" t="n">
-        <v>27</v>
-      </c>
-      <c r="E74" t="n">
-        <v>44</v>
-      </c>
-      <c r="F74" t="n">
-        <v>46</v>
-      </c>
-      <c r="G74" t="n">
-        <v>49</v>
-      </c>
-      <c r="H74" t="n">
-        <v>24</v>
-      </c>
-      <c r="I74" t="n">
-        <v>172</v>
-      </c>
-      <c r="J74" t="n">
-        <v>4</v>
-      </c>
-      <c r="K74" t="n">
-        <v>2</v>
-      </c>
-      <c r="L74" t="n">
-        <v>4</v>
-      </c>
-      <c r="M74" t="n">
-        <v>2</v>
-      </c>
-      <c r="N74" t="n">
-        <v>0</v>
-      </c>
-      <c r="O74" t="n">
-        <v>8.2608</v>
-      </c>
-      <c r="P74" t="n">
-        <v>179.8319</v>
-      </c>
-      <c r="Q74" t="inlineStr">
-        <is>
-          <t>UK49sGeneticOptimizer_v1</t>
-        </is>
-      </c>
-      <c r="R74" t="inlineStr">
-        <is>
-          <t>2026-05-23 08:33:20</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="n">
-        <v>74</v>
-      </c>
-      <c r="B75" t="n">
-        <v>1</v>
-      </c>
-      <c r="C75" t="n">
-        <v>3</v>
-      </c>
-      <c r="D75" t="n">
-        <v>5</v>
-      </c>
-      <c r="E75" t="n">
-        <v>23</v>
-      </c>
-      <c r="F75" t="n">
-        <v>46</v>
-      </c>
-      <c r="G75" t="n">
-        <v>49</v>
-      </c>
-      <c r="H75" t="n">
-        <v>26</v>
-      </c>
-      <c r="I75" t="n">
-        <v>127</v>
-      </c>
-      <c r="J75" t="n">
-        <v>2</v>
-      </c>
-      <c r="K75" t="n">
-        <v>4</v>
-      </c>
-      <c r="L75" t="n">
-        <v>5</v>
-      </c>
-      <c r="M75" t="n">
-        <v>1</v>
-      </c>
-      <c r="N75" t="n">
-        <v>0</v>
-      </c>
-      <c r="O75" t="n">
-        <v>9.0465</v>
-      </c>
-      <c r="P75" t="n">
-        <v>177.1764</v>
-      </c>
-      <c r="Q75" t="inlineStr">
-        <is>
-          <t>UK49sGeneticOptimizer_v1</t>
-        </is>
-      </c>
-      <c r="R75" t="inlineStr">
-        <is>
-          <t>2026-05-23 08:33:20</t>
+          <t>2026-05-24 05:37:07</t>
         </is>
       </c>
     </row>
@@ -4985,10 +4805,10 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>184.9217</v>
+        <v>185.3164</v>
       </c>
       <c r="C2" t="n">
-        <v>163.2051</v>
+        <v>163.2829</v>
       </c>
     </row>
     <row r="3">
@@ -4996,10 +4816,10 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>192.2041</v>
+        <v>187.2822</v>
       </c>
       <c r="C3" t="n">
-        <v>171.8109</v>
+        <v>170.9248</v>
       </c>
     </row>
     <row r="4">
@@ -5007,10 +4827,10 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>192.785</v>
+        <v>195.4234</v>
       </c>
       <c r="C4" t="n">
-        <v>177.6655</v>
+        <v>176.4241</v>
       </c>
     </row>
     <row r="5">
@@ -5018,10 +4838,10 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>195.977</v>
+        <v>196.7507</v>
       </c>
       <c r="C5" t="n">
-        <v>181.4765</v>
+        <v>182.0025</v>
       </c>
     </row>
     <row r="6">
@@ -5029,10 +4849,10 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>197.8235</v>
+        <v>199.873</v>
       </c>
       <c r="C6" t="n">
-        <v>185.0472</v>
+        <v>183.6741</v>
       </c>
     </row>
     <row r="7">
@@ -5040,10 +4860,10 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>197.8235</v>
+        <v>199.873</v>
       </c>
       <c r="C7" t="n">
-        <v>186.6795</v>
+        <v>187.6531</v>
       </c>
     </row>
     <row r="8">
@@ -5051,10 +4871,10 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>200.2028</v>
+        <v>200.8628</v>
       </c>
       <c r="C8" t="n">
-        <v>189.9709</v>
+        <v>190.4475</v>
       </c>
     </row>
     <row r="9">
@@ -5062,10 +4882,10 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>200.2028</v>
+        <v>200.8628</v>
       </c>
       <c r="C9" t="n">
-        <v>193.6241</v>
+        <v>191.6657</v>
       </c>
     </row>
     <row r="10">
@@ -5073,10 +4893,10 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>200.2028</v>
+        <v>200.8628</v>
       </c>
       <c r="C10" t="n">
-        <v>195.3716</v>
+        <v>194.8026</v>
       </c>
     </row>
     <row r="11">
@@ -5084,10 +4904,10 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>200.2028</v>
+        <v>200.8628</v>
       </c>
       <c r="C11" t="n">
-        <v>198.8998</v>
+        <v>197.5956</v>
       </c>
     </row>
     <row r="12">
@@ -5095,10 +4915,10 @@
         <v>11</v>
       </c>
       <c r="B12" t="n">
-        <v>200.2028</v>
+        <v>200.8628</v>
       </c>
       <c r="C12" t="n">
-        <v>198.0531</v>
+        <v>198.0932</v>
       </c>
     </row>
     <row r="13">
@@ -5106,10 +4926,10 @@
         <v>12</v>
       </c>
       <c r="B13" t="n">
-        <v>200.2028</v>
+        <v>200.8628</v>
       </c>
       <c r="C13" t="n">
-        <v>197.9675</v>
+        <v>198.8608</v>
       </c>
     </row>
     <row r="14">
@@ -5117,10 +4937,10 @@
         <v>13</v>
       </c>
       <c r="B14" t="n">
-        <v>200.2028</v>
+        <v>200.8628</v>
       </c>
       <c r="C14" t="n">
-        <v>197.9629</v>
+        <v>198.4005</v>
       </c>
     </row>
     <row r="15">
@@ -5128,10 +4948,10 @@
         <v>14</v>
       </c>
       <c r="B15" t="n">
-        <v>200.2028</v>
+        <v>200.8628</v>
       </c>
       <c r="C15" t="n">
-        <v>198.5364</v>
+        <v>199.2691</v>
       </c>
     </row>
     <row r="16">
@@ -5139,10 +4959,10 @@
         <v>15</v>
       </c>
       <c r="B16" t="n">
-        <v>200.2028</v>
+        <v>200.8628</v>
       </c>
       <c r="C16" t="n">
-        <v>198.4018</v>
+        <v>198.9758</v>
       </c>
     </row>
     <row r="17">
@@ -5150,10 +4970,10 @@
         <v>16</v>
       </c>
       <c r="B17" t="n">
-        <v>200.2028</v>
+        <v>200.8628</v>
       </c>
       <c r="C17" t="n">
-        <v>198.4063</v>
+        <v>199.2431</v>
       </c>
     </row>
     <row r="18">
@@ -5161,10 +4981,10 @@
         <v>17</v>
       </c>
       <c r="B18" t="n">
-        <v>200.2028</v>
+        <v>200.8628</v>
       </c>
       <c r="C18" t="n">
-        <v>198.697</v>
+        <v>199.2249</v>
       </c>
     </row>
     <row r="19">
@@ -5172,10 +4992,10 @@
         <v>18</v>
       </c>
       <c r="B19" t="n">
-        <v>200.2028</v>
+        <v>200.8628</v>
       </c>
       <c r="C19" t="n">
-        <v>198.2298</v>
+        <v>198.8481</v>
       </c>
     </row>
     <row r="20">
@@ -5183,10 +5003,10 @@
         <v>19</v>
       </c>
       <c r="B20" t="n">
-        <v>200.2028</v>
+        <v>200.8628</v>
       </c>
       <c r="C20" t="n">
-        <v>197.8945</v>
+        <v>198.5775</v>
       </c>
     </row>
     <row r="21">
@@ -5194,10 +5014,10 @@
         <v>20</v>
       </c>
       <c r="B21" t="n">
-        <v>200.2028</v>
+        <v>200.8628</v>
       </c>
       <c r="C21" t="n">
-        <v>198.5843</v>
+        <v>199.1525</v>
       </c>
     </row>
     <row r="22">
@@ -5205,10 +5025,10 @@
         <v>21</v>
       </c>
       <c r="B22" t="n">
-        <v>200.2028</v>
+        <v>200.8628</v>
       </c>
       <c r="C22" t="n">
-        <v>198.8248</v>
+        <v>199.5745</v>
       </c>
     </row>
     <row r="23">
@@ -5216,10 +5036,10 @@
         <v>22</v>
       </c>
       <c r="B23" t="n">
-        <v>200.2028</v>
+        <v>200.8628</v>
       </c>
       <c r="C23" t="n">
-        <v>198.4169</v>
+        <v>199.0941</v>
       </c>
     </row>
     <row r="24">
@@ -5227,10 +5047,10 @@
         <v>23</v>
       </c>
       <c r="B24" t="n">
-        <v>200.2028</v>
+        <v>200.8628</v>
       </c>
       <c r="C24" t="n">
-        <v>198.5959</v>
+        <v>199.0645</v>
       </c>
     </row>
     <row r="25">
@@ -5238,10 +5058,10 @@
         <v>24</v>
       </c>
       <c r="B25" t="n">
-        <v>200.2028</v>
+        <v>200.8628</v>
       </c>
       <c r="C25" t="n">
-        <v>198.6475</v>
+        <v>199.2743</v>
       </c>
     </row>
     <row r="26">
@@ -5249,10 +5069,10 @@
         <v>25</v>
       </c>
       <c r="B26" t="n">
-        <v>200.2028</v>
+        <v>200.8628</v>
       </c>
       <c r="C26" t="n">
-        <v>198.3802</v>
+        <v>199.1917</v>
       </c>
     </row>
     <row r="27">
@@ -5260,10 +5080,10 @@
         <v>26</v>
       </c>
       <c r="B27" t="n">
-        <v>200.2028</v>
+        <v>200.8628</v>
       </c>
       <c r="C27" t="n">
-        <v>198.4205</v>
+        <v>198.9672</v>
       </c>
     </row>
     <row r="28">
@@ -5271,10 +5091,10 @@
         <v>27</v>
       </c>
       <c r="B28" t="n">
-        <v>200.2028</v>
+        <v>200.8628</v>
       </c>
       <c r="C28" t="n">
-        <v>198.5182</v>
+        <v>198.9732</v>
       </c>
     </row>
     <row r="29">
@@ -5282,10 +5102,10 @@
         <v>28</v>
       </c>
       <c r="B29" t="n">
-        <v>200.2028</v>
+        <v>200.8628</v>
       </c>
       <c r="C29" t="n">
-        <v>198.4365</v>
+        <v>199.3355</v>
       </c>
     </row>
     <row r="30">
@@ -5293,10 +5113,10 @@
         <v>29</v>
       </c>
       <c r="B30" t="n">
-        <v>200.2028</v>
+        <v>200.8628</v>
       </c>
       <c r="C30" t="n">
-        <v>198.7438</v>
+        <v>199.4118</v>
       </c>
     </row>
     <row r="31">
@@ -5304,10 +5124,10 @@
         <v>30</v>
       </c>
       <c r="B31" t="n">
-        <v>200.2028</v>
+        <v>200.8628</v>
       </c>
       <c r="C31" t="n">
-        <v>198.168</v>
+        <v>198.7681</v>
       </c>
     </row>
     <row r="32">
@@ -5315,10 +5135,10 @@
         <v>31</v>
       </c>
       <c r="B32" t="n">
-        <v>200.2028</v>
+        <v>200.8628</v>
       </c>
       <c r="C32" t="n">
-        <v>198.5964</v>
+        <v>199.194</v>
       </c>
     </row>
     <row r="33">
@@ -5326,10 +5146,10 @@
         <v>32</v>
       </c>
       <c r="B33" t="n">
-        <v>200.2028</v>
+        <v>200.8628</v>
       </c>
       <c r="C33" t="n">
-        <v>198.235</v>
+        <v>198.9555</v>
       </c>
     </row>
     <row r="34">
@@ -5337,10 +5157,10 @@
         <v>33</v>
       </c>
       <c r="B34" t="n">
-        <v>200.2028</v>
+        <v>200.8628</v>
       </c>
       <c r="C34" t="n">
-        <v>197.988</v>
+        <v>198.5969</v>
       </c>
     </row>
     <row r="35">
@@ -5348,10 +5168,10 @@
         <v>34</v>
       </c>
       <c r="B35" t="n">
-        <v>200.2028</v>
+        <v>200.8628</v>
       </c>
       <c r="C35" t="n">
-        <v>198.6299</v>
+        <v>199.3215</v>
       </c>
     </row>
     <row r="36">
@@ -5359,10 +5179,10 @@
         <v>35</v>
       </c>
       <c r="B36" t="n">
-        <v>200.2028</v>
+        <v>200.8628</v>
       </c>
       <c r="C36" t="n">
-        <v>198.1391</v>
+        <v>198.6748</v>
       </c>
     </row>
     <row r="37">
@@ -5370,10 +5190,10 @@
         <v>36</v>
       </c>
       <c r="B37" t="n">
-        <v>200.2028</v>
+        <v>200.8628</v>
       </c>
       <c r="C37" t="n">
-        <v>197.873</v>
+        <v>198.5806</v>
       </c>
     </row>
     <row r="38">
@@ -5381,10 +5201,10 @@
         <v>37</v>
       </c>
       <c r="B38" t="n">
-        <v>200.2028</v>
+        <v>200.8628</v>
       </c>
       <c r="C38" t="n">
-        <v>198.4196</v>
+        <v>199.1297</v>
       </c>
     </row>
     <row r="39">
@@ -5392,10 +5212,10 @@
         <v>38</v>
       </c>
       <c r="B39" t="n">
-        <v>200.2028</v>
+        <v>200.8628</v>
       </c>
       <c r="C39" t="n">
-        <v>198.4341</v>
+        <v>198.9588</v>
       </c>
     </row>
     <row r="40">
@@ -5403,10 +5223,10 @@
         <v>39</v>
       </c>
       <c r="B40" t="n">
-        <v>200.2028</v>
+        <v>200.8628</v>
       </c>
       <c r="C40" t="n">
-        <v>198.1242</v>
+        <v>198.8646</v>
       </c>
     </row>
     <row r="41">
@@ -5414,10 +5234,10 @@
         <v>40</v>
       </c>
       <c r="B41" t="n">
-        <v>200.2028</v>
+        <v>200.8628</v>
       </c>
       <c r="C41" t="n">
-        <v>198.8308</v>
+        <v>199.4256</v>
       </c>
     </row>
     <row r="42">
@@ -5425,10 +5245,10 @@
         <v>41</v>
       </c>
       <c r="B42" t="n">
-        <v>200.2028</v>
+        <v>200.8628</v>
       </c>
       <c r="C42" t="n">
-        <v>197.8849</v>
+        <v>198.4707</v>
       </c>
     </row>
     <row r="43">
@@ -5436,10 +5256,10 @@
         <v>42</v>
       </c>
       <c r="B43" t="n">
-        <v>200.2028</v>
+        <v>200.8628</v>
       </c>
       <c r="C43" t="n">
-        <v>198.3993</v>
+        <v>199.0786</v>
       </c>
     </row>
     <row r="44">
@@ -5447,10 +5267,10 @@
         <v>43</v>
       </c>
       <c r="B44" t="n">
-        <v>200.2028</v>
+        <v>200.8628</v>
       </c>
       <c r="C44" t="n">
-        <v>198.9409</v>
+        <v>199.467</v>
       </c>
     </row>
     <row r="45">
@@ -5458,10 +5278,10 @@
         <v>44</v>
       </c>
       <c r="B45" t="n">
-        <v>200.2028</v>
+        <v>200.8628</v>
       </c>
       <c r="C45" t="n">
-        <v>198.9175</v>
+        <v>199.6442</v>
       </c>
     </row>
     <row r="46">
@@ -5469,10 +5289,10 @@
         <v>45</v>
       </c>
       <c r="B46" t="n">
-        <v>200.2028</v>
+        <v>200.8628</v>
       </c>
       <c r="C46" t="n">
-        <v>198.545</v>
+        <v>199.2963</v>
       </c>
     </row>
     <row r="47">
@@ -5480,10 +5300,10 @@
         <v>46</v>
       </c>
       <c r="B47" t="n">
-        <v>200.2028</v>
+        <v>200.8628</v>
       </c>
       <c r="C47" t="n">
-        <v>198.3851</v>
+        <v>198.914</v>
       </c>
     </row>
     <row r="48">
@@ -5491,10 +5311,10 @@
         <v>47</v>
       </c>
       <c r="B48" t="n">
-        <v>200.2028</v>
+        <v>200.8628</v>
       </c>
       <c r="C48" t="n">
-        <v>197.9867</v>
+        <v>198.8055</v>
       </c>
     </row>
     <row r="49">
@@ -5502,10 +5322,10 @@
         <v>48</v>
       </c>
       <c r="B49" t="n">
-        <v>200.2028</v>
+        <v>200.8628</v>
       </c>
       <c r="C49" t="n">
-        <v>198.1904</v>
+        <v>198.6878</v>
       </c>
     </row>
     <row r="50">
@@ -5513,10 +5333,10 @@
         <v>49</v>
       </c>
       <c r="B50" t="n">
-        <v>200.2028</v>
+        <v>200.8628</v>
       </c>
       <c r="C50" t="n">
-        <v>197.8119</v>
+        <v>198.4252</v>
       </c>
     </row>
     <row r="51">
@@ -5524,10 +5344,10 @@
         <v>50</v>
       </c>
       <c r="B51" t="n">
-        <v>200.2028</v>
+        <v>200.8628</v>
       </c>
       <c r="C51" t="n">
-        <v>198.4427</v>
+        <v>199.2495</v>
       </c>
     </row>
     <row r="52">
@@ -5535,10 +5355,10 @@
         <v>51</v>
       </c>
       <c r="B52" t="n">
-        <v>200.2028</v>
+        <v>200.8628</v>
       </c>
       <c r="C52" t="n">
-        <v>199.0039</v>
+        <v>199.537</v>
       </c>
     </row>
     <row r="53">
@@ -5546,10 +5366,10 @@
         <v>52</v>
       </c>
       <c r="B53" t="n">
-        <v>200.2028</v>
+        <v>200.8628</v>
       </c>
       <c r="C53" t="n">
-        <v>198.6232</v>
+        <v>199.2424</v>
       </c>
     </row>
     <row r="54">
@@ -5557,10 +5377,10 @@
         <v>53</v>
       </c>
       <c r="B54" t="n">
-        <v>200.2028</v>
+        <v>200.8628</v>
       </c>
       <c r="C54" t="n">
-        <v>198.1959</v>
+        <v>198.7908</v>
       </c>
     </row>
     <row r="55">
@@ -5568,10 +5388,10 @@
         <v>54</v>
       </c>
       <c r="B55" t="n">
-        <v>200.2028</v>
+        <v>200.8628</v>
       </c>
       <c r="C55" t="n">
-        <v>198.2886</v>
+        <v>198.9297</v>
       </c>
     </row>
     <row r="56">
@@ -5579,10 +5399,10 @@
         <v>55</v>
       </c>
       <c r="B56" t="n">
-        <v>200.2028</v>
+        <v>200.8628</v>
       </c>
       <c r="C56" t="n">
-        <v>198.5052</v>
+        <v>199.1739</v>
       </c>
     </row>
     <row r="57">
@@ -5590,10 +5410,10 @@
         <v>56</v>
       </c>
       <c r="B57" t="n">
-        <v>200.2028</v>
+        <v>200.8628</v>
       </c>
       <c r="C57" t="n">
-        <v>198.7935</v>
+        <v>199.4678</v>
       </c>
     </row>
     <row r="58">
@@ -5601,10 +5421,10 @@
         <v>57</v>
       </c>
       <c r="B58" t="n">
-        <v>200.2028</v>
+        <v>200.8628</v>
       </c>
       <c r="C58" t="n">
-        <v>198.1261</v>
+        <v>198.81</v>
       </c>
     </row>
     <row r="59">
@@ -5612,10 +5432,10 @@
         <v>58</v>
       </c>
       <c r="B59" t="n">
-        <v>200.2028</v>
+        <v>200.8628</v>
       </c>
       <c r="C59" t="n">
-        <v>198.3807</v>
+        <v>198.9308</v>
       </c>
     </row>
     <row r="60">
@@ -5623,10 +5443,10 @@
         <v>59</v>
       </c>
       <c r="B60" t="n">
-        <v>200.2028</v>
+        <v>200.8628</v>
       </c>
       <c r="C60" t="n">
-        <v>197.8234</v>
+        <v>198.4026</v>
       </c>
     </row>
     <row r="61">
@@ -5634,10 +5454,10 @@
         <v>60</v>
       </c>
       <c r="B61" t="n">
-        <v>200.2028</v>
+        <v>200.8628</v>
       </c>
       <c r="C61" t="n">
-        <v>198.3317</v>
+        <v>199.0792</v>
       </c>
     </row>
   </sheetData>

--- a/data/exports/optimization/uk49s_genetic_optimizer_results.xlsx
+++ b/data/exports/optimization/uk49s_genetic_optimizer_results.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R72"/>
+  <dimension ref="A1:R73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -532,7 +532,7 @@
         <v>49</v>
       </c>
       <c r="H2" t="n">
-        <v>2</v>
+        <v>31</v>
       </c>
       <c r="I2" t="n">
         <v>148</v>
@@ -556,7 +556,7 @@
         <v>14.7051</v>
       </c>
       <c r="P2" t="n">
-        <v>200.8628</v>
+        <v>201.0628</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -565,7 +565,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-05-24 05:37:07</t>
+          <t>2026-05-25 14:34:22</t>
         </is>
       </c>
     </row>
@@ -592,7 +592,7 @@
         <v>49</v>
       </c>
       <c r="H3" t="n">
-        <v>6</v>
+        <v>38</v>
       </c>
       <c r="I3" t="n">
         <v>148</v>
@@ -616,7 +616,7 @@
         <v>14.7051</v>
       </c>
       <c r="P3" t="n">
-        <v>200.8628</v>
+        <v>201.0628</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -625,7 +625,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-05-24 05:37:07</t>
+          <t>2026-05-25 14:34:22</t>
         </is>
       </c>
     </row>
@@ -652,7 +652,7 @@
         <v>49</v>
       </c>
       <c r="H4" t="n">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="I4" t="n">
         <v>148</v>
@@ -676,7 +676,7 @@
         <v>14.7051</v>
       </c>
       <c r="P4" t="n">
-        <v>200.8628</v>
+        <v>201.0628</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -685,7 +685,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2026-05-24 05:37:07</t>
+          <t>2026-05-25 14:34:22</t>
         </is>
       </c>
     </row>
@@ -712,7 +712,7 @@
         <v>49</v>
       </c>
       <c r="H5" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="I5" t="n">
         <v>148</v>
@@ -736,7 +736,7 @@
         <v>14.7051</v>
       </c>
       <c r="P5" t="n">
-        <v>200.8628</v>
+        <v>201.0628</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -745,7 +745,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-05-24 05:37:07</t>
+          <t>2026-05-25 14:34:22</t>
         </is>
       </c>
     </row>
@@ -772,7 +772,7 @@
         <v>49</v>
       </c>
       <c r="H6" t="n">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="I6" t="n">
         <v>148</v>
@@ -796,7 +796,7 @@
         <v>14.7051</v>
       </c>
       <c r="P6" t="n">
-        <v>200.8628</v>
+        <v>201.0628</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -805,7 +805,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>2026-05-24 05:37:07</t>
+          <t>2026-05-25 14:34:22</t>
         </is>
       </c>
     </row>
@@ -832,7 +832,7 @@
         <v>49</v>
       </c>
       <c r="H7" t="n">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="I7" t="n">
         <v>148</v>
@@ -856,7 +856,7 @@
         <v>14.7051</v>
       </c>
       <c r="P7" t="n">
-        <v>200.8628</v>
+        <v>201.0628</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
@@ -865,7 +865,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>2026-05-24 05:37:07</t>
+          <t>2026-05-25 14:34:22</t>
         </is>
       </c>
     </row>
@@ -892,7 +892,7 @@
         <v>49</v>
       </c>
       <c r="H8" t="n">
-        <v>9</v>
+        <v>43</v>
       </c>
       <c r="I8" t="n">
         <v>148</v>
@@ -916,7 +916,7 @@
         <v>14.7051</v>
       </c>
       <c r="P8" t="n">
-        <v>200.8628</v>
+        <v>201.0628</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>2026-05-24 05:37:07</t>
+          <t>2026-05-25 14:34:22</t>
         </is>
       </c>
     </row>
@@ -952,7 +952,7 @@
         <v>49</v>
       </c>
       <c r="H9" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="I9" t="n">
         <v>148</v>
@@ -976,7 +976,7 @@
         <v>14.7051</v>
       </c>
       <c r="P9" t="n">
-        <v>200.8628</v>
+        <v>201.0628</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
@@ -985,7 +985,7 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>2026-05-24 05:37:07</t>
+          <t>2026-05-25 14:34:22</t>
         </is>
       </c>
     </row>
@@ -1012,7 +1012,7 @@
         <v>49</v>
       </c>
       <c r="H10" t="n">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="I10" t="n">
         <v>148</v>
@@ -1036,7 +1036,7 @@
         <v>14.7051</v>
       </c>
       <c r="P10" t="n">
-        <v>200.8628</v>
+        <v>201.0628</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
@@ -1045,7 +1045,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>2026-05-24 05:37:07</t>
+          <t>2026-05-25 14:34:22</t>
         </is>
       </c>
     </row>
@@ -1072,7 +1072,7 @@
         <v>49</v>
       </c>
       <c r="H11" t="n">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="I11" t="n">
         <v>148</v>
@@ -1096,7 +1096,7 @@
         <v>14.7051</v>
       </c>
       <c r="P11" t="n">
-        <v>200.8628</v>
+        <v>201.0628</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
@@ -1105,7 +1105,7 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>2026-05-24 05:37:07</t>
+          <t>2026-05-25 14:34:22</t>
         </is>
       </c>
     </row>
@@ -1132,7 +1132,7 @@
         <v>49</v>
       </c>
       <c r="H12" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="I12" t="n">
         <v>148</v>
@@ -1156,7 +1156,7 @@
         <v>14.7051</v>
       </c>
       <c r="P12" t="n">
-        <v>200.8628</v>
+        <v>201.0628</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
@@ -1165,7 +1165,7 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>2026-05-24 05:37:07</t>
+          <t>2026-05-25 14:34:22</t>
         </is>
       </c>
     </row>
@@ -1192,7 +1192,7 @@
         <v>49</v>
       </c>
       <c r="H13" t="n">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="I13" t="n">
         <v>148</v>
@@ -1216,7 +1216,7 @@
         <v>14.7051</v>
       </c>
       <c r="P13" t="n">
-        <v>200.8628</v>
+        <v>201.0628</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
@@ -1225,7 +1225,7 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>2026-05-24 05:37:07</t>
+          <t>2026-05-25 14:34:22</t>
         </is>
       </c>
     </row>
@@ -1252,7 +1252,7 @@
         <v>49</v>
       </c>
       <c r="H14" t="n">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="I14" t="n">
         <v>148</v>
@@ -1276,7 +1276,7 @@
         <v>14.7051</v>
       </c>
       <c r="P14" t="n">
-        <v>200.8628</v>
+        <v>201.0628</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
@@ -1285,7 +1285,7 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>2026-05-24 05:37:07</t>
+          <t>2026-05-25 14:34:22</t>
         </is>
       </c>
     </row>
@@ -1312,7 +1312,7 @@
         <v>49</v>
       </c>
       <c r="H15" t="n">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="I15" t="n">
         <v>148</v>
@@ -1336,7 +1336,7 @@
         <v>14.7051</v>
       </c>
       <c r="P15" t="n">
-        <v>200.8628</v>
+        <v>201.0628</v>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
@@ -1345,7 +1345,7 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>2026-05-24 05:37:07</t>
+          <t>2026-05-25 14:34:22</t>
         </is>
       </c>
     </row>
@@ -1372,7 +1372,7 @@
         <v>49</v>
       </c>
       <c r="H16" t="n">
-        <v>10</v>
+        <v>33</v>
       </c>
       <c r="I16" t="n">
         <v>148</v>
@@ -1396,7 +1396,7 @@
         <v>14.7051</v>
       </c>
       <c r="P16" t="n">
-        <v>200.8628</v>
+        <v>201.0628</v>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
@@ -1405,7 +1405,7 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>2026-05-24 05:37:07</t>
+          <t>2026-05-25 14:34:22</t>
         </is>
       </c>
     </row>
@@ -1432,7 +1432,7 @@
         <v>49</v>
       </c>
       <c r="H17" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="I17" t="n">
         <v>148</v>
@@ -1456,7 +1456,7 @@
         <v>14.7051</v>
       </c>
       <c r="P17" t="n">
-        <v>200.8628</v>
+        <v>201.0628</v>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
@@ -1465,7 +1465,7 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>2026-05-24 05:37:07</t>
+          <t>2026-05-25 14:34:22</t>
         </is>
       </c>
     </row>
@@ -1492,7 +1492,7 @@
         <v>49</v>
       </c>
       <c r="H18" t="n">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="I18" t="n">
         <v>148</v>
@@ -1516,7 +1516,7 @@
         <v>14.7051</v>
       </c>
       <c r="P18" t="n">
-        <v>200.8628</v>
+        <v>201.0628</v>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
@@ -1525,7 +1525,7 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>2026-05-24 05:37:07</t>
+          <t>2026-05-25 14:34:22</t>
         </is>
       </c>
     </row>
@@ -1552,7 +1552,7 @@
         <v>49</v>
       </c>
       <c r="H19" t="n">
-        <v>33</v>
+        <v>48</v>
       </c>
       <c r="I19" t="n">
         <v>148</v>
@@ -1576,7 +1576,7 @@
         <v>14.7051</v>
       </c>
       <c r="P19" t="n">
-        <v>200.8628</v>
+        <v>201.0628</v>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
@@ -1585,7 +1585,7 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>2026-05-24 05:37:07</t>
+          <t>2026-05-25 14:34:22</t>
         </is>
       </c>
     </row>
@@ -1612,7 +1612,7 @@
         <v>49</v>
       </c>
       <c r="H20" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="I20" t="n">
         <v>148</v>
@@ -1636,7 +1636,7 @@
         <v>14.7051</v>
       </c>
       <c r="P20" t="n">
-        <v>200.8628</v>
+        <v>201.0628</v>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
@@ -1645,7 +1645,7 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>2026-05-24 05:37:07</t>
+          <t>2026-05-25 14:34:22</t>
         </is>
       </c>
     </row>
@@ -1672,7 +1672,7 @@
         <v>49</v>
       </c>
       <c r="H21" t="n">
-        <v>31</v>
+        <v>7</v>
       </c>
       <c r="I21" t="n">
         <v>148</v>
@@ -1696,7 +1696,7 @@
         <v>14.7051</v>
       </c>
       <c r="P21" t="n">
-        <v>200.8628</v>
+        <v>201.0628</v>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
@@ -1705,7 +1705,7 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>2026-05-24 05:37:07</t>
+          <t>2026-05-25 14:34:22</t>
         </is>
       </c>
     </row>
@@ -1732,7 +1732,7 @@
         <v>49</v>
       </c>
       <c r="H22" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="I22" t="n">
         <v>148</v>
@@ -1756,7 +1756,7 @@
         <v>14.7051</v>
       </c>
       <c r="P22" t="n">
-        <v>200.8628</v>
+        <v>201.0628</v>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
@@ -1765,7 +1765,7 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>2026-05-24 05:37:07</t>
+          <t>2026-05-25 14:34:22</t>
         </is>
       </c>
     </row>
@@ -1792,7 +1792,7 @@
         <v>49</v>
       </c>
       <c r="H23" t="n">
-        <v>47</v>
+        <v>15</v>
       </c>
       <c r="I23" t="n">
         <v>148</v>
@@ -1816,7 +1816,7 @@
         <v>14.7051</v>
       </c>
       <c r="P23" t="n">
-        <v>200.8628</v>
+        <v>201.0628</v>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
@@ -1825,7 +1825,7 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>2026-05-24 05:37:07</t>
+          <t>2026-05-25 14:34:22</t>
         </is>
       </c>
     </row>
@@ -1852,7 +1852,7 @@
         <v>49</v>
       </c>
       <c r="H24" t="n">
-        <v>14</v>
+        <v>47</v>
       </c>
       <c r="I24" t="n">
         <v>148</v>
@@ -1876,7 +1876,7 @@
         <v>14.7051</v>
       </c>
       <c r="P24" t="n">
-        <v>200.8628</v>
+        <v>201.0628</v>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
@@ -1885,7 +1885,7 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>2026-05-24 05:37:07</t>
+          <t>2026-05-25 14:34:22</t>
         </is>
       </c>
     </row>
@@ -1912,7 +1912,7 @@
         <v>49</v>
       </c>
       <c r="H25" t="n">
-        <v>42</v>
+        <v>14</v>
       </c>
       <c r="I25" t="n">
         <v>148</v>
@@ -1936,7 +1936,7 @@
         <v>14.7051</v>
       </c>
       <c r="P25" t="n">
-        <v>200.8628</v>
+        <v>201.0628</v>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
@@ -1945,7 +1945,7 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>2026-05-24 05:37:07</t>
+          <t>2026-05-25 14:34:22</t>
         </is>
       </c>
     </row>
@@ -1972,7 +1972,7 @@
         <v>49</v>
       </c>
       <c r="H26" t="n">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="I26" t="n">
         <v>148</v>
@@ -1996,7 +1996,7 @@
         <v>14.7051</v>
       </c>
       <c r="P26" t="n">
-        <v>200.8628</v>
+        <v>201.0628</v>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
@@ -2005,7 +2005,7 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>2026-05-24 05:37:07</t>
+          <t>2026-05-25 14:34:22</t>
         </is>
       </c>
     </row>
@@ -2032,7 +2032,7 @@
         <v>49</v>
       </c>
       <c r="H27" t="n">
-        <v>22</v>
+        <v>42</v>
       </c>
       <c r="I27" t="n">
         <v>148</v>
@@ -2056,7 +2056,7 @@
         <v>14.7051</v>
       </c>
       <c r="P27" t="n">
-        <v>200.8628</v>
+        <v>201.0628</v>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
@@ -2065,7 +2065,7 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>2026-05-24 05:37:07</t>
+          <t>2026-05-25 14:34:22</t>
         </is>
       </c>
     </row>
@@ -2092,7 +2092,7 @@
         <v>49</v>
       </c>
       <c r="H28" t="n">
-        <v>39</v>
+        <v>21</v>
       </c>
       <c r="I28" t="n">
         <v>148</v>
@@ -2116,7 +2116,7 @@
         <v>14.7051</v>
       </c>
       <c r="P28" t="n">
-        <v>200.8628</v>
+        <v>201.0628</v>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
@@ -2125,7 +2125,7 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>2026-05-24 05:37:07</t>
+          <t>2026-05-25 14:34:22</t>
         </is>
       </c>
     </row>
@@ -2152,7 +2152,7 @@
         <v>49</v>
       </c>
       <c r="H29" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I29" t="n">
         <v>148</v>
@@ -2176,7 +2176,7 @@
         <v>14.7051</v>
       </c>
       <c r="P29" t="n">
-        <v>200.8628</v>
+        <v>201.0628</v>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
@@ -2185,7 +2185,7 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>2026-05-24 05:37:07</t>
+          <t>2026-05-25 14:34:22</t>
         </is>
       </c>
     </row>
@@ -2212,7 +2212,7 @@
         <v>49</v>
       </c>
       <c r="H30" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="I30" t="n">
         <v>148</v>
@@ -2236,7 +2236,7 @@
         <v>14.7051</v>
       </c>
       <c r="P30" t="n">
-        <v>200.8628</v>
+        <v>201.0628</v>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
@@ -2245,7 +2245,7 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>2026-05-24 05:37:07</t>
+          <t>2026-05-25 14:34:22</t>
         </is>
       </c>
     </row>
@@ -2257,10 +2257,10 @@
         <v>1</v>
       </c>
       <c r="C31" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D31" t="n">
-        <v>42</v>
+        <v>5</v>
       </c>
       <c r="E31" t="n">
         <v>44</v>
@@ -2272,31 +2272,31 @@
         <v>49</v>
       </c>
       <c r="H31" t="n">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="I31" t="n">
-        <v>187</v>
+        <v>148</v>
       </c>
       <c r="J31" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L31" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M31" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N31" t="n">
         <v>0</v>
       </c>
       <c r="O31" t="n">
-        <v>13.7201</v>
+        <v>14.7051</v>
       </c>
       <c r="P31" t="n">
-        <v>197.6001</v>
+        <v>201.0628</v>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
@@ -2305,7 +2305,7 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>2026-05-24 05:37:07</t>
+          <t>2026-05-25 14:34:22</t>
         </is>
       </c>
     </row>
@@ -2314,7 +2314,7 @@
         <v>31</v>
       </c>
       <c r="B32" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C32" t="n">
         <v>3</v>
@@ -2332,10 +2332,10 @@
         <v>49</v>
       </c>
       <c r="H32" t="n">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="I32" t="n">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="J32" t="n">
         <v>3</v>
@@ -2344,19 +2344,19 @@
         <v>3</v>
       </c>
       <c r="L32" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M32" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O32" t="n">
-        <v>14.8135</v>
+        <v>14.7051</v>
       </c>
       <c r="P32" t="n">
-        <v>197.1138</v>
+        <v>201.0628</v>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
@@ -2365,7 +2365,7 @@
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>2026-05-24 05:37:07</t>
+          <t>2026-05-25 14:34:22</t>
         </is>
       </c>
     </row>
@@ -2377,46 +2377,46 @@
         <v>1</v>
       </c>
       <c r="C33" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D33" t="n">
-        <v>5</v>
+        <v>42</v>
       </c>
       <c r="E33" t="n">
-        <v>8</v>
+        <v>44</v>
       </c>
       <c r="F33" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="G33" t="n">
         <v>49</v>
       </c>
       <c r="H33" t="n">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="I33" t="n">
-        <v>110</v>
+        <v>187</v>
       </c>
       <c r="J33" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K33" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L33" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M33" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N33" t="n">
         <v>0</v>
       </c>
       <c r="O33" t="n">
-        <v>13.2454</v>
+        <v>13.7201</v>
       </c>
       <c r="P33" t="n">
-        <v>196.2934</v>
+        <v>197.8001</v>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
@@ -2425,7 +2425,7 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>2026-05-24 05:37:07</t>
+          <t>2026-05-25 14:34:22</t>
         </is>
       </c>
     </row>
@@ -2434,7 +2434,7 @@
         <v>33</v>
       </c>
       <c r="B34" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C34" t="n">
         <v>3</v>
@@ -2443,19 +2443,19 @@
         <v>5</v>
       </c>
       <c r="E34" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="F34" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="G34" t="n">
         <v>49</v>
       </c>
       <c r="H34" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="I34" t="n">
-        <v>142</v>
+        <v>149</v>
       </c>
       <c r="J34" t="n">
         <v>3</v>
@@ -2464,19 +2464,19 @@
         <v>3</v>
       </c>
       <c r="L34" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M34" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O34" t="n">
-        <v>12.753</v>
+        <v>14.8135</v>
       </c>
       <c r="P34" t="n">
-        <v>196.0826</v>
+        <v>197.3138</v>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
@@ -2485,7 +2485,7 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>2026-05-24 05:37:07</t>
+          <t>2026-05-25 14:34:22</t>
         </is>
       </c>
     </row>
@@ -2500,43 +2500,43 @@
         <v>3</v>
       </c>
       <c r="D35" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E35" t="n">
-        <v>44</v>
+        <v>8</v>
       </c>
       <c r="F35" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="G35" t="n">
         <v>49</v>
       </c>
       <c r="H35" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="I35" t="n">
-        <v>147</v>
+        <v>110</v>
       </c>
       <c r="J35" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K35" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L35" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M35" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O35" t="n">
-        <v>15.2132</v>
+        <v>13.2454</v>
       </c>
       <c r="P35" t="n">
-        <v>195.6929</v>
+        <v>196.4934</v>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
@@ -2545,7 +2545,7 @@
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>2026-05-24 05:37:07</t>
+          <t>2026-05-25 14:34:22</t>
         </is>
       </c>
     </row>
@@ -2557,25 +2557,25 @@
         <v>1</v>
       </c>
       <c r="C36" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D36" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E36" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="F36" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="G36" t="n">
         <v>49</v>
       </c>
       <c r="H36" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="I36" t="n">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="J36" t="n">
         <v>3</v>
@@ -2584,19 +2584,19 @@
         <v>3</v>
       </c>
       <c r="L36" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M36" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N36" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O36" t="n">
-        <v>15.7175</v>
+        <v>12.753</v>
       </c>
       <c r="P36" t="n">
-        <v>195.0938</v>
+        <v>196.2826</v>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
@@ -2605,7 +2605,7 @@
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>2026-05-24 05:37:07</t>
+          <t>2026-05-25 14:34:22</t>
         </is>
       </c>
     </row>
@@ -2620,10 +2620,10 @@
         <v>3</v>
       </c>
       <c r="D37" t="n">
-        <v>44</v>
+        <v>4</v>
       </c>
       <c r="E37" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F37" t="n">
         <v>46</v>
@@ -2632,31 +2632,31 @@
         <v>49</v>
       </c>
       <c r="H37" t="n">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="I37" t="n">
-        <v>188</v>
+        <v>147</v>
       </c>
       <c r="J37" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K37" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L37" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M37" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N37" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O37" t="n">
-        <v>15.7175</v>
+        <v>15.2132</v>
       </c>
       <c r="P37" t="n">
-        <v>194.9938</v>
+        <v>195.8929</v>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
@@ -2665,7 +2665,7 @@
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>2026-05-24 05:37:07</t>
+          <t>2026-05-25 14:34:22</t>
         </is>
       </c>
     </row>
@@ -2677,46 +2677,46 @@
         <v>1</v>
       </c>
       <c r="C38" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D38" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E38" t="n">
-        <v>9</v>
+        <v>44</v>
       </c>
       <c r="F38" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="G38" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="H38" t="n">
-        <v>6</v>
+        <v>29</v>
       </c>
       <c r="I38" t="n">
-        <v>108</v>
+        <v>145</v>
       </c>
       <c r="J38" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K38" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L38" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M38" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O38" t="n">
-        <v>13.0231</v>
+        <v>15.7175</v>
       </c>
       <c r="P38" t="n">
-        <v>194.9576</v>
+        <v>195.2938</v>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
@@ -2725,7 +2725,7 @@
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>2026-05-24 05:37:07</t>
+          <t>2026-05-25 14:34:22</t>
         </is>
       </c>
     </row>
@@ -2734,49 +2734,49 @@
         <v>38</v>
       </c>
       <c r="B39" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C39" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D39" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E39" t="n">
-        <v>44</v>
+        <v>9</v>
       </c>
       <c r="F39" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="G39" t="n">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="H39" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="I39" t="n">
-        <v>153</v>
+        <v>108</v>
       </c>
       <c r="J39" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K39" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L39" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M39" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O39" t="n">
-        <v>14.4139</v>
+        <v>13.0231</v>
       </c>
       <c r="P39" t="n">
-        <v>194.7547</v>
+        <v>195.2576</v>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
@@ -2785,7 +2785,7 @@
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>2026-05-24 05:37:07</t>
+          <t>2026-05-25 14:34:22</t>
         </is>
       </c>
     </row>
@@ -2800,28 +2800,28 @@
         <v>3</v>
       </c>
       <c r="D40" t="n">
-        <v>5</v>
+        <v>44</v>
       </c>
       <c r="E40" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="F40" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="G40" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="H40" t="n">
-        <v>21</v>
+        <v>41</v>
       </c>
       <c r="I40" t="n">
-        <v>142</v>
+        <v>188</v>
       </c>
       <c r="J40" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K40" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L40" t="n">
         <v>4</v>
@@ -2830,13 +2830,13 @@
         <v>2</v>
       </c>
       <c r="N40" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O40" t="n">
-        <v>14.5052</v>
+        <v>15.7175</v>
       </c>
       <c r="P40" t="n">
-        <v>194.5229</v>
+        <v>195.1938</v>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
@@ -2845,7 +2845,7 @@
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>2026-05-24 05:37:07</t>
+          <t>2026-05-25 14:34:22</t>
         </is>
       </c>
     </row>
@@ -2854,13 +2854,13 @@
         <v>40</v>
       </c>
       <c r="B41" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C41" t="n">
         <v>5</v>
       </c>
       <c r="D41" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E41" t="n">
         <v>44</v>
@@ -2872,10 +2872,10 @@
         <v>49</v>
       </c>
       <c r="H41" t="n">
-        <v>6</v>
+        <v>31</v>
       </c>
       <c r="I41" t="n">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="J41" t="n">
         <v>3</v>
@@ -2884,19 +2884,19 @@
         <v>3</v>
       </c>
       <c r="L41" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M41" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O41" t="n">
-        <v>12.7216</v>
+        <v>14.4139</v>
       </c>
       <c r="P41" t="n">
-        <v>194.4441</v>
+        <v>194.9547</v>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
@@ -2905,7 +2905,7 @@
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>2026-05-24 05:37:07</t>
+          <t>2026-05-25 14:34:22</t>
         </is>
       </c>
     </row>
@@ -2917,46 +2917,46 @@
         <v>1</v>
       </c>
       <c r="C42" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D42" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E42" t="n">
+        <v>44</v>
+      </c>
+      <c r="F42" t="n">
+        <v>46</v>
+      </c>
+      <c r="G42" t="n">
+        <v>49</v>
+      </c>
+      <c r="H42" t="n">
         <v>6</v>
       </c>
-      <c r="F42" t="n">
-        <v>44</v>
-      </c>
-      <c r="G42" t="n">
-        <v>46</v>
-      </c>
-      <c r="H42" t="n">
-        <v>38</v>
-      </c>
       <c r="I42" t="n">
-        <v>105</v>
+        <v>154</v>
       </c>
       <c r="J42" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K42" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L42" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M42" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O42" t="n">
-        <v>14.5052</v>
+        <v>12.7216</v>
       </c>
       <c r="P42" t="n">
-        <v>194.1829</v>
+        <v>194.8841</v>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
@@ -2965,7 +2965,7 @@
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>2026-05-24 05:37:07</t>
+          <t>2026-05-25 14:34:22</t>
         </is>
       </c>
     </row>
@@ -2977,31 +2977,31 @@
         <v>1</v>
       </c>
       <c r="C43" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D43" t="n">
+        <v>5</v>
+      </c>
+      <c r="E43" t="n">
         <v>43</v>
       </c>
-      <c r="E43" t="n">
-        <v>44</v>
-      </c>
       <c r="F43" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="G43" t="n">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="H43" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="I43" t="n">
-        <v>188</v>
+        <v>142</v>
       </c>
       <c r="J43" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K43" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L43" t="n">
         <v>4</v>
@@ -3013,10 +3013,10 @@
         <v>1</v>
       </c>
       <c r="O43" t="n">
-        <v>14.2352</v>
+        <v>14.5052</v>
       </c>
       <c r="P43" t="n">
-        <v>193.8079</v>
+        <v>194.6229</v>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
@@ -3025,7 +3025,7 @@
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>2026-05-24 05:37:07</t>
+          <t>2026-05-25 14:34:22</t>
         </is>
       </c>
     </row>
@@ -3034,34 +3034,34 @@
         <v>43</v>
       </c>
       <c r="B44" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C44" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D44" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E44" t="n">
-        <v>44</v>
+        <v>6</v>
       </c>
       <c r="F44" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="G44" t="n">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="H44" t="n">
         <v>38</v>
       </c>
       <c r="I44" t="n">
-        <v>157</v>
+        <v>105</v>
       </c>
       <c r="J44" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K44" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L44" t="n">
         <v>3</v>
@@ -3070,13 +3070,13 @@
         <v>3</v>
       </c>
       <c r="N44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O44" t="n">
-        <v>12.4483</v>
+        <v>14.5052</v>
       </c>
       <c r="P44" t="n">
-        <v>193.1807</v>
+        <v>194.2829</v>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
@@ -3085,7 +3085,7 @@
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>2026-05-24 05:37:07</t>
+          <t>2026-05-25 14:34:22</t>
         </is>
       </c>
     </row>
@@ -3097,46 +3097,46 @@
         <v>1</v>
       </c>
       <c r="C45" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D45" t="n">
-        <v>5</v>
+        <v>43</v>
       </c>
       <c r="E45" t="n">
-        <v>10</v>
+        <v>44</v>
       </c>
       <c r="F45" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="G45" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="H45" t="n">
-        <v>29</v>
+        <v>43</v>
       </c>
       <c r="I45" t="n">
-        <v>109</v>
+        <v>188</v>
       </c>
       <c r="J45" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K45" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L45" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M45" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O45" t="n">
-        <v>12.5539</v>
+        <v>14.2352</v>
       </c>
       <c r="P45" t="n">
-        <v>192.7247</v>
+        <v>194.0079</v>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
@@ -3145,7 +3145,7 @@
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>2026-05-24 05:37:07</t>
+          <t>2026-05-25 14:34:22</t>
         </is>
       </c>
     </row>
@@ -3154,28 +3154,28 @@
         <v>45</v>
       </c>
       <c r="B46" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C46" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D46" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E46" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="F46" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="G46" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="H46" t="n">
-        <v>21</v>
+        <v>39</v>
       </c>
       <c r="I46" t="n">
-        <v>137</v>
+        <v>157</v>
       </c>
       <c r="J46" t="n">
         <v>3</v>
@@ -3193,10 +3193,10 @@
         <v>0</v>
       </c>
       <c r="O46" t="n">
-        <v>12.0996</v>
+        <v>12.4483</v>
       </c>
       <c r="P46" t="n">
-        <v>192.709</v>
+        <v>193.3807</v>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
@@ -3205,7 +3205,7 @@
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>2026-05-24 05:37:07</t>
+          <t>2026-05-25 14:34:22</t>
         </is>
       </c>
     </row>
@@ -3223,40 +3223,40 @@
         <v>5</v>
       </c>
       <c r="E47" t="n">
-        <v>12</v>
+        <v>38</v>
       </c>
       <c r="F47" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="G47" t="n">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="H47" t="n">
-        <v>2</v>
+        <v>40</v>
       </c>
       <c r="I47" t="n">
-        <v>116</v>
+        <v>137</v>
       </c>
       <c r="J47" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K47" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L47" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M47" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N47" t="n">
         <v>0</v>
       </c>
       <c r="O47" t="n">
-        <v>12.3386</v>
+        <v>12.0996</v>
       </c>
       <c r="P47" t="n">
-        <v>192.6064</v>
+        <v>193.009</v>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
@@ -3265,7 +3265,7 @@
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>2026-05-24 05:37:07</t>
+          <t>2026-05-25 14:34:22</t>
         </is>
       </c>
     </row>
@@ -3280,43 +3280,43 @@
         <v>3</v>
       </c>
       <c r="D48" t="n">
-        <v>37</v>
+        <v>5</v>
       </c>
       <c r="E48" t="n">
-        <v>44</v>
+        <v>10</v>
       </c>
       <c r="F48" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="G48" t="n">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="H48" t="n">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="I48" t="n">
-        <v>180</v>
+        <v>109</v>
       </c>
       <c r="J48" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K48" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L48" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M48" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N48" t="n">
         <v>0</v>
       </c>
       <c r="O48" t="n">
-        <v>12.3386</v>
+        <v>12.5539</v>
       </c>
       <c r="P48" t="n">
-        <v>192.3864</v>
+        <v>192.8247</v>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
@@ -3325,7 +3325,7 @@
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>2026-05-24 05:37:07</t>
+          <t>2026-05-25 14:34:22</t>
         </is>
       </c>
     </row>
@@ -3337,13 +3337,13 @@
         <v>1</v>
       </c>
       <c r="C49" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D49" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E49" t="n">
-        <v>44</v>
+        <v>12</v>
       </c>
       <c r="F49" t="n">
         <v>46</v>
@@ -3352,31 +3352,31 @@
         <v>49</v>
       </c>
       <c r="H49" t="n">
-        <v>2</v>
+        <v>31</v>
       </c>
       <c r="I49" t="n">
-        <v>155</v>
+        <v>116</v>
       </c>
       <c r="J49" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K49" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L49" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M49" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N49" t="n">
         <v>0</v>
       </c>
       <c r="O49" t="n">
-        <v>12.2409</v>
+        <v>12.3386</v>
       </c>
       <c r="P49" t="n">
-        <v>191.7423</v>
+        <v>192.8064</v>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
@@ -3385,7 +3385,7 @@
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>2026-05-24 05:37:07</t>
+          <t>2026-05-25 14:34:22</t>
         </is>
       </c>
     </row>
@@ -3400,28 +3400,28 @@
         <v>3</v>
       </c>
       <c r="D50" t="n">
-        <v>5</v>
+        <v>37</v>
       </c>
       <c r="E50" t="n">
-        <v>14</v>
+        <v>44</v>
       </c>
       <c r="F50" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="G50" t="n">
         <v>49</v>
       </c>
       <c r="H50" t="n">
-        <v>38</v>
+        <v>8</v>
       </c>
       <c r="I50" t="n">
-        <v>116</v>
+        <v>180</v>
       </c>
       <c r="J50" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K50" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L50" t="n">
         <v>4</v>
@@ -3433,10 +3433,10 @@
         <v>0</v>
       </c>
       <c r="O50" t="n">
-        <v>10.5186</v>
+        <v>12.3386</v>
       </c>
       <c r="P50" t="n">
-        <v>191.6964</v>
+        <v>192.5864</v>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
@@ -3445,7 +3445,7 @@
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>2026-05-24 05:37:07</t>
+          <t>2026-05-25 14:34:22</t>
         </is>
       </c>
     </row>
@@ -3463,40 +3463,40 @@
         <v>5</v>
       </c>
       <c r="E51" t="n">
-        <v>44</v>
+        <v>14</v>
       </c>
       <c r="F51" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="G51" t="n">
         <v>49</v>
       </c>
       <c r="H51" t="n">
-        <v>2</v>
+        <v>38</v>
       </c>
       <c r="I51" t="n">
-        <v>147</v>
+        <v>116</v>
       </c>
       <c r="J51" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K51" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L51" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M51" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O51" t="n">
-        <v>14.7323</v>
+        <v>10.5186</v>
       </c>
       <c r="P51" t="n">
-        <v>191.5707</v>
+        <v>191.7964</v>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
@@ -3505,7 +3505,7 @@
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>2026-05-24 05:37:07</t>
+          <t>2026-05-25 14:34:22</t>
         </is>
       </c>
     </row>
@@ -3523,19 +3523,19 @@
         <v>5</v>
       </c>
       <c r="E52" t="n">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="F52" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G52" t="n">
         <v>49</v>
       </c>
       <c r="H52" t="n">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="I52" t="n">
-        <v>136</v>
+        <v>147</v>
       </c>
       <c r="J52" t="n">
         <v>3</v>
@@ -3544,19 +3544,19 @@
         <v>3</v>
       </c>
       <c r="L52" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M52" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O52" t="n">
-        <v>10.1311</v>
+        <v>14.7323</v>
       </c>
       <c r="P52" t="n">
-        <v>191.3679</v>
+        <v>191.6707</v>
       </c>
       <c r="Q52" t="inlineStr">
         <is>
@@ -3565,7 +3565,7 @@
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>2026-05-24 05:37:07</t>
+          <t>2026-05-25 14:34:22</t>
         </is>
       </c>
     </row>
@@ -3583,16 +3583,16 @@
         <v>5</v>
       </c>
       <c r="E53" t="n">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="F53" t="n">
         <v>44</v>
       </c>
       <c r="G53" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="H53" t="n">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="I53" t="n">
         <v>136</v>
@@ -3613,10 +3613,10 @@
         <v>0</v>
       </c>
       <c r="O53" t="n">
-        <v>11.6619</v>
+        <v>10.1311</v>
       </c>
       <c r="P53" t="n">
-        <v>190.0548</v>
+        <v>191.4679</v>
       </c>
       <c r="Q53" t="inlineStr">
         <is>
@@ -3625,7 +3625,7 @@
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>2026-05-24 05:37:07</t>
+          <t>2026-05-25 14:34:22</t>
         </is>
       </c>
     </row>
@@ -3640,28 +3640,28 @@
         <v>3</v>
       </c>
       <c r="D54" t="n">
-        <v>31</v>
+        <v>5</v>
       </c>
       <c r="E54" t="n">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="F54" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="G54" t="n">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="H54" t="n">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="I54" t="n">
-        <v>174</v>
+        <v>136</v>
       </c>
       <c r="J54" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K54" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L54" t="n">
         <v>4</v>
@@ -3673,10 +3673,10 @@
         <v>0</v>
       </c>
       <c r="O54" t="n">
-        <v>10.0916</v>
+        <v>11.6619</v>
       </c>
       <c r="P54" t="n">
-        <v>189.249</v>
+        <v>190.1548</v>
       </c>
       <c r="Q54" t="inlineStr">
         <is>
@@ -3685,7 +3685,7 @@
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>2026-05-24 05:37:07</t>
+          <t>2026-05-25 14:34:22</t>
         </is>
       </c>
     </row>
@@ -3700,43 +3700,43 @@
         <v>3</v>
       </c>
       <c r="D55" t="n">
-        <v>5</v>
+        <v>31</v>
       </c>
       <c r="E55" t="n">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="F55" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="G55" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="H55" t="n">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="I55" t="n">
-        <v>135</v>
+        <v>174</v>
       </c>
       <c r="J55" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K55" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L55" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M55" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N55" t="n">
         <v>0</v>
       </c>
       <c r="O55" t="n">
-        <v>11.2428</v>
+        <v>10.0916</v>
       </c>
       <c r="P55" t="n">
-        <v>188.2469</v>
+        <v>189.449</v>
       </c>
       <c r="Q55" t="inlineStr">
         <is>
@@ -3745,7 +3745,7 @@
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>2026-05-24 05:37:07</t>
+          <t>2026-05-25 14:34:22</t>
         </is>
       </c>
     </row>
@@ -3763,19 +3763,19 @@
         <v>5</v>
       </c>
       <c r="E56" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="F56" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="G56" t="n">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="H56" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="I56" t="n">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="J56" t="n">
         <v>3</v>
@@ -3784,19 +3784,19 @@
         <v>3</v>
       </c>
       <c r="L56" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M56" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N56" t="n">
         <v>0</v>
       </c>
       <c r="O56" t="n">
-        <v>9.8102</v>
+        <v>11.2428</v>
       </c>
       <c r="P56" t="n">
-        <v>188.2255</v>
+        <v>188.4469</v>
       </c>
       <c r="Q56" t="inlineStr">
         <is>
@@ -3805,7 +3805,7 @@
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>2026-05-24 05:37:07</t>
+          <t>2026-05-25 14:34:22</t>
         </is>
       </c>
     </row>
@@ -3820,10 +3820,10 @@
         <v>3</v>
       </c>
       <c r="D57" t="n">
-        <v>33</v>
+        <v>5</v>
       </c>
       <c r="E57" t="n">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="F57" t="n">
         <v>46</v>
@@ -3832,16 +3832,16 @@
         <v>49</v>
       </c>
       <c r="H57" t="n">
-        <v>38</v>
+        <v>15</v>
       </c>
       <c r="I57" t="n">
-        <v>176</v>
+        <v>136</v>
       </c>
       <c r="J57" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K57" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L57" t="n">
         <v>4</v>
@@ -3853,10 +3853,10 @@
         <v>0</v>
       </c>
       <c r="O57" t="n">
-        <v>10.7443</v>
+        <v>9.8102</v>
       </c>
       <c r="P57" t="n">
-        <v>187.9808</v>
+        <v>188.4255</v>
       </c>
       <c r="Q57" t="inlineStr">
         <is>
@@ -3865,7 +3865,7 @@
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>2026-05-24 05:37:07</t>
+          <t>2026-05-25 14:34:22</t>
         </is>
       </c>
     </row>
@@ -3874,16 +3874,16 @@
         <v>57</v>
       </c>
       <c r="B58" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C58" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D58" t="n">
-        <v>44</v>
+        <v>33</v>
       </c>
       <c r="E58" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F58" t="n">
         <v>46</v>
@@ -3892,10 +3892,10 @@
         <v>49</v>
       </c>
       <c r="H58" t="n">
-        <v>6</v>
+        <v>38</v>
       </c>
       <c r="I58" t="n">
-        <v>192</v>
+        <v>176</v>
       </c>
       <c r="J58" t="n">
         <v>4</v>
@@ -3910,13 +3910,13 @@
         <v>2</v>
       </c>
       <c r="N58" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O58" t="n">
-        <v>14.9184</v>
+        <v>10.7443</v>
       </c>
       <c r="P58" t="n">
-        <v>187.1961</v>
+        <v>188.1808</v>
       </c>
       <c r="Q58" t="inlineStr">
         <is>
@@ -3925,7 +3925,7 @@
       </c>
       <c r="R58" t="inlineStr">
         <is>
-          <t>2026-05-24 05:37:07</t>
+          <t>2026-05-25 14:34:22</t>
         </is>
       </c>
     </row>
@@ -3934,16 +3934,16 @@
         <v>58</v>
       </c>
       <c r="B59" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C59" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D59" t="n">
-        <v>5</v>
+        <v>44</v>
       </c>
       <c r="E59" t="n">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="F59" t="n">
         <v>46</v>
@@ -3952,31 +3952,31 @@
         <v>49</v>
       </c>
       <c r="H59" t="n">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="I59" t="n">
-        <v>143</v>
+        <v>192</v>
       </c>
       <c r="J59" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K59" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L59" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M59" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N59" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O59" t="n">
-        <v>12.3386</v>
+        <v>14.9184</v>
       </c>
       <c r="P59" t="n">
-        <v>187.1264</v>
+        <v>187.3961</v>
       </c>
       <c r="Q59" t="inlineStr">
         <is>
@@ -3985,7 +3985,7 @@
       </c>
       <c r="R59" t="inlineStr">
         <is>
-          <t>2026-05-24 05:37:07</t>
+          <t>2026-05-25 14:34:22</t>
         </is>
       </c>
     </row>
@@ -4003,19 +4003,19 @@
         <v>5</v>
       </c>
       <c r="E60" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="F60" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="G60" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="H60" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="I60" t="n">
-        <v>134</v>
+        <v>143</v>
       </c>
       <c r="J60" t="n">
         <v>3</v>
@@ -4024,19 +4024,19 @@
         <v>3</v>
       </c>
       <c r="L60" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M60" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N60" t="n">
         <v>0</v>
       </c>
       <c r="O60" t="n">
-        <v>10.8444</v>
+        <v>12.3386</v>
       </c>
       <c r="P60" t="n">
-        <v>187.0909</v>
+        <v>187.3264</v>
       </c>
       <c r="Q60" t="inlineStr">
         <is>
@@ -4045,7 +4045,7 @@
       </c>
       <c r="R60" t="inlineStr">
         <is>
-          <t>2026-05-24 05:37:07</t>
+          <t>2026-05-25 14:34:22</t>
         </is>
       </c>
     </row>
@@ -4063,7 +4063,7 @@
         <v>5</v>
       </c>
       <c r="E61" t="n">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="F61" t="n">
         <v>44</v>
@@ -4072,31 +4072,31 @@
         <v>46</v>
       </c>
       <c r="H61" t="n">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="I61" t="n">
-        <v>123</v>
+        <v>134</v>
       </c>
       <c r="J61" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K61" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L61" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M61" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N61" t="n">
         <v>0</v>
       </c>
       <c r="O61" t="n">
-        <v>8.579000000000001</v>
+        <v>10.8444</v>
       </c>
       <c r="P61" t="n">
-        <v>185.9076</v>
+        <v>187.2909</v>
       </c>
       <c r="Q61" t="inlineStr">
         <is>
@@ -4105,7 +4105,7 @@
       </c>
       <c r="R61" t="inlineStr">
         <is>
-          <t>2026-05-24 05:37:07</t>
+          <t>2026-05-25 14:34:22</t>
         </is>
       </c>
     </row>
@@ -4120,43 +4120,43 @@
         <v>3</v>
       </c>
       <c r="D62" t="n">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="E62" t="n">
-        <v>44</v>
+        <v>24</v>
       </c>
       <c r="F62" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="G62" t="n">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="H62" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="I62" t="n">
-        <v>164</v>
+        <v>123</v>
       </c>
       <c r="J62" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K62" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L62" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M62" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N62" t="n">
         <v>0</v>
       </c>
       <c r="O62" t="n">
-        <v>9.0465</v>
+        <v>8.579000000000001</v>
       </c>
       <c r="P62" t="n">
-        <v>185.2164</v>
+        <v>186.2476</v>
       </c>
       <c r="Q62" t="inlineStr">
         <is>
@@ -4165,7 +4165,7 @@
       </c>
       <c r="R62" t="inlineStr">
         <is>
-          <t>2026-05-24 05:37:07</t>
+          <t>2026-05-25 14:34:22</t>
         </is>
       </c>
     </row>
@@ -4180,28 +4180,28 @@
         <v>3</v>
       </c>
       <c r="D63" t="n">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="E63" t="n">
-        <v>21</v>
+        <v>44</v>
       </c>
       <c r="F63" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="G63" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="H63" t="n">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="I63" t="n">
-        <v>120</v>
+        <v>164</v>
       </c>
       <c r="J63" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K63" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L63" t="n">
         <v>4</v>
@@ -4213,10 +4213,10 @@
         <v>0</v>
       </c>
       <c r="O63" t="n">
-        <v>8.8544</v>
+        <v>9.0465</v>
       </c>
       <c r="P63" t="n">
-        <v>184.4559</v>
+        <v>185.4164</v>
       </c>
       <c r="Q63" t="inlineStr">
         <is>
@@ -4225,7 +4225,7 @@
       </c>
       <c r="R63" t="inlineStr">
         <is>
-          <t>2026-05-24 05:37:07</t>
+          <t>2026-05-25 14:34:22</t>
         </is>
       </c>
     </row>
@@ -4234,49 +4234,49 @@
         <v>63</v>
       </c>
       <c r="B64" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C64" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D64" t="n">
-        <v>28</v>
+        <v>5</v>
       </c>
       <c r="E64" t="n">
-        <v>44</v>
+        <v>21</v>
       </c>
       <c r="F64" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="G64" t="n">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="H64" t="n">
-        <v>16</v>
+        <v>33</v>
       </c>
       <c r="I64" t="n">
-        <v>175</v>
+        <v>120</v>
       </c>
       <c r="J64" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K64" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L64" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M64" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N64" t="n">
         <v>0</v>
       </c>
       <c r="O64" t="n">
-        <v>8.704000000000001</v>
+        <v>8.8544</v>
       </c>
       <c r="P64" t="n">
-        <v>184.1001</v>
+        <v>184.5559</v>
       </c>
       <c r="Q64" t="inlineStr">
         <is>
@@ -4285,7 +4285,7 @@
       </c>
       <c r="R64" t="inlineStr">
         <is>
-          <t>2026-05-24 05:37:07</t>
+          <t>2026-05-25 14:34:22</t>
         </is>
       </c>
     </row>
@@ -4294,13 +4294,13 @@
         <v>64</v>
       </c>
       <c r="B65" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C65" t="n">
         <v>5</v>
       </c>
       <c r="D65" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="E65" t="n">
         <v>44</v>
@@ -4312,7 +4312,7 @@
         <v>49</v>
       </c>
       <c r="H65" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="I65" t="n">
         <v>175</v>
@@ -4333,10 +4333,10 @@
         <v>0</v>
       </c>
       <c r="O65" t="n">
-        <v>8.822699999999999</v>
+        <v>8.704000000000001</v>
       </c>
       <c r="P65" t="n">
-        <v>183.8567</v>
+        <v>184.4001</v>
       </c>
       <c r="Q65" t="inlineStr">
         <is>
@@ -4345,7 +4345,7 @@
       </c>
       <c r="R65" t="inlineStr">
         <is>
-          <t>2026-05-24 05:37:07</t>
+          <t>2026-05-25 14:34:22</t>
         </is>
       </c>
     </row>
@@ -4357,31 +4357,31 @@
         <v>1</v>
       </c>
       <c r="C66" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D66" t="n">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="E66" t="n">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="F66" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="G66" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="H66" t="n">
-        <v>49</v>
+        <v>31</v>
       </c>
       <c r="I66" t="n">
-        <v>127</v>
+        <v>175</v>
       </c>
       <c r="J66" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K66" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L66" t="n">
         <v>3</v>
@@ -4393,10 +4393,10 @@
         <v>0</v>
       </c>
       <c r="O66" t="n">
-        <v>8.8544</v>
+        <v>8.822699999999999</v>
       </c>
       <c r="P66" t="n">
-        <v>183.6359</v>
+        <v>184.0567</v>
       </c>
       <c r="Q66" t="inlineStr">
         <is>
@@ -4405,7 +4405,7 @@
       </c>
       <c r="R66" t="inlineStr">
         <is>
-          <t>2026-05-24 05:37:07</t>
+          <t>2026-05-25 14:34:22</t>
         </is>
       </c>
     </row>
@@ -4417,25 +4417,25 @@
         <v>1</v>
       </c>
       <c r="C67" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D67" t="n">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="E67" t="n">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="F67" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="G67" t="n">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="H67" t="n">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="I67" t="n">
-        <v>166</v>
+        <v>127</v>
       </c>
       <c r="J67" t="n">
         <v>3</v>
@@ -4444,19 +4444,19 @@
         <v>3</v>
       </c>
       <c r="L67" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M67" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N67" t="n">
         <v>0</v>
       </c>
       <c r="O67" t="n">
-        <v>8.4048</v>
+        <v>8.8544</v>
       </c>
       <c r="P67" t="n">
-        <v>183.2119</v>
+        <v>183.8359</v>
       </c>
       <c r="Q67" t="inlineStr">
         <is>
@@ -4465,7 +4465,7 @@
       </c>
       <c r="R67" t="inlineStr">
         <is>
-          <t>2026-05-24 05:37:07</t>
+          <t>2026-05-25 14:34:22</t>
         </is>
       </c>
     </row>
@@ -4477,25 +4477,25 @@
         <v>1</v>
       </c>
       <c r="C68" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D68" t="n">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="E68" t="n">
-        <v>27</v>
+        <v>44</v>
       </c>
       <c r="F68" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="G68" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="H68" t="n">
-        <v>25</v>
+        <v>43</v>
       </c>
       <c r="I68" t="n">
-        <v>126</v>
+        <v>166</v>
       </c>
       <c r="J68" t="n">
         <v>3</v>
@@ -4513,10 +4513,10 @@
         <v>0</v>
       </c>
       <c r="O68" t="n">
-        <v>8.7178</v>
+        <v>8.4048</v>
       </c>
       <c r="P68" t="n">
-        <v>181.5945</v>
+        <v>183.4119</v>
       </c>
       <c r="Q68" t="inlineStr">
         <is>
@@ -4525,7 +4525,7 @@
       </c>
       <c r="R68" t="inlineStr">
         <is>
-          <t>2026-05-24 05:37:07</t>
+          <t>2026-05-25 14:34:22</t>
         </is>
       </c>
     </row>
@@ -4537,31 +4537,31 @@
         <v>1</v>
       </c>
       <c r="C69" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D69" t="n">
+        <v>5</v>
+      </c>
+      <c r="E69" t="n">
+        <v>27</v>
+      </c>
+      <c r="F69" t="n">
+        <v>44</v>
+      </c>
+      <c r="G69" t="n">
+        <v>46</v>
+      </c>
+      <c r="H69" t="n">
         <v>25</v>
       </c>
-      <c r="E69" t="n">
-        <v>44</v>
-      </c>
-      <c r="F69" t="n">
-        <v>46</v>
-      </c>
-      <c r="G69" t="n">
-        <v>49</v>
-      </c>
-      <c r="H69" t="n">
-        <v>38</v>
-      </c>
       <c r="I69" t="n">
-        <v>170</v>
+        <v>126</v>
       </c>
       <c r="J69" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K69" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L69" t="n">
         <v>4</v>
@@ -4573,10 +4573,10 @@
         <v>0</v>
       </c>
       <c r="O69" t="n">
-        <v>8.1142</v>
+        <v>8.7178</v>
       </c>
       <c r="P69" t="n">
-        <v>181.2455</v>
+        <v>181.6945</v>
       </c>
       <c r="Q69" t="inlineStr">
         <is>
@@ -4585,7 +4585,7 @@
       </c>
       <c r="R69" t="inlineStr">
         <is>
-          <t>2026-05-24 05:37:07</t>
+          <t>2026-05-25 14:34:22</t>
         </is>
       </c>
     </row>
@@ -4597,13 +4597,13 @@
         <v>1</v>
       </c>
       <c r="C70" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D70" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="E70" t="n">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="F70" t="n">
         <v>46</v>
@@ -4612,31 +4612,31 @@
         <v>49</v>
       </c>
       <c r="H70" t="n">
-        <v>19</v>
+        <v>39</v>
       </c>
       <c r="I70" t="n">
-        <v>135</v>
+        <v>170</v>
       </c>
       <c r="J70" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K70" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L70" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M70" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N70" t="n">
         <v>0</v>
       </c>
       <c r="O70" t="n">
-        <v>9.5624</v>
+        <v>8.1142</v>
       </c>
       <c r="P70" t="n">
-        <v>181.2261</v>
+        <v>181.4455</v>
       </c>
       <c r="Q70" t="inlineStr">
         <is>
@@ -4645,7 +4645,7 @@
       </c>
       <c r="R70" t="inlineStr">
         <is>
-          <t>2026-05-24 05:37:07</t>
+          <t>2026-05-25 14:34:22</t>
         </is>
       </c>
     </row>
@@ -4657,13 +4657,13 @@
         <v>1</v>
       </c>
       <c r="C71" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D71" t="n">
-        <v>27</v>
+        <v>5</v>
       </c>
       <c r="E71" t="n">
-        <v>44</v>
+        <v>31</v>
       </c>
       <c r="F71" t="n">
         <v>46</v>
@@ -4672,31 +4672,31 @@
         <v>49</v>
       </c>
       <c r="H71" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="I71" t="n">
-        <v>172</v>
+        <v>135</v>
       </c>
       <c r="J71" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K71" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L71" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M71" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N71" t="n">
         <v>0</v>
       </c>
       <c r="O71" t="n">
-        <v>8.2608</v>
+        <v>9.5624</v>
       </c>
       <c r="P71" t="n">
-        <v>180.1719</v>
+        <v>181.4261</v>
       </c>
       <c r="Q71" t="inlineStr">
         <is>
@@ -4705,7 +4705,7 @@
       </c>
       <c r="R71" t="inlineStr">
         <is>
-          <t>2026-05-24 05:37:07</t>
+          <t>2026-05-25 14:34:22</t>
         </is>
       </c>
     </row>
@@ -4717,55 +4717,115 @@
         <v>1</v>
       </c>
       <c r="C72" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D72" t="n">
-        <v>5</v>
+        <v>27</v>
       </c>
       <c r="E72" t="n">
+        <v>44</v>
+      </c>
+      <c r="F72" t="n">
+        <v>46</v>
+      </c>
+      <c r="G72" t="n">
+        <v>49</v>
+      </c>
+      <c r="H72" t="n">
+        <v>24</v>
+      </c>
+      <c r="I72" t="n">
+        <v>172</v>
+      </c>
+      <c r="J72" t="n">
+        <v>4</v>
+      </c>
+      <c r="K72" t="n">
+        <v>2</v>
+      </c>
+      <c r="L72" t="n">
+        <v>4</v>
+      </c>
+      <c r="M72" t="n">
+        <v>2</v>
+      </c>
+      <c r="N72" t="n">
+        <v>0</v>
+      </c>
+      <c r="O72" t="n">
+        <v>8.2608</v>
+      </c>
+      <c r="P72" t="n">
+        <v>180.3719</v>
+      </c>
+      <c r="Q72" t="inlineStr">
+        <is>
+          <t>UK49sGeneticOptimizer_v1</t>
+        </is>
+      </c>
+      <c r="R72" t="inlineStr">
+        <is>
+          <t>2026-05-25 14:34:22</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>72</v>
+      </c>
+      <c r="B73" t="n">
+        <v>1</v>
+      </c>
+      <c r="C73" t="n">
+        <v>3</v>
+      </c>
+      <c r="D73" t="n">
+        <v>5</v>
+      </c>
+      <c r="E73" t="n">
         <v>23</v>
       </c>
-      <c r="F72" t="n">
-        <v>46</v>
-      </c>
-      <c r="G72" t="n">
-        <v>49</v>
-      </c>
-      <c r="H72" t="n">
-        <v>6</v>
-      </c>
-      <c r="I72" t="n">
+      <c r="F73" t="n">
+        <v>46</v>
+      </c>
+      <c r="G73" t="n">
+        <v>49</v>
+      </c>
+      <c r="H73" t="n">
+        <v>8</v>
+      </c>
+      <c r="I73" t="n">
         <v>127</v>
       </c>
-      <c r="J72" t="n">
-        <v>2</v>
-      </c>
-      <c r="K72" t="n">
-        <v>4</v>
-      </c>
-      <c r="L72" t="n">
-        <v>5</v>
-      </c>
-      <c r="M72" t="n">
-        <v>1</v>
-      </c>
-      <c r="N72" t="n">
-        <v>0</v>
-      </c>
-      <c r="O72" t="n">
+      <c r="J73" t="n">
+        <v>2</v>
+      </c>
+      <c r="K73" t="n">
+        <v>4</v>
+      </c>
+      <c r="L73" t="n">
+        <v>5</v>
+      </c>
+      <c r="M73" t="n">
+        <v>1</v>
+      </c>
+      <c r="N73" t="n">
+        <v>0</v>
+      </c>
+      <c r="O73" t="n">
         <v>9.0465</v>
       </c>
-      <c r="P72" t="n">
-        <v>177.8364</v>
-      </c>
-      <c r="Q72" t="inlineStr">
-        <is>
-          <t>UK49sGeneticOptimizer_v1</t>
-        </is>
-      </c>
-      <c r="R72" t="inlineStr">
-        <is>
-          <t>2026-05-24 05:37:07</t>
+      <c r="P73" t="n">
+        <v>178.0364</v>
+      </c>
+      <c r="Q73" t="inlineStr">
+        <is>
+          <t>UK49sGeneticOptimizer_v1</t>
+        </is>
+      </c>
+      <c r="R73" t="inlineStr">
+        <is>
+          <t>2026-05-25 14:34:22</t>
         </is>
       </c>
     </row>
@@ -4805,10 +4865,10 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>185.3164</v>
+        <v>185.5164</v>
       </c>
       <c r="C2" t="n">
-        <v>163.2829</v>
+        <v>163.5212</v>
       </c>
     </row>
     <row r="3">
@@ -4816,10 +4876,10 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>187.2822</v>
+        <v>190.438</v>
       </c>
       <c r="C3" t="n">
-        <v>170.9248</v>
+        <v>172.0636</v>
       </c>
     </row>
     <row r="4">
@@ -4827,10 +4887,10 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>195.4234</v>
+        <v>193.5394</v>
       </c>
       <c r="C4" t="n">
-        <v>176.4241</v>
+        <v>177.6398</v>
       </c>
     </row>
     <row r="5">
@@ -4838,10 +4898,10 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>196.7507</v>
+        <v>197.5781</v>
       </c>
       <c r="C5" t="n">
-        <v>182.0025</v>
+        <v>182.3188</v>
       </c>
     </row>
     <row r="6">
@@ -4849,10 +4909,10 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>199.873</v>
+        <v>199.2828</v>
       </c>
       <c r="C6" t="n">
-        <v>183.6741</v>
+        <v>185.6147</v>
       </c>
     </row>
     <row r="7">
@@ -4860,10 +4920,10 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>199.873</v>
+        <v>199.2828</v>
       </c>
       <c r="C7" t="n">
-        <v>187.6531</v>
+        <v>188.2036</v>
       </c>
     </row>
     <row r="8">
@@ -4871,10 +4931,10 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>200.8628</v>
+        <v>199.973</v>
       </c>
       <c r="C8" t="n">
-        <v>190.4475</v>
+        <v>191.17</v>
       </c>
     </row>
     <row r="9">
@@ -4882,10 +4942,10 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>200.8628</v>
+        <v>199.973</v>
       </c>
       <c r="C9" t="n">
-        <v>191.6657</v>
+        <v>193.5536</v>
       </c>
     </row>
     <row r="10">
@@ -4893,10 +4953,10 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>200.8628</v>
+        <v>199.973</v>
       </c>
       <c r="C10" t="n">
-        <v>194.8026</v>
+        <v>193.2323</v>
       </c>
     </row>
     <row r="11">
@@ -4904,10 +4964,10 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>200.8628</v>
+        <v>199.973</v>
       </c>
       <c r="C11" t="n">
-        <v>197.5956</v>
+        <v>194.9455</v>
       </c>
     </row>
     <row r="12">
@@ -4915,10 +4975,10 @@
         <v>11</v>
       </c>
       <c r="B12" t="n">
-        <v>200.8628</v>
+        <v>199.973</v>
       </c>
       <c r="C12" t="n">
-        <v>198.0932</v>
+        <v>197.8841</v>
       </c>
     </row>
     <row r="13">
@@ -4926,10 +4986,10 @@
         <v>12</v>
       </c>
       <c r="B13" t="n">
-        <v>200.8628</v>
+        <v>199.973</v>
       </c>
       <c r="C13" t="n">
-        <v>198.8608</v>
+        <v>198.0144</v>
       </c>
     </row>
     <row r="14">
@@ -4937,10 +4997,10 @@
         <v>13</v>
       </c>
       <c r="B14" t="n">
-        <v>200.8628</v>
+        <v>199.973</v>
       </c>
       <c r="C14" t="n">
-        <v>198.4005</v>
+        <v>197.8478</v>
       </c>
     </row>
     <row r="15">
@@ -4948,10 +5008,10 @@
         <v>14</v>
       </c>
       <c r="B15" t="n">
-        <v>200.8628</v>
+        <v>199.973</v>
       </c>
       <c r="C15" t="n">
-        <v>199.2691</v>
+        <v>198.3778</v>
       </c>
     </row>
     <row r="16">
@@ -4959,10 +5019,10 @@
         <v>15</v>
       </c>
       <c r="B16" t="n">
-        <v>200.8628</v>
+        <v>201.0628</v>
       </c>
       <c r="C16" t="n">
-        <v>198.9758</v>
+        <v>198.2511</v>
       </c>
     </row>
     <row r="17">
@@ -4970,10 +5030,10 @@
         <v>16</v>
       </c>
       <c r="B17" t="n">
-        <v>200.8628</v>
+        <v>201.0628</v>
       </c>
       <c r="C17" t="n">
-        <v>199.2431</v>
+        <v>198.3533</v>
       </c>
     </row>
     <row r="18">
@@ -4981,10 +5041,10 @@
         <v>17</v>
       </c>
       <c r="B18" t="n">
-        <v>200.8628</v>
+        <v>201.0628</v>
       </c>
       <c r="C18" t="n">
-        <v>199.2249</v>
+        <v>198.1387</v>
       </c>
     </row>
     <row r="19">
@@ -4992,10 +5052,10 @@
         <v>18</v>
       </c>
       <c r="B19" t="n">
-        <v>200.8628</v>
+        <v>201.0628</v>
       </c>
       <c r="C19" t="n">
-        <v>198.8481</v>
+        <v>197.9426</v>
       </c>
     </row>
     <row r="20">
@@ -5003,10 +5063,10 @@
         <v>19</v>
       </c>
       <c r="B20" t="n">
-        <v>200.8628</v>
+        <v>201.0628</v>
       </c>
       <c r="C20" t="n">
-        <v>198.5775</v>
+        <v>198.9629</v>
       </c>
     </row>
     <row r="21">
@@ -5014,10 +5074,10 @@
         <v>20</v>
       </c>
       <c r="B21" t="n">
-        <v>200.8628</v>
+        <v>201.0628</v>
       </c>
       <c r="C21" t="n">
-        <v>199.1525</v>
+        <v>199.3537</v>
       </c>
     </row>
     <row r="22">
@@ -5025,10 +5085,10 @@
         <v>21</v>
       </c>
       <c r="B22" t="n">
-        <v>200.8628</v>
+        <v>201.0628</v>
       </c>
       <c r="C22" t="n">
-        <v>199.5745</v>
+        <v>199.7184</v>
       </c>
     </row>
     <row r="23">
@@ -5036,10 +5096,10 @@
         <v>22</v>
       </c>
       <c r="B23" t="n">
-        <v>200.8628</v>
+        <v>201.0628</v>
       </c>
       <c r="C23" t="n">
-        <v>199.0941</v>
+        <v>199.283</v>
       </c>
     </row>
     <row r="24">
@@ -5047,10 +5107,10 @@
         <v>23</v>
       </c>
       <c r="B24" t="n">
-        <v>200.8628</v>
+        <v>201.0628</v>
       </c>
       <c r="C24" t="n">
-        <v>199.0645</v>
+        <v>199.3334</v>
       </c>
     </row>
     <row r="25">
@@ -5058,10 +5118,10 @@
         <v>24</v>
       </c>
       <c r="B25" t="n">
-        <v>200.8628</v>
+        <v>201.0628</v>
       </c>
       <c r="C25" t="n">
-        <v>199.2743</v>
+        <v>199.4764</v>
       </c>
     </row>
     <row r="26">
@@ -5069,10 +5129,10 @@
         <v>25</v>
       </c>
       <c r="B26" t="n">
-        <v>200.8628</v>
+        <v>201.0628</v>
       </c>
       <c r="C26" t="n">
-        <v>199.1917</v>
+        <v>199.3789</v>
       </c>
     </row>
     <row r="27">
@@ -5080,10 +5140,10 @@
         <v>26</v>
       </c>
       <c r="B27" t="n">
-        <v>200.8628</v>
+        <v>201.0628</v>
       </c>
       <c r="C27" t="n">
-        <v>198.9672</v>
+        <v>199.0857</v>
       </c>
     </row>
     <row r="28">
@@ -5091,10 +5151,10 @@
         <v>27</v>
       </c>
       <c r="B28" t="n">
-        <v>200.8628</v>
+        <v>201.0628</v>
       </c>
       <c r="C28" t="n">
-        <v>198.9732</v>
+        <v>199.2707</v>
       </c>
     </row>
     <row r="29">
@@ -5102,10 +5162,10 @@
         <v>28</v>
       </c>
       <c r="B29" t="n">
-        <v>200.8628</v>
+        <v>201.0628</v>
       </c>
       <c r="C29" t="n">
-        <v>199.3355</v>
+        <v>199.5397</v>
       </c>
     </row>
     <row r="30">
@@ -5113,10 +5173,10 @@
         <v>29</v>
       </c>
       <c r="B30" t="n">
-        <v>200.8628</v>
+        <v>201.0628</v>
       </c>
       <c r="C30" t="n">
-        <v>199.4118</v>
+        <v>199.6156</v>
       </c>
     </row>
     <row r="31">
@@ -5124,10 +5184,10 @@
         <v>30</v>
       </c>
       <c r="B31" t="n">
-        <v>200.8628</v>
+        <v>201.0628</v>
       </c>
       <c r="C31" t="n">
-        <v>198.7681</v>
+        <v>198.9083</v>
       </c>
     </row>
     <row r="32">
@@ -5135,10 +5195,10 @@
         <v>31</v>
       </c>
       <c r="B32" t="n">
-        <v>200.8628</v>
+        <v>201.0628</v>
       </c>
       <c r="C32" t="n">
-        <v>199.194</v>
+        <v>199.4584</v>
       </c>
     </row>
     <row r="33">
@@ -5146,10 +5206,10 @@
         <v>32</v>
       </c>
       <c r="B33" t="n">
-        <v>200.8628</v>
+        <v>201.0628</v>
       </c>
       <c r="C33" t="n">
-        <v>198.9555</v>
+        <v>199.1568</v>
       </c>
     </row>
     <row r="34">
@@ -5157,10 +5217,10 @@
         <v>33</v>
       </c>
       <c r="B34" t="n">
-        <v>200.8628</v>
+        <v>201.0628</v>
       </c>
       <c r="C34" t="n">
-        <v>198.5969</v>
+        <v>198.7564</v>
       </c>
     </row>
     <row r="35">
@@ -5168,10 +5228,10 @@
         <v>34</v>
       </c>
       <c r="B35" t="n">
-        <v>200.8628</v>
+        <v>201.0628</v>
       </c>
       <c r="C35" t="n">
-        <v>199.3215</v>
+        <v>199.5506</v>
       </c>
     </row>
     <row r="36">
@@ -5179,10 +5239,10 @@
         <v>35</v>
       </c>
       <c r="B36" t="n">
-        <v>200.8628</v>
+        <v>201.0628</v>
       </c>
       <c r="C36" t="n">
-        <v>198.6748</v>
+        <v>198.7809</v>
       </c>
     </row>
     <row r="37">
@@ -5190,10 +5250,10 @@
         <v>36</v>
       </c>
       <c r="B37" t="n">
-        <v>200.8628</v>
+        <v>201.0628</v>
       </c>
       <c r="C37" t="n">
-        <v>198.5806</v>
+        <v>198.8873</v>
       </c>
     </row>
     <row r="38">
@@ -5201,10 +5261,10 @@
         <v>37</v>
       </c>
       <c r="B38" t="n">
-        <v>200.8628</v>
+        <v>201.0628</v>
       </c>
       <c r="C38" t="n">
-        <v>199.1297</v>
+        <v>199.2874</v>
       </c>
     </row>
     <row r="39">
@@ -5212,10 +5272,10 @@
         <v>38</v>
       </c>
       <c r="B39" t="n">
-        <v>200.8628</v>
+        <v>201.0628</v>
       </c>
       <c r="C39" t="n">
-        <v>198.9588</v>
+        <v>199.117</v>
       </c>
     </row>
     <row r="40">
@@ -5223,10 +5283,10 @@
         <v>39</v>
       </c>
       <c r="B40" t="n">
-        <v>200.8628</v>
+        <v>201.0628</v>
       </c>
       <c r="C40" t="n">
-        <v>198.8646</v>
+        <v>199.1313</v>
       </c>
     </row>
     <row r="41">
@@ -5234,10 +5294,10 @@
         <v>40</v>
       </c>
       <c r="B41" t="n">
-        <v>200.8628</v>
+        <v>201.0628</v>
       </c>
       <c r="C41" t="n">
-        <v>199.4256</v>
+        <v>199.6223</v>
       </c>
     </row>
     <row r="42">
@@ -5245,10 +5305,10 @@
         <v>41</v>
       </c>
       <c r="B42" t="n">
-        <v>200.8628</v>
+        <v>201.0628</v>
       </c>
       <c r="C42" t="n">
-        <v>198.4707</v>
+        <v>198.7013</v>
       </c>
     </row>
     <row r="43">
@@ -5256,10 +5316,10 @@
         <v>42</v>
       </c>
       <c r="B43" t="n">
-        <v>200.8628</v>
+        <v>201.0628</v>
       </c>
       <c r="C43" t="n">
-        <v>199.0786</v>
+        <v>199.2782</v>
       </c>
     </row>
     <row r="44">
@@ -5267,10 +5327,10 @@
         <v>43</v>
       </c>
       <c r="B44" t="n">
-        <v>200.8628</v>
+        <v>201.0628</v>
       </c>
       <c r="C44" t="n">
-        <v>199.467</v>
+        <v>199.6678</v>
       </c>
     </row>
     <row r="45">
@@ -5278,10 +5338,10 @@
         <v>44</v>
       </c>
       <c r="B45" t="n">
-        <v>200.8628</v>
+        <v>201.0628</v>
       </c>
       <c r="C45" t="n">
-        <v>199.6442</v>
+        <v>199.7717</v>
       </c>
     </row>
     <row r="46">
@@ -5289,10 +5349,10 @@
         <v>45</v>
       </c>
       <c r="B46" t="n">
-        <v>200.8628</v>
+        <v>201.0628</v>
       </c>
       <c r="C46" t="n">
-        <v>199.2963</v>
+        <v>199.5718</v>
       </c>
     </row>
     <row r="47">
@@ -5300,10 +5360,10 @@
         <v>46</v>
       </c>
       <c r="B47" t="n">
-        <v>200.8628</v>
+        <v>201.0628</v>
       </c>
       <c r="C47" t="n">
-        <v>198.914</v>
+        <v>199.0637</v>
       </c>
     </row>
     <row r="48">
@@ -5311,10 +5371,10 @@
         <v>47</v>
       </c>
       <c r="B48" t="n">
-        <v>200.8628</v>
+        <v>201.0628</v>
       </c>
       <c r="C48" t="n">
-        <v>198.8055</v>
+        <v>199.0506</v>
       </c>
     </row>
     <row r="49">
@@ -5322,10 +5382,10 @@
         <v>48</v>
       </c>
       <c r="B49" t="n">
-        <v>200.8628</v>
+        <v>201.0628</v>
       </c>
       <c r="C49" t="n">
-        <v>198.6878</v>
+        <v>198.8556</v>
       </c>
     </row>
     <row r="50">
@@ -5333,10 +5393,10 @@
         <v>49</v>
       </c>
       <c r="B50" t="n">
-        <v>200.8628</v>
+        <v>201.0628</v>
       </c>
       <c r="C50" t="n">
-        <v>198.4252</v>
+        <v>198.6801</v>
       </c>
     </row>
     <row r="51">
@@ -5344,10 +5404,10 @@
         <v>50</v>
       </c>
       <c r="B51" t="n">
-        <v>200.8628</v>
+        <v>201.0628</v>
       </c>
       <c r="C51" t="n">
-        <v>199.2495</v>
+        <v>199.4379</v>
       </c>
     </row>
     <row r="52">
@@ -5355,10 +5415,10 @@
         <v>51</v>
       </c>
       <c r="B52" t="n">
-        <v>200.8628</v>
+        <v>201.0628</v>
       </c>
       <c r="C52" t="n">
-        <v>199.537</v>
+        <v>199.7527</v>
       </c>
     </row>
     <row r="53">
@@ -5366,10 +5426,10 @@
         <v>52</v>
       </c>
       <c r="B53" t="n">
-        <v>200.8628</v>
+        <v>201.0628</v>
       </c>
       <c r="C53" t="n">
-        <v>199.2424</v>
+        <v>199.4437</v>
       </c>
     </row>
     <row r="54">
@@ -5377,10 +5437,10 @@
         <v>53</v>
       </c>
       <c r="B54" t="n">
-        <v>200.8628</v>
+        <v>201.0628</v>
       </c>
       <c r="C54" t="n">
-        <v>198.7908</v>
+        <v>198.9938</v>
       </c>
     </row>
     <row r="55">
@@ -5388,10 +5448,10 @@
         <v>54</v>
       </c>
       <c r="B55" t="n">
-        <v>200.8628</v>
+        <v>201.0628</v>
       </c>
       <c r="C55" t="n">
-        <v>198.9297</v>
+        <v>199.1345</v>
       </c>
     </row>
     <row r="56">
@@ -5399,10 +5459,10 @@
         <v>55</v>
       </c>
       <c r="B56" t="n">
-        <v>200.8628</v>
+        <v>201.0628</v>
       </c>
       <c r="C56" t="n">
-        <v>199.1739</v>
+        <v>199.3785</v>
       </c>
     </row>
     <row r="57">
@@ -5410,10 +5470,10 @@
         <v>56</v>
       </c>
       <c r="B57" t="n">
-        <v>200.8628</v>
+        <v>201.0628</v>
       </c>
       <c r="C57" t="n">
-        <v>199.4678</v>
+        <v>199.6699</v>
       </c>
     </row>
     <row r="58">
@@ -5421,10 +5481,10 @@
         <v>57</v>
       </c>
       <c r="B58" t="n">
-        <v>200.8628</v>
+        <v>201.0628</v>
       </c>
       <c r="C58" t="n">
-        <v>198.81</v>
+        <v>199.0154</v>
       </c>
     </row>
     <row r="59">
@@ -5432,10 +5492,10 @@
         <v>58</v>
       </c>
       <c r="B59" t="n">
-        <v>200.8628</v>
+        <v>201.0628</v>
       </c>
       <c r="C59" t="n">
-        <v>198.9308</v>
+        <v>199.1356</v>
       </c>
     </row>
     <row r="60">
@@ -5443,10 +5503,10 @@
         <v>59</v>
       </c>
       <c r="B60" t="n">
-        <v>200.8628</v>
+        <v>201.0628</v>
       </c>
       <c r="C60" t="n">
-        <v>198.4026</v>
+        <v>198.4903</v>
       </c>
     </row>
     <row r="61">
@@ -5454,10 +5514,10 @@
         <v>60</v>
       </c>
       <c r="B61" t="n">
-        <v>200.8628</v>
+        <v>201.0628</v>
       </c>
       <c r="C61" t="n">
-        <v>199.0792</v>
+        <v>199.362</v>
       </c>
     </row>
   </sheetData>

--- a/data/exports/optimization/uk49s_genetic_optimizer_results.xlsx
+++ b/data/exports/optimization/uk49s_genetic_optimizer_results.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R73"/>
+  <dimension ref="A1:R71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -532,7 +532,7 @@
         <v>49</v>
       </c>
       <c r="H2" t="n">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="I2" t="n">
         <v>148</v>
@@ -556,7 +556,7 @@
         <v>14.7051</v>
       </c>
       <c r="P2" t="n">
-        <v>201.0628</v>
+        <v>201.1628</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -565,7 +565,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:22</t>
+          <t>2026-05-26 14:23:40</t>
         </is>
       </c>
     </row>
@@ -592,7 +592,7 @@
         <v>49</v>
       </c>
       <c r="H3" t="n">
-        <v>38</v>
+        <v>15</v>
       </c>
       <c r="I3" t="n">
         <v>148</v>
@@ -616,7 +616,7 @@
         <v>14.7051</v>
       </c>
       <c r="P3" t="n">
-        <v>201.0628</v>
+        <v>201.1628</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -625,7 +625,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:22</t>
+          <t>2026-05-26 14:23:40</t>
         </is>
       </c>
     </row>
@@ -652,7 +652,7 @@
         <v>49</v>
       </c>
       <c r="H4" t="n">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="I4" t="n">
         <v>148</v>
@@ -676,7 +676,7 @@
         <v>14.7051</v>
       </c>
       <c r="P4" t="n">
-        <v>201.0628</v>
+        <v>201.1628</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -685,7 +685,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:22</t>
+          <t>2026-05-26 14:23:40</t>
         </is>
       </c>
     </row>
@@ -712,7 +712,7 @@
         <v>49</v>
       </c>
       <c r="H5" t="n">
-        <v>41</v>
+        <v>9</v>
       </c>
       <c r="I5" t="n">
         <v>148</v>
@@ -736,7 +736,7 @@
         <v>14.7051</v>
       </c>
       <c r="P5" t="n">
-        <v>201.0628</v>
+        <v>201.1628</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -745,7 +745,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:22</t>
+          <t>2026-05-26 14:23:40</t>
         </is>
       </c>
     </row>
@@ -772,7 +772,7 @@
         <v>49</v>
       </c>
       <c r="H6" t="n">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="I6" t="n">
         <v>148</v>
@@ -796,7 +796,7 @@
         <v>14.7051</v>
       </c>
       <c r="P6" t="n">
-        <v>201.0628</v>
+        <v>201.1628</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -805,7 +805,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:22</t>
+          <t>2026-05-26 14:23:40</t>
         </is>
       </c>
     </row>
@@ -832,7 +832,7 @@
         <v>49</v>
       </c>
       <c r="H7" t="n">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="I7" t="n">
         <v>148</v>
@@ -856,7 +856,7 @@
         <v>14.7051</v>
       </c>
       <c r="P7" t="n">
-        <v>201.0628</v>
+        <v>201.1628</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
@@ -865,7 +865,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:22</t>
+          <t>2026-05-26 14:23:40</t>
         </is>
       </c>
     </row>
@@ -892,7 +892,7 @@
         <v>49</v>
       </c>
       <c r="H8" t="n">
-        <v>43</v>
+        <v>24</v>
       </c>
       <c r="I8" t="n">
         <v>148</v>
@@ -916,7 +916,7 @@
         <v>14.7051</v>
       </c>
       <c r="P8" t="n">
-        <v>201.0628</v>
+        <v>201.1628</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:22</t>
+          <t>2026-05-26 14:23:40</t>
         </is>
       </c>
     </row>
@@ -952,7 +952,7 @@
         <v>49</v>
       </c>
       <c r="H9" t="n">
-        <v>8</v>
+        <v>39</v>
       </c>
       <c r="I9" t="n">
         <v>148</v>
@@ -976,7 +976,7 @@
         <v>14.7051</v>
       </c>
       <c r="P9" t="n">
-        <v>201.0628</v>
+        <v>201.1628</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
@@ -985,7 +985,7 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:22</t>
+          <t>2026-05-26 14:23:40</t>
         </is>
       </c>
     </row>
@@ -1012,7 +1012,7 @@
         <v>49</v>
       </c>
       <c r="H10" t="n">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="I10" t="n">
         <v>148</v>
@@ -1036,7 +1036,7 @@
         <v>14.7051</v>
       </c>
       <c r="P10" t="n">
-        <v>201.0628</v>
+        <v>201.1628</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
@@ -1045,7 +1045,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:22</t>
+          <t>2026-05-26 14:23:40</t>
         </is>
       </c>
     </row>
@@ -1072,7 +1072,7 @@
         <v>49</v>
       </c>
       <c r="H11" t="n">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="I11" t="n">
         <v>148</v>
@@ -1096,7 +1096,7 @@
         <v>14.7051</v>
       </c>
       <c r="P11" t="n">
-        <v>201.0628</v>
+        <v>201.1628</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
@@ -1105,7 +1105,7 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:22</t>
+          <t>2026-05-26 14:23:40</t>
         </is>
       </c>
     </row>
@@ -1132,7 +1132,7 @@
         <v>49</v>
       </c>
       <c r="H12" t="n">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="I12" t="n">
         <v>148</v>
@@ -1156,7 +1156,7 @@
         <v>14.7051</v>
       </c>
       <c r="P12" t="n">
-        <v>201.0628</v>
+        <v>201.1628</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
@@ -1165,7 +1165,7 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:22</t>
+          <t>2026-05-26 14:23:40</t>
         </is>
       </c>
     </row>
@@ -1192,7 +1192,7 @@
         <v>49</v>
       </c>
       <c r="H13" t="n">
-        <v>39</v>
+        <v>16</v>
       </c>
       <c r="I13" t="n">
         <v>148</v>
@@ -1216,7 +1216,7 @@
         <v>14.7051</v>
       </c>
       <c r="P13" t="n">
-        <v>201.0628</v>
+        <v>201.1628</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
@@ -1225,7 +1225,7 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:22</t>
+          <t>2026-05-26 14:23:40</t>
         </is>
       </c>
     </row>
@@ -1252,7 +1252,7 @@
         <v>49</v>
       </c>
       <c r="H14" t="n">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="I14" t="n">
         <v>148</v>
@@ -1276,7 +1276,7 @@
         <v>14.7051</v>
       </c>
       <c r="P14" t="n">
-        <v>201.0628</v>
+        <v>201.1628</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
@@ -1285,7 +1285,7 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:22</t>
+          <t>2026-05-26 14:23:40</t>
         </is>
       </c>
     </row>
@@ -1312,7 +1312,7 @@
         <v>49</v>
       </c>
       <c r="H15" t="n">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="I15" t="n">
         <v>148</v>
@@ -1336,7 +1336,7 @@
         <v>14.7051</v>
       </c>
       <c r="P15" t="n">
-        <v>201.0628</v>
+        <v>201.1628</v>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
@@ -1345,7 +1345,7 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:22</t>
+          <t>2026-05-26 14:23:40</t>
         </is>
       </c>
     </row>
@@ -1372,7 +1372,7 @@
         <v>49</v>
       </c>
       <c r="H16" t="n">
-        <v>33</v>
+        <v>11</v>
       </c>
       <c r="I16" t="n">
         <v>148</v>
@@ -1396,7 +1396,7 @@
         <v>14.7051</v>
       </c>
       <c r="P16" t="n">
-        <v>201.0628</v>
+        <v>201.1628</v>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
@@ -1405,7 +1405,7 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:22</t>
+          <t>2026-05-26 14:23:40</t>
         </is>
       </c>
     </row>
@@ -1432,7 +1432,7 @@
         <v>49</v>
       </c>
       <c r="H17" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="I17" t="n">
         <v>148</v>
@@ -1456,7 +1456,7 @@
         <v>14.7051</v>
       </c>
       <c r="P17" t="n">
-        <v>201.0628</v>
+        <v>201.1628</v>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
@@ -1465,7 +1465,7 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:22</t>
+          <t>2026-05-26 14:23:40</t>
         </is>
       </c>
     </row>
@@ -1492,7 +1492,7 @@
         <v>49</v>
       </c>
       <c r="H18" t="n">
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="I18" t="n">
         <v>148</v>
@@ -1516,7 +1516,7 @@
         <v>14.7051</v>
       </c>
       <c r="P18" t="n">
-        <v>201.0628</v>
+        <v>201.1628</v>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
@@ -1525,7 +1525,7 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:22</t>
+          <t>2026-05-26 14:23:40</t>
         </is>
       </c>
     </row>
@@ -1552,7 +1552,7 @@
         <v>49</v>
       </c>
       <c r="H19" t="n">
-        <v>48</v>
+        <v>33</v>
       </c>
       <c r="I19" t="n">
         <v>148</v>
@@ -1576,7 +1576,7 @@
         <v>14.7051</v>
       </c>
       <c r="P19" t="n">
-        <v>201.0628</v>
+        <v>201.1628</v>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
@@ -1585,7 +1585,7 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:22</t>
+          <t>2026-05-26 14:23:40</t>
         </is>
       </c>
     </row>
@@ -1612,7 +1612,7 @@
         <v>49</v>
       </c>
       <c r="H20" t="n">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="I20" t="n">
         <v>148</v>
@@ -1636,7 +1636,7 @@
         <v>14.7051</v>
       </c>
       <c r="P20" t="n">
-        <v>201.0628</v>
+        <v>201.1628</v>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
@@ -1645,7 +1645,7 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:22</t>
+          <t>2026-05-26 14:23:40</t>
         </is>
       </c>
     </row>
@@ -1672,7 +1672,7 @@
         <v>49</v>
       </c>
       <c r="H21" t="n">
-        <v>7</v>
+        <v>31</v>
       </c>
       <c r="I21" t="n">
         <v>148</v>
@@ -1696,7 +1696,7 @@
         <v>14.7051</v>
       </c>
       <c r="P21" t="n">
-        <v>201.0628</v>
+        <v>201.1628</v>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
@@ -1705,7 +1705,7 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:22</t>
+          <t>2026-05-26 14:23:40</t>
         </is>
       </c>
     </row>
@@ -1732,7 +1732,7 @@
         <v>49</v>
       </c>
       <c r="H22" t="n">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="I22" t="n">
         <v>148</v>
@@ -1756,7 +1756,7 @@
         <v>14.7051</v>
       </c>
       <c r="P22" t="n">
-        <v>201.0628</v>
+        <v>201.1628</v>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
@@ -1765,7 +1765,7 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:22</t>
+          <t>2026-05-26 14:23:40</t>
         </is>
       </c>
     </row>
@@ -1792,7 +1792,7 @@
         <v>49</v>
       </c>
       <c r="H23" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I23" t="n">
         <v>148</v>
@@ -1816,7 +1816,7 @@
         <v>14.7051</v>
       </c>
       <c r="P23" t="n">
-        <v>201.0628</v>
+        <v>201.1628</v>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
@@ -1825,7 +1825,7 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:22</t>
+          <t>2026-05-26 14:23:40</t>
         </is>
       </c>
     </row>
@@ -1852,7 +1852,7 @@
         <v>49</v>
       </c>
       <c r="H24" t="n">
-        <v>47</v>
+        <v>13</v>
       </c>
       <c r="I24" t="n">
         <v>148</v>
@@ -1876,7 +1876,7 @@
         <v>14.7051</v>
       </c>
       <c r="P24" t="n">
-        <v>201.0628</v>
+        <v>201.1628</v>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
@@ -1885,7 +1885,7 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:22</t>
+          <t>2026-05-26 14:23:40</t>
         </is>
       </c>
     </row>
@@ -1912,7 +1912,7 @@
         <v>49</v>
       </c>
       <c r="H25" t="n">
-        <v>14</v>
+        <v>42</v>
       </c>
       <c r="I25" t="n">
         <v>148</v>
@@ -1936,7 +1936,7 @@
         <v>14.7051</v>
       </c>
       <c r="P25" t="n">
-        <v>201.0628</v>
+        <v>201.1628</v>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
@@ -1945,7 +1945,7 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:22</t>
+          <t>2026-05-26 14:23:40</t>
         </is>
       </c>
     </row>
@@ -1972,7 +1972,7 @@
         <v>49</v>
       </c>
       <c r="H26" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="I26" t="n">
         <v>148</v>
@@ -1996,7 +1996,7 @@
         <v>14.7051</v>
       </c>
       <c r="P26" t="n">
-        <v>201.0628</v>
+        <v>201.1628</v>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
@@ -2005,7 +2005,7 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:22</t>
+          <t>2026-05-26 14:23:40</t>
         </is>
       </c>
     </row>
@@ -2032,7 +2032,7 @@
         <v>49</v>
       </c>
       <c r="H27" t="n">
-        <v>42</v>
+        <v>22</v>
       </c>
       <c r="I27" t="n">
         <v>148</v>
@@ -2056,7 +2056,7 @@
         <v>14.7051</v>
       </c>
       <c r="P27" t="n">
-        <v>201.0628</v>
+        <v>201.1628</v>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
@@ -2065,7 +2065,7 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:22</t>
+          <t>2026-05-26 14:23:40</t>
         </is>
       </c>
     </row>
@@ -2092,7 +2092,7 @@
         <v>49</v>
       </c>
       <c r="H28" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="I28" t="n">
         <v>148</v>
@@ -2116,7 +2116,7 @@
         <v>14.7051</v>
       </c>
       <c r="P28" t="n">
-        <v>201.0628</v>
+        <v>201.1628</v>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
@@ -2125,7 +2125,7 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:22</t>
+          <t>2026-05-26 14:23:40</t>
         </is>
       </c>
     </row>
@@ -2152,7 +2152,7 @@
         <v>49</v>
       </c>
       <c r="H29" t="n">
-        <v>23</v>
+        <v>2</v>
       </c>
       <c r="I29" t="n">
         <v>148</v>
@@ -2176,7 +2176,7 @@
         <v>14.7051</v>
       </c>
       <c r="P29" t="n">
-        <v>201.0628</v>
+        <v>201.1628</v>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
@@ -2185,7 +2185,7 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:22</t>
+          <t>2026-05-26 14:23:40</t>
         </is>
       </c>
     </row>
@@ -2212,7 +2212,7 @@
         <v>49</v>
       </c>
       <c r="H30" t="n">
-        <v>22</v>
+        <v>40</v>
       </c>
       <c r="I30" t="n">
         <v>148</v>
@@ -2236,7 +2236,7 @@
         <v>14.7051</v>
       </c>
       <c r="P30" t="n">
-        <v>201.0628</v>
+        <v>201.1628</v>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
@@ -2245,7 +2245,7 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:22</t>
+          <t>2026-05-26 14:23:40</t>
         </is>
       </c>
     </row>
@@ -2257,10 +2257,10 @@
         <v>1</v>
       </c>
       <c r="C31" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D31" t="n">
-        <v>5</v>
+        <v>42</v>
       </c>
       <c r="E31" t="n">
         <v>44</v>
@@ -2272,31 +2272,31 @@
         <v>49</v>
       </c>
       <c r="H31" t="n">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="I31" t="n">
-        <v>148</v>
+        <v>187</v>
       </c>
       <c r="J31" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K31" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L31" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N31" t="n">
         <v>0</v>
       </c>
       <c r="O31" t="n">
-        <v>14.7051</v>
+        <v>13.7201</v>
       </c>
       <c r="P31" t="n">
-        <v>201.0628</v>
+        <v>197.9001</v>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
@@ -2305,7 +2305,7 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:22</t>
+          <t>2026-05-26 14:23:40</t>
         </is>
       </c>
     </row>
@@ -2314,7 +2314,7 @@
         <v>31</v>
       </c>
       <c r="B32" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C32" t="n">
         <v>3</v>
@@ -2332,10 +2332,10 @@
         <v>49</v>
       </c>
       <c r="H32" t="n">
-        <v>2</v>
+        <v>41</v>
       </c>
       <c r="I32" t="n">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="J32" t="n">
         <v>3</v>
@@ -2344,19 +2344,19 @@
         <v>3</v>
       </c>
       <c r="L32" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M32" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O32" t="n">
-        <v>14.7051</v>
+        <v>14.8135</v>
       </c>
       <c r="P32" t="n">
-        <v>201.0628</v>
+        <v>197.3138</v>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
@@ -2365,7 +2365,7 @@
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:22</t>
+          <t>2026-05-26 14:23:40</t>
         </is>
       </c>
     </row>
@@ -2374,13 +2374,13 @@
         <v>32</v>
       </c>
       <c r="B33" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C33" t="n">
         <v>5</v>
       </c>
       <c r="D33" t="n">
-        <v>42</v>
+        <v>6</v>
       </c>
       <c r="E33" t="n">
         <v>44</v>
@@ -2392,16 +2392,16 @@
         <v>49</v>
       </c>
       <c r="H33" t="n">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="I33" t="n">
-        <v>187</v>
+        <v>153</v>
       </c>
       <c r="J33" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K33" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L33" t="n">
         <v>3</v>
@@ -2410,13 +2410,13 @@
         <v>3</v>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O33" t="n">
-        <v>13.7201</v>
+        <v>14.4139</v>
       </c>
       <c r="P33" t="n">
-        <v>197.8001</v>
+        <v>196.9547</v>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
@@ -2425,7 +2425,7 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:22</t>
+          <t>2026-05-26 14:23:40</t>
         </is>
       </c>
     </row>
@@ -2434,7 +2434,7 @@
         <v>33</v>
       </c>
       <c r="B34" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C34" t="n">
         <v>3</v>
@@ -2443,40 +2443,40 @@
         <v>5</v>
       </c>
       <c r="E34" t="n">
-        <v>44</v>
+        <v>8</v>
       </c>
       <c r="F34" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="G34" t="n">
         <v>49</v>
       </c>
       <c r="H34" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="I34" t="n">
-        <v>149</v>
+        <v>110</v>
       </c>
       <c r="J34" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K34" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L34" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M34" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O34" t="n">
-        <v>14.8135</v>
+        <v>13.2454</v>
       </c>
       <c r="P34" t="n">
-        <v>197.3138</v>
+        <v>196.5934</v>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
@@ -2485,7 +2485,7 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:22</t>
+          <t>2026-05-26 14:23:40</t>
         </is>
       </c>
     </row>
@@ -2503,19 +2503,19 @@
         <v>5</v>
       </c>
       <c r="E35" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F35" t="n">
         <v>44</v>
       </c>
       <c r="G35" t="n">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="H35" t="n">
-        <v>9</v>
+        <v>41</v>
       </c>
       <c r="I35" t="n">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="J35" t="n">
         <v>2</v>
@@ -2524,19 +2524,19 @@
         <v>4</v>
       </c>
       <c r="L35" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M35" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O35" t="n">
-        <v>13.2454</v>
+        <v>14.5052</v>
       </c>
       <c r="P35" t="n">
-        <v>196.4934</v>
+        <v>196.3829</v>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
@@ -2545,7 +2545,7 @@
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:22</t>
+          <t>2026-05-26 14:23:40</t>
         </is>
       </c>
     </row>
@@ -2572,7 +2572,7 @@
         <v>49</v>
       </c>
       <c r="H36" t="n">
-        <v>17</v>
+        <v>41</v>
       </c>
       <c r="I36" t="n">
         <v>142</v>
@@ -2596,7 +2596,7 @@
         <v>12.753</v>
       </c>
       <c r="P36" t="n">
-        <v>196.2826</v>
+        <v>196.3826</v>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
@@ -2605,7 +2605,7 @@
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:22</t>
+          <t>2026-05-26 14:23:40</t>
         </is>
       </c>
     </row>
@@ -2632,7 +2632,7 @@
         <v>49</v>
       </c>
       <c r="H37" t="n">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="I37" t="n">
         <v>147</v>
@@ -2656,7 +2656,7 @@
         <v>15.2132</v>
       </c>
       <c r="P37" t="n">
-        <v>195.8929</v>
+        <v>195.9929</v>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
@@ -2665,7 +2665,7 @@
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:22</t>
+          <t>2026-05-26 14:23:40</t>
         </is>
       </c>
     </row>
@@ -2677,13 +2677,13 @@
         <v>1</v>
       </c>
       <c r="C38" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D38" t="n">
-        <v>3</v>
+        <v>44</v>
       </c>
       <c r="E38" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F38" t="n">
         <v>46</v>
@@ -2692,22 +2692,22 @@
         <v>49</v>
       </c>
       <c r="H38" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="I38" t="n">
-        <v>145</v>
+        <v>188</v>
       </c>
       <c r="J38" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K38" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L38" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M38" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N38" t="n">
         <v>2</v>
@@ -2716,7 +2716,7 @@
         <v>15.7175</v>
       </c>
       <c r="P38" t="n">
-        <v>195.2938</v>
+        <v>195.3938</v>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
@@ -2725,7 +2725,7 @@
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:22</t>
+          <t>2026-05-26 14:23:40</t>
         </is>
       </c>
     </row>
@@ -2737,46 +2737,46 @@
         <v>1</v>
       </c>
       <c r="C39" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D39" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E39" t="n">
-        <v>9</v>
+        <v>44</v>
       </c>
       <c r="F39" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="G39" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="H39" t="n">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="I39" t="n">
-        <v>108</v>
+        <v>145</v>
       </c>
       <c r="J39" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K39" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L39" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M39" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O39" t="n">
-        <v>13.0231</v>
+        <v>15.7175</v>
       </c>
       <c r="P39" t="n">
-        <v>195.2576</v>
+        <v>195.3938</v>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
@@ -2785,7 +2785,7 @@
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:22</t>
+          <t>2026-05-26 14:23:40</t>
         </is>
       </c>
     </row>
@@ -2800,28 +2800,28 @@
         <v>3</v>
       </c>
       <c r="D40" t="n">
-        <v>44</v>
+        <v>5</v>
       </c>
       <c r="E40" t="n">
-        <v>45</v>
+        <v>9</v>
       </c>
       <c r="F40" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="G40" t="n">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="H40" t="n">
-        <v>41</v>
+        <v>25</v>
       </c>
       <c r="I40" t="n">
-        <v>188</v>
+        <v>108</v>
       </c>
       <c r="J40" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K40" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L40" t="n">
         <v>4</v>
@@ -2830,13 +2830,13 @@
         <v>2</v>
       </c>
       <c r="N40" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O40" t="n">
-        <v>15.7175</v>
+        <v>13.0231</v>
       </c>
       <c r="P40" t="n">
-        <v>195.1938</v>
+        <v>195.3576</v>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
@@ -2845,7 +2845,7 @@
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:22</t>
+          <t>2026-05-26 14:23:40</t>
         </is>
       </c>
     </row>
@@ -2854,28 +2854,28 @@
         <v>40</v>
       </c>
       <c r="B41" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C41" t="n">
         <v>5</v>
       </c>
       <c r="D41" t="n">
+        <v>9</v>
+      </c>
+      <c r="E41" t="n">
+        <v>44</v>
+      </c>
+      <c r="F41" t="n">
+        <v>46</v>
+      </c>
+      <c r="G41" t="n">
+        <v>49</v>
+      </c>
+      <c r="H41" t="n">
         <v>6</v>
       </c>
-      <c r="E41" t="n">
-        <v>44</v>
-      </c>
-      <c r="F41" t="n">
-        <v>46</v>
-      </c>
-      <c r="G41" t="n">
-        <v>49</v>
-      </c>
-      <c r="H41" t="n">
-        <v>31</v>
-      </c>
       <c r="I41" t="n">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="J41" t="n">
         <v>3</v>
@@ -2884,19 +2884,19 @@
         <v>3</v>
       </c>
       <c r="L41" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M41" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O41" t="n">
-        <v>14.4139</v>
+        <v>12.7216</v>
       </c>
       <c r="P41" t="n">
-        <v>194.9547</v>
+        <v>194.9841</v>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
@@ -2905,7 +2905,7 @@
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:22</t>
+          <t>2026-05-26 14:23:40</t>
         </is>
       </c>
     </row>
@@ -2917,25 +2917,25 @@
         <v>1</v>
       </c>
       <c r="C42" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D42" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E42" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F42" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="G42" t="n">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="H42" t="n">
-        <v>6</v>
+        <v>41</v>
       </c>
       <c r="I42" t="n">
-        <v>154</v>
+        <v>142</v>
       </c>
       <c r="J42" t="n">
         <v>3</v>
@@ -2950,13 +2950,13 @@
         <v>2</v>
       </c>
       <c r="N42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O42" t="n">
-        <v>12.7216</v>
+        <v>14.5052</v>
       </c>
       <c r="P42" t="n">
-        <v>194.8841</v>
+        <v>194.7229</v>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
@@ -2965,7 +2965,7 @@
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:22</t>
+          <t>2026-05-26 14:23:40</t>
         </is>
       </c>
     </row>
@@ -2977,31 +2977,31 @@
         <v>1</v>
       </c>
       <c r="C43" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D43" t="n">
-        <v>5</v>
+        <v>43</v>
       </c>
       <c r="E43" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F43" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="G43" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="H43" t="n">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="I43" t="n">
-        <v>142</v>
+        <v>188</v>
       </c>
       <c r="J43" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K43" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L43" t="n">
         <v>4</v>
@@ -3013,10 +3013,10 @@
         <v>1</v>
       </c>
       <c r="O43" t="n">
-        <v>14.5052</v>
+        <v>14.2352</v>
       </c>
       <c r="P43" t="n">
-        <v>194.6229</v>
+        <v>194.1079</v>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
@@ -3025,7 +3025,7 @@
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:22</t>
+          <t>2026-05-26 14:23:40</t>
         </is>
       </c>
     </row>
@@ -3034,34 +3034,34 @@
         <v>43</v>
       </c>
       <c r="B44" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C44" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D44" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E44" t="n">
-        <v>6</v>
+        <v>44</v>
       </c>
       <c r="F44" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="G44" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="H44" t="n">
-        <v>38</v>
+        <v>15</v>
       </c>
       <c r="I44" t="n">
-        <v>105</v>
+        <v>157</v>
       </c>
       <c r="J44" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K44" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L44" t="n">
         <v>3</v>
@@ -3070,13 +3070,13 @@
         <v>3</v>
       </c>
       <c r="N44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O44" t="n">
-        <v>14.5052</v>
+        <v>12.4483</v>
       </c>
       <c r="P44" t="n">
-        <v>194.2829</v>
+        <v>193.3807</v>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
@@ -3085,7 +3085,7 @@
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:22</t>
+          <t>2026-05-26 14:23:40</t>
         </is>
       </c>
     </row>
@@ -3097,46 +3097,46 @@
         <v>1</v>
       </c>
       <c r="C45" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D45" t="n">
-        <v>43</v>
+        <v>5</v>
       </c>
       <c r="E45" t="n">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="F45" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="G45" t="n">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="H45" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="I45" t="n">
-        <v>188</v>
+        <v>137</v>
       </c>
       <c r="J45" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K45" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L45" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M45" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O45" t="n">
-        <v>14.2352</v>
+        <v>12.0996</v>
       </c>
       <c r="P45" t="n">
-        <v>194.0079</v>
+        <v>193.109</v>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
@@ -3145,7 +3145,7 @@
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:22</t>
+          <t>2026-05-26 14:23:40</t>
         </is>
       </c>
     </row>
@@ -3154,16 +3154,16 @@
         <v>45</v>
       </c>
       <c r="B46" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C46" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D46" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E46" t="n">
-        <v>44</v>
+        <v>12</v>
       </c>
       <c r="F46" t="n">
         <v>46</v>
@@ -3172,31 +3172,31 @@
         <v>49</v>
       </c>
       <c r="H46" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="I46" t="n">
-        <v>157</v>
+        <v>116</v>
       </c>
       <c r="J46" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K46" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L46" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M46" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N46" t="n">
         <v>0</v>
       </c>
       <c r="O46" t="n">
-        <v>12.4483</v>
+        <v>12.3386</v>
       </c>
       <c r="P46" t="n">
-        <v>193.3807</v>
+        <v>193.0464</v>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
@@ -3205,7 +3205,7 @@
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:22</t>
+          <t>2026-05-26 14:23:40</t>
         </is>
       </c>
     </row>
@@ -3223,7 +3223,7 @@
         <v>5</v>
       </c>
       <c r="E47" t="n">
-        <v>38</v>
+        <v>10</v>
       </c>
       <c r="F47" t="n">
         <v>44</v>
@@ -3232,16 +3232,16 @@
         <v>46</v>
       </c>
       <c r="H47" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="I47" t="n">
-        <v>137</v>
+        <v>109</v>
       </c>
       <c r="J47" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K47" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L47" t="n">
         <v>3</v>
@@ -3253,10 +3253,10 @@
         <v>0</v>
       </c>
       <c r="O47" t="n">
-        <v>12.0996</v>
+        <v>12.5539</v>
       </c>
       <c r="P47" t="n">
-        <v>193.009</v>
+        <v>192.9247</v>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
@@ -3265,7 +3265,7 @@
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:22</t>
+          <t>2026-05-26 14:23:40</t>
         </is>
       </c>
     </row>
@@ -3280,43 +3280,43 @@
         <v>3</v>
       </c>
       <c r="D48" t="n">
-        <v>5</v>
+        <v>37</v>
       </c>
       <c r="E48" t="n">
-        <v>10</v>
+        <v>44</v>
       </c>
       <c r="F48" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="G48" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="H48" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="I48" t="n">
-        <v>109</v>
+        <v>180</v>
       </c>
       <c r="J48" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K48" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L48" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M48" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N48" t="n">
         <v>0</v>
       </c>
       <c r="O48" t="n">
-        <v>12.5539</v>
+        <v>12.3386</v>
       </c>
       <c r="P48" t="n">
-        <v>192.8247</v>
+        <v>192.6864</v>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
@@ -3325,7 +3325,7 @@
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:22</t>
+          <t>2026-05-26 14:23:40</t>
         </is>
       </c>
     </row>
@@ -3343,16 +3343,16 @@
         <v>5</v>
       </c>
       <c r="E49" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F49" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="G49" t="n">
         <v>49</v>
       </c>
       <c r="H49" t="n">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="I49" t="n">
         <v>116</v>
@@ -3373,10 +3373,10 @@
         <v>0</v>
       </c>
       <c r="O49" t="n">
-        <v>12.3386</v>
+        <v>10.5186</v>
       </c>
       <c r="P49" t="n">
-        <v>192.8064</v>
+        <v>192.0364</v>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
@@ -3385,7 +3385,7 @@
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:22</t>
+          <t>2026-05-26 14:23:40</t>
         </is>
       </c>
     </row>
@@ -3400,43 +3400,43 @@
         <v>3</v>
       </c>
       <c r="D50" t="n">
-        <v>37</v>
+        <v>5</v>
       </c>
       <c r="E50" t="n">
         <v>44</v>
       </c>
       <c r="F50" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G50" t="n">
         <v>49</v>
       </c>
       <c r="H50" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="I50" t="n">
-        <v>180</v>
+        <v>147</v>
       </c>
       <c r="J50" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K50" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L50" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M50" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O50" t="n">
-        <v>12.3386</v>
+        <v>14.7323</v>
       </c>
       <c r="P50" t="n">
-        <v>192.5864</v>
+        <v>191.8707</v>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
@@ -3445,7 +3445,7 @@
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:22</t>
+          <t>2026-05-26 14:23:40</t>
         </is>
       </c>
     </row>
@@ -3463,7 +3463,7 @@
         <v>5</v>
       </c>
       <c r="E51" t="n">
-        <v>14</v>
+        <v>34</v>
       </c>
       <c r="F51" t="n">
         <v>44</v>
@@ -3472,16 +3472,16 @@
         <v>49</v>
       </c>
       <c r="H51" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="I51" t="n">
-        <v>116</v>
+        <v>136</v>
       </c>
       <c r="J51" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K51" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L51" t="n">
         <v>4</v>
@@ -3493,10 +3493,10 @@
         <v>0</v>
       </c>
       <c r="O51" t="n">
-        <v>10.5186</v>
+        <v>10.1311</v>
       </c>
       <c r="P51" t="n">
-        <v>191.7964</v>
+        <v>191.5679</v>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
@@ -3505,7 +3505,7 @@
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:22</t>
+          <t>2026-05-26 14:23:40</t>
         </is>
       </c>
     </row>
@@ -3523,19 +3523,19 @@
         <v>5</v>
       </c>
       <c r="E52" t="n">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="F52" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="G52" t="n">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="H52" t="n">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="I52" t="n">
-        <v>147</v>
+        <v>136</v>
       </c>
       <c r="J52" t="n">
         <v>3</v>
@@ -3544,19 +3544,19 @@
         <v>3</v>
       </c>
       <c r="L52" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M52" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O52" t="n">
-        <v>14.7323</v>
+        <v>11.6619</v>
       </c>
       <c r="P52" t="n">
-        <v>191.6707</v>
+        <v>190.2548</v>
       </c>
       <c r="Q52" t="inlineStr">
         <is>
@@ -3565,7 +3565,7 @@
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:22</t>
+          <t>2026-05-26 14:23:40</t>
         </is>
       </c>
     </row>
@@ -3580,28 +3580,28 @@
         <v>3</v>
       </c>
       <c r="D53" t="n">
-        <v>5</v>
+        <v>31</v>
       </c>
       <c r="E53" t="n">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="F53" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="G53" t="n">
         <v>49</v>
       </c>
       <c r="H53" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="I53" t="n">
-        <v>136</v>
+        <v>174</v>
       </c>
       <c r="J53" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K53" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L53" t="n">
         <v>4</v>
@@ -3613,10 +3613,10 @@
         <v>0</v>
       </c>
       <c r="O53" t="n">
-        <v>10.1311</v>
+        <v>10.0916</v>
       </c>
       <c r="P53" t="n">
-        <v>191.4679</v>
+        <v>189.549</v>
       </c>
       <c r="Q53" t="inlineStr">
         <is>
@@ -3625,7 +3625,7 @@
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:22</t>
+          <t>2026-05-26 14:23:40</t>
         </is>
       </c>
     </row>
@@ -3643,7 +3643,7 @@
         <v>5</v>
       </c>
       <c r="E54" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F54" t="n">
         <v>44</v>
@@ -3652,10 +3652,10 @@
         <v>46</v>
       </c>
       <c r="H54" t="n">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="I54" t="n">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="J54" t="n">
         <v>3</v>
@@ -3664,19 +3664,19 @@
         <v>3</v>
       </c>
       <c r="L54" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M54" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N54" t="n">
         <v>0</v>
       </c>
       <c r="O54" t="n">
-        <v>11.6619</v>
+        <v>11.2428</v>
       </c>
       <c r="P54" t="n">
-        <v>190.1548</v>
+        <v>188.5469</v>
       </c>
       <c r="Q54" t="inlineStr">
         <is>
@@ -3685,7 +3685,7 @@
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:22</t>
+          <t>2026-05-26 14:23:40</t>
         </is>
       </c>
     </row>
@@ -3700,10 +3700,10 @@
         <v>3</v>
       </c>
       <c r="D55" t="n">
-        <v>31</v>
+        <v>5</v>
       </c>
       <c r="E55" t="n">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="F55" t="n">
         <v>46</v>
@@ -3712,16 +3712,16 @@
         <v>49</v>
       </c>
       <c r="H55" t="n">
-        <v>41</v>
+        <v>15</v>
       </c>
       <c r="I55" t="n">
-        <v>174</v>
+        <v>136</v>
       </c>
       <c r="J55" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K55" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L55" t="n">
         <v>4</v>
@@ -3733,10 +3733,10 @@
         <v>0</v>
       </c>
       <c r="O55" t="n">
-        <v>10.0916</v>
+        <v>9.8102</v>
       </c>
       <c r="P55" t="n">
-        <v>189.449</v>
+        <v>188.5255</v>
       </c>
       <c r="Q55" t="inlineStr">
         <is>
@@ -3745,7 +3745,7 @@
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:22</t>
+          <t>2026-05-26 14:23:40</t>
         </is>
       </c>
     </row>
@@ -3760,43 +3760,43 @@
         <v>3</v>
       </c>
       <c r="D56" t="n">
-        <v>5</v>
+        <v>33</v>
       </c>
       <c r="E56" t="n">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="F56" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="G56" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="H56" t="n">
-        <v>4</v>
+        <v>41</v>
       </c>
       <c r="I56" t="n">
-        <v>135</v>
+        <v>176</v>
       </c>
       <c r="J56" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K56" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L56" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M56" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N56" t="n">
         <v>0</v>
       </c>
       <c r="O56" t="n">
-        <v>11.2428</v>
+        <v>10.7443</v>
       </c>
       <c r="P56" t="n">
-        <v>188.4469</v>
+        <v>188.2808</v>
       </c>
       <c r="Q56" t="inlineStr">
         <is>
@@ -3805,7 +3805,7 @@
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:22</t>
+          <t>2026-05-26 14:23:40</t>
         </is>
       </c>
     </row>
@@ -3814,16 +3814,16 @@
         <v>56</v>
       </c>
       <c r="B57" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C57" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D57" t="n">
-        <v>5</v>
+        <v>44</v>
       </c>
       <c r="E57" t="n">
-        <v>32</v>
+        <v>45</v>
       </c>
       <c r="F57" t="n">
         <v>46</v>
@@ -3832,16 +3832,16 @@
         <v>49</v>
       </c>
       <c r="H57" t="n">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="I57" t="n">
-        <v>136</v>
+        <v>192</v>
       </c>
       <c r="J57" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K57" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L57" t="n">
         <v>4</v>
@@ -3850,13 +3850,13 @@
         <v>2</v>
       </c>
       <c r="N57" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O57" t="n">
-        <v>9.8102</v>
+        <v>14.9184</v>
       </c>
       <c r="P57" t="n">
-        <v>188.4255</v>
+        <v>187.4961</v>
       </c>
       <c r="Q57" t="inlineStr">
         <is>
@@ -3865,7 +3865,7 @@
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:22</t>
+          <t>2026-05-26 14:23:40</t>
         </is>
       </c>
     </row>
@@ -3880,10 +3880,10 @@
         <v>3</v>
       </c>
       <c r="D58" t="n">
-        <v>33</v>
+        <v>5</v>
       </c>
       <c r="E58" t="n">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="F58" t="n">
         <v>46</v>
@@ -3892,31 +3892,31 @@
         <v>49</v>
       </c>
       <c r="H58" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="I58" t="n">
-        <v>176</v>
+        <v>143</v>
       </c>
       <c r="J58" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K58" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L58" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M58" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N58" t="n">
         <v>0</v>
       </c>
       <c r="O58" t="n">
-        <v>10.7443</v>
+        <v>12.3386</v>
       </c>
       <c r="P58" t="n">
-        <v>188.1808</v>
+        <v>187.4264</v>
       </c>
       <c r="Q58" t="inlineStr">
         <is>
@@ -3925,7 +3925,7 @@
       </c>
       <c r="R58" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:22</t>
+          <t>2026-05-26 14:23:40</t>
         </is>
       </c>
     </row>
@@ -3934,34 +3934,34 @@
         <v>58</v>
       </c>
       <c r="B59" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C59" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D59" t="n">
-        <v>44</v>
+        <v>5</v>
       </c>
       <c r="E59" t="n">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="F59" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="G59" t="n">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="H59" t="n">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="I59" t="n">
-        <v>192</v>
+        <v>134</v>
       </c>
       <c r="J59" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K59" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L59" t="n">
         <v>4</v>
@@ -3970,13 +3970,13 @@
         <v>2</v>
       </c>
       <c r="N59" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O59" t="n">
-        <v>14.9184</v>
+        <v>10.8444</v>
       </c>
       <c r="P59" t="n">
-        <v>187.3961</v>
+        <v>187.3909</v>
       </c>
       <c r="Q59" t="inlineStr">
         <is>
@@ -3985,7 +3985,7 @@
       </c>
       <c r="R59" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:22</t>
+          <t>2026-05-26 14:23:40</t>
         </is>
       </c>
     </row>
@@ -4003,40 +4003,40 @@
         <v>5</v>
       </c>
       <c r="E60" t="n">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="F60" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="G60" t="n">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="H60" t="n">
-        <v>41</v>
+        <v>28</v>
       </c>
       <c r="I60" t="n">
-        <v>143</v>
+        <v>123</v>
       </c>
       <c r="J60" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K60" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L60" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M60" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N60" t="n">
         <v>0</v>
       </c>
       <c r="O60" t="n">
-        <v>12.3386</v>
+        <v>8.579000000000001</v>
       </c>
       <c r="P60" t="n">
-        <v>187.3264</v>
+        <v>186.4476</v>
       </c>
       <c r="Q60" t="inlineStr">
         <is>
@@ -4045,7 +4045,7 @@
       </c>
       <c r="R60" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:22</t>
+          <t>2026-05-26 14:23:40</t>
         </is>
       </c>
     </row>
@@ -4060,22 +4060,22 @@
         <v>3</v>
       </c>
       <c r="D61" t="n">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="E61" t="n">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="F61" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="G61" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="H61" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="I61" t="n">
-        <v>134</v>
+        <v>164</v>
       </c>
       <c r="J61" t="n">
         <v>3</v>
@@ -4093,10 +4093,10 @@
         <v>0</v>
       </c>
       <c r="O61" t="n">
-        <v>10.8444</v>
+        <v>9.0465</v>
       </c>
       <c r="P61" t="n">
-        <v>187.2909</v>
+        <v>185.5164</v>
       </c>
       <c r="Q61" t="inlineStr">
         <is>
@@ -4105,7 +4105,7 @@
       </c>
       <c r="R61" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:22</t>
+          <t>2026-05-26 14:23:40</t>
         </is>
       </c>
     </row>
@@ -4123,7 +4123,7 @@
         <v>5</v>
       </c>
       <c r="E62" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F62" t="n">
         <v>44</v>
@@ -4132,10 +4132,10 @@
         <v>46</v>
       </c>
       <c r="H62" t="n">
-        <v>28</v>
+        <v>41</v>
       </c>
       <c r="I62" t="n">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="J62" t="n">
         <v>2</v>
@@ -4144,19 +4144,19 @@
         <v>4</v>
       </c>
       <c r="L62" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M62" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N62" t="n">
         <v>0</v>
       </c>
       <c r="O62" t="n">
-        <v>8.579000000000001</v>
+        <v>8.8544</v>
       </c>
       <c r="P62" t="n">
-        <v>186.2476</v>
+        <v>184.6559</v>
       </c>
       <c r="Q62" t="inlineStr">
         <is>
@@ -4165,7 +4165,7 @@
       </c>
       <c r="R62" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:22</t>
+          <t>2026-05-26 14:23:40</t>
         </is>
       </c>
     </row>
@@ -4174,13 +4174,13 @@
         <v>62</v>
       </c>
       <c r="B63" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C63" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D63" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="E63" t="n">
         <v>44</v>
@@ -4192,31 +4192,31 @@
         <v>49</v>
       </c>
       <c r="H63" t="n">
-        <v>19</v>
+        <v>41</v>
       </c>
       <c r="I63" t="n">
-        <v>164</v>
+        <v>175</v>
       </c>
       <c r="J63" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K63" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L63" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M63" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N63" t="n">
         <v>0</v>
       </c>
       <c r="O63" t="n">
-        <v>9.0465</v>
+        <v>8.704000000000001</v>
       </c>
       <c r="P63" t="n">
-        <v>185.4164</v>
+        <v>184.5001</v>
       </c>
       <c r="Q63" t="inlineStr">
         <is>
@@ -4225,7 +4225,7 @@
       </c>
       <c r="R63" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:22</t>
+          <t>2026-05-26 14:23:40</t>
         </is>
       </c>
     </row>
@@ -4237,46 +4237,46 @@
         <v>1</v>
       </c>
       <c r="C64" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D64" t="n">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="E64" t="n">
-        <v>21</v>
+        <v>44</v>
       </c>
       <c r="F64" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="G64" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="H64" t="n">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="I64" t="n">
-        <v>120</v>
+        <v>175</v>
       </c>
       <c r="J64" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K64" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L64" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M64" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N64" t="n">
         <v>0</v>
       </c>
       <c r="O64" t="n">
-        <v>8.8544</v>
+        <v>8.822699999999999</v>
       </c>
       <c r="P64" t="n">
-        <v>184.5559</v>
+        <v>184.1567</v>
       </c>
       <c r="Q64" t="inlineStr">
         <is>
@@ -4285,7 +4285,7 @@
       </c>
       <c r="R64" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:22</t>
+          <t>2026-05-26 14:23:40</t>
         </is>
       </c>
     </row>
@@ -4294,34 +4294,34 @@
         <v>64</v>
       </c>
       <c r="B65" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C65" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D65" t="n">
+        <v>5</v>
+      </c>
+      <c r="E65" t="n">
         <v>28</v>
       </c>
-      <c r="E65" t="n">
-        <v>44</v>
-      </c>
       <c r="F65" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="G65" t="n">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="H65" t="n">
-        <v>9</v>
+        <v>49</v>
       </c>
       <c r="I65" t="n">
-        <v>175</v>
+        <v>127</v>
       </c>
       <c r="J65" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K65" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L65" t="n">
         <v>3</v>
@@ -4333,10 +4333,10 @@
         <v>0</v>
       </c>
       <c r="O65" t="n">
-        <v>8.704000000000001</v>
+        <v>8.8544</v>
       </c>
       <c r="P65" t="n">
-        <v>184.4001</v>
+        <v>184.0359</v>
       </c>
       <c r="Q65" t="inlineStr">
         <is>
@@ -4345,7 +4345,7 @@
       </c>
       <c r="R65" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:22</t>
+          <t>2026-05-26 14:23:40</t>
         </is>
       </c>
     </row>
@@ -4360,7 +4360,7 @@
         <v>5</v>
       </c>
       <c r="D66" t="n">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="E66" t="n">
         <v>44</v>
@@ -4372,31 +4372,31 @@
         <v>49</v>
       </c>
       <c r="H66" t="n">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="I66" t="n">
-        <v>175</v>
+        <v>166</v>
       </c>
       <c r="J66" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K66" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L66" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M66" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N66" t="n">
         <v>0</v>
       </c>
       <c r="O66" t="n">
-        <v>8.822699999999999</v>
+        <v>8.4048</v>
       </c>
       <c r="P66" t="n">
-        <v>184.0567</v>
+        <v>183.5119</v>
       </c>
       <c r="Q66" t="inlineStr">
         <is>
@@ -4405,7 +4405,7 @@
       </c>
       <c r="R66" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:22</t>
+          <t>2026-05-26 14:23:40</t>
         </is>
       </c>
     </row>
@@ -4423,7 +4423,7 @@
         <v>5</v>
       </c>
       <c r="E67" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F67" t="n">
         <v>44</v>
@@ -4432,10 +4432,10 @@
         <v>46</v>
       </c>
       <c r="H67" t="n">
-        <v>49</v>
+        <v>25</v>
       </c>
       <c r="I67" t="n">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="J67" t="n">
         <v>3</v>
@@ -4444,19 +4444,19 @@
         <v>3</v>
       </c>
       <c r="L67" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M67" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N67" t="n">
         <v>0</v>
       </c>
       <c r="O67" t="n">
-        <v>8.8544</v>
+        <v>8.7178</v>
       </c>
       <c r="P67" t="n">
-        <v>183.8359</v>
+        <v>181.7945</v>
       </c>
       <c r="Q67" t="inlineStr">
         <is>
@@ -4465,7 +4465,7 @@
       </c>
       <c r="R67" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:22</t>
+          <t>2026-05-26 14:23:40</t>
         </is>
       </c>
     </row>
@@ -4480,7 +4480,7 @@
         <v>5</v>
       </c>
       <c r="D68" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E68" t="n">
         <v>44</v>
@@ -4492,16 +4492,16 @@
         <v>49</v>
       </c>
       <c r="H68" t="n">
-        <v>43</v>
+        <v>15</v>
       </c>
       <c r="I68" t="n">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="J68" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K68" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L68" t="n">
         <v>4</v>
@@ -4513,10 +4513,10 @@
         <v>0</v>
       </c>
       <c r="O68" t="n">
-        <v>8.4048</v>
+        <v>8.1142</v>
       </c>
       <c r="P68" t="n">
-        <v>183.4119</v>
+        <v>181.6855</v>
       </c>
       <c r="Q68" t="inlineStr">
         <is>
@@ -4525,7 +4525,7 @@
       </c>
       <c r="R68" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:22</t>
+          <t>2026-05-26 14:23:40</t>
         </is>
       </c>
     </row>
@@ -4543,19 +4543,19 @@
         <v>5</v>
       </c>
       <c r="E69" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="F69" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="G69" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="H69" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="I69" t="n">
-        <v>126</v>
+        <v>135</v>
       </c>
       <c r="J69" t="n">
         <v>3</v>
@@ -4564,19 +4564,19 @@
         <v>3</v>
       </c>
       <c r="L69" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M69" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N69" t="n">
         <v>0</v>
       </c>
       <c r="O69" t="n">
-        <v>8.7178</v>
+        <v>9.5624</v>
       </c>
       <c r="P69" t="n">
-        <v>181.6945</v>
+        <v>181.5261</v>
       </c>
       <c r="Q69" t="inlineStr">
         <is>
@@ -4585,7 +4585,7 @@
       </c>
       <c r="R69" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:22</t>
+          <t>2026-05-26 14:23:40</t>
         </is>
       </c>
     </row>
@@ -4600,7 +4600,7 @@
         <v>5</v>
       </c>
       <c r="D70" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E70" t="n">
         <v>44</v>
@@ -4612,10 +4612,10 @@
         <v>49</v>
       </c>
       <c r="H70" t="n">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="I70" t="n">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="J70" t="n">
         <v>4</v>
@@ -4633,10 +4633,10 @@
         <v>0</v>
       </c>
       <c r="O70" t="n">
-        <v>8.1142</v>
+        <v>8.2608</v>
       </c>
       <c r="P70" t="n">
-        <v>181.4455</v>
+        <v>180.4719</v>
       </c>
       <c r="Q70" t="inlineStr">
         <is>
@@ -4645,7 +4645,7 @@
       </c>
       <c r="R70" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:22</t>
+          <t>2026-05-26 14:23:40</t>
         </is>
       </c>
     </row>
@@ -4663,7 +4663,7 @@
         <v>5</v>
       </c>
       <c r="E71" t="n">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="F71" t="n">
         <v>46</v>
@@ -4672,16 +4672,16 @@
         <v>49</v>
       </c>
       <c r="H71" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="I71" t="n">
-        <v>135</v>
+        <v>127</v>
       </c>
       <c r="J71" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K71" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L71" t="n">
         <v>5</v>
@@ -4693,10 +4693,10 @@
         <v>0</v>
       </c>
       <c r="O71" t="n">
-        <v>9.5624</v>
+        <v>9.0465</v>
       </c>
       <c r="P71" t="n">
-        <v>181.4261</v>
+        <v>178.1364</v>
       </c>
       <c r="Q71" t="inlineStr">
         <is>
@@ -4705,127 +4705,7 @@
       </c>
       <c r="R71" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:22</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="n">
-        <v>71</v>
-      </c>
-      <c r="B72" t="n">
-        <v>1</v>
-      </c>
-      <c r="C72" t="n">
-        <v>5</v>
-      </c>
-      <c r="D72" t="n">
-        <v>27</v>
-      </c>
-      <c r="E72" t="n">
-        <v>44</v>
-      </c>
-      <c r="F72" t="n">
-        <v>46</v>
-      </c>
-      <c r="G72" t="n">
-        <v>49</v>
-      </c>
-      <c r="H72" t="n">
-        <v>24</v>
-      </c>
-      <c r="I72" t="n">
-        <v>172</v>
-      </c>
-      <c r="J72" t="n">
-        <v>4</v>
-      </c>
-      <c r="K72" t="n">
-        <v>2</v>
-      </c>
-      <c r="L72" t="n">
-        <v>4</v>
-      </c>
-      <c r="M72" t="n">
-        <v>2</v>
-      </c>
-      <c r="N72" t="n">
-        <v>0</v>
-      </c>
-      <c r="O72" t="n">
-        <v>8.2608</v>
-      </c>
-      <c r="P72" t="n">
-        <v>180.3719</v>
-      </c>
-      <c r="Q72" t="inlineStr">
-        <is>
-          <t>UK49sGeneticOptimizer_v1</t>
-        </is>
-      </c>
-      <c r="R72" t="inlineStr">
-        <is>
-          <t>2026-05-25 14:34:22</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="n">
-        <v>72</v>
-      </c>
-      <c r="B73" t="n">
-        <v>1</v>
-      </c>
-      <c r="C73" t="n">
-        <v>3</v>
-      </c>
-      <c r="D73" t="n">
-        <v>5</v>
-      </c>
-      <c r="E73" t="n">
-        <v>23</v>
-      </c>
-      <c r="F73" t="n">
-        <v>46</v>
-      </c>
-      <c r="G73" t="n">
-        <v>49</v>
-      </c>
-      <c r="H73" t="n">
-        <v>8</v>
-      </c>
-      <c r="I73" t="n">
-        <v>127</v>
-      </c>
-      <c r="J73" t="n">
-        <v>2</v>
-      </c>
-      <c r="K73" t="n">
-        <v>4</v>
-      </c>
-      <c r="L73" t="n">
-        <v>5</v>
-      </c>
-      <c r="M73" t="n">
-        <v>1</v>
-      </c>
-      <c r="N73" t="n">
-        <v>0</v>
-      </c>
-      <c r="O73" t="n">
-        <v>9.0465</v>
-      </c>
-      <c r="P73" t="n">
-        <v>178.0364</v>
-      </c>
-      <c r="Q73" t="inlineStr">
-        <is>
-          <t>UK49sGeneticOptimizer_v1</t>
-        </is>
-      </c>
-      <c r="R73" t="inlineStr">
-        <is>
-          <t>2026-05-25 14:34:22</t>
+          <t>2026-05-26 14:23:40</t>
         </is>
       </c>
     </row>
@@ -4865,10 +4745,10 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>185.5164</v>
+        <v>187.9364</v>
       </c>
       <c r="C2" t="n">
-        <v>163.5212</v>
+        <v>163.7456</v>
       </c>
     </row>
     <row r="3">
@@ -4876,10 +4756,10 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>190.438</v>
+        <v>188.7857</v>
       </c>
       <c r="C3" t="n">
-        <v>172.0636</v>
+        <v>171.2047</v>
       </c>
     </row>
     <row r="4">
@@ -4887,10 +4767,10 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>193.5394</v>
+        <v>194.0009</v>
       </c>
       <c r="C4" t="n">
-        <v>177.6398</v>
+        <v>177.2654</v>
       </c>
     </row>
     <row r="5">
@@ -4898,10 +4778,10 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>197.5781</v>
+        <v>196.1534</v>
       </c>
       <c r="C5" t="n">
-        <v>182.3188</v>
+        <v>183.3124</v>
       </c>
     </row>
     <row r="6">
@@ -4909,10 +4789,10 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>199.2828</v>
+        <v>197.5781</v>
       </c>
       <c r="C6" t="n">
-        <v>185.6147</v>
+        <v>186.0474</v>
       </c>
     </row>
     <row r="7">
@@ -4920,10 +4800,10 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>199.2828</v>
+        <v>199.3828</v>
       </c>
       <c r="C7" t="n">
-        <v>188.2036</v>
+        <v>187.6509</v>
       </c>
     </row>
     <row r="8">
@@ -4931,10 +4811,10 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>199.973</v>
+        <v>200.073</v>
       </c>
       <c r="C8" t="n">
-        <v>191.17</v>
+        <v>189.4962</v>
       </c>
     </row>
     <row r="9">
@@ -4942,10 +4822,10 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>199.973</v>
+        <v>200.7228</v>
       </c>
       <c r="C9" t="n">
-        <v>193.5536</v>
+        <v>193.3432</v>
       </c>
     </row>
     <row r="10">
@@ -4953,10 +4833,10 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>199.973</v>
+        <v>201.1628</v>
       </c>
       <c r="C10" t="n">
-        <v>193.2323</v>
+        <v>195.8227</v>
       </c>
     </row>
     <row r="11">
@@ -4964,10 +4844,10 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>199.973</v>
+        <v>201.1628</v>
       </c>
       <c r="C11" t="n">
-        <v>194.9455</v>
+        <v>195.7128</v>
       </c>
     </row>
     <row r="12">
@@ -4975,10 +4855,10 @@
         <v>11</v>
       </c>
       <c r="B12" t="n">
-        <v>199.973</v>
+        <v>201.1628</v>
       </c>
       <c r="C12" t="n">
-        <v>197.8841</v>
+        <v>197.9913</v>
       </c>
     </row>
     <row r="13">
@@ -4986,10 +4866,10 @@
         <v>12</v>
       </c>
       <c r="B13" t="n">
-        <v>199.973</v>
+        <v>201.1628</v>
       </c>
       <c r="C13" t="n">
-        <v>198.0144</v>
+        <v>198.2188</v>
       </c>
     </row>
     <row r="14">
@@ -4997,10 +4877,10 @@
         <v>13</v>
       </c>
       <c r="B14" t="n">
-        <v>199.973</v>
+        <v>201.1628</v>
       </c>
       <c r="C14" t="n">
-        <v>197.8478</v>
+        <v>198.5954</v>
       </c>
     </row>
     <row r="15">
@@ -5008,10 +4888,10 @@
         <v>14</v>
       </c>
       <c r="B15" t="n">
-        <v>199.973</v>
+        <v>201.1628</v>
       </c>
       <c r="C15" t="n">
-        <v>198.3778</v>
+        <v>199.6283</v>
       </c>
     </row>
     <row r="16">
@@ -5019,10 +4899,10 @@
         <v>15</v>
       </c>
       <c r="B16" t="n">
-        <v>201.0628</v>
+        <v>201.1628</v>
       </c>
       <c r="C16" t="n">
-        <v>198.2511</v>
+        <v>199.2441</v>
       </c>
     </row>
     <row r="17">
@@ -5030,10 +4910,10 @@
         <v>16</v>
       </c>
       <c r="B17" t="n">
-        <v>201.0628</v>
+        <v>201.1628</v>
       </c>
       <c r="C17" t="n">
-        <v>198.3533</v>
+        <v>199.5706</v>
       </c>
     </row>
     <row r="18">
@@ -5041,10 +4921,10 @@
         <v>17</v>
       </c>
       <c r="B18" t="n">
-        <v>201.0628</v>
+        <v>201.1628</v>
       </c>
       <c r="C18" t="n">
-        <v>198.1387</v>
+        <v>199.4644</v>
       </c>
     </row>
     <row r="19">
@@ -5052,10 +4932,10 @@
         <v>18</v>
       </c>
       <c r="B19" t="n">
-        <v>201.0628</v>
+        <v>201.1628</v>
       </c>
       <c r="C19" t="n">
-        <v>197.9426</v>
+        <v>199.1622</v>
       </c>
     </row>
     <row r="20">
@@ -5063,10 +4943,10 @@
         <v>19</v>
       </c>
       <c r="B20" t="n">
-        <v>201.0628</v>
+        <v>201.1628</v>
       </c>
       <c r="C20" t="n">
-        <v>198.9629</v>
+        <v>198.9106</v>
       </c>
     </row>
     <row r="21">
@@ -5074,10 +4954,10 @@
         <v>20</v>
       </c>
       <c r="B21" t="n">
-        <v>201.0628</v>
+        <v>201.1628</v>
       </c>
       <c r="C21" t="n">
-        <v>199.3537</v>
+        <v>199.4692</v>
       </c>
     </row>
     <row r="22">
@@ -5085,10 +4965,10 @@
         <v>21</v>
       </c>
       <c r="B22" t="n">
-        <v>201.0628</v>
+        <v>201.1628</v>
       </c>
       <c r="C22" t="n">
-        <v>199.7184</v>
+        <v>199.8183</v>
       </c>
     </row>
     <row r="23">
@@ -5096,10 +4976,10 @@
         <v>22</v>
       </c>
       <c r="B23" t="n">
-        <v>201.0628</v>
+        <v>201.1628</v>
       </c>
       <c r="C23" t="n">
-        <v>199.283</v>
+        <v>199.3764</v>
       </c>
     </row>
     <row r="24">
@@ -5107,10 +4987,10 @@
         <v>23</v>
       </c>
       <c r="B24" t="n">
-        <v>201.0628</v>
+        <v>201.1628</v>
       </c>
       <c r="C24" t="n">
-        <v>199.3334</v>
+        <v>199.4304</v>
       </c>
     </row>
     <row r="25">
@@ -5118,10 +4998,10 @@
         <v>24</v>
       </c>
       <c r="B25" t="n">
-        <v>201.0628</v>
+        <v>201.1628</v>
       </c>
       <c r="C25" t="n">
-        <v>199.4764</v>
+        <v>199.5798</v>
       </c>
     </row>
     <row r="26">
@@ -5129,10 +5009,10 @@
         <v>25</v>
       </c>
       <c r="B26" t="n">
-        <v>201.0628</v>
+        <v>201.1628</v>
       </c>
       <c r="C26" t="n">
-        <v>199.3789</v>
+        <v>199.4962</v>
       </c>
     </row>
     <row r="27">
@@ -5140,10 +5020,10 @@
         <v>26</v>
       </c>
       <c r="B27" t="n">
-        <v>201.0628</v>
+        <v>201.1628</v>
       </c>
       <c r="C27" t="n">
-        <v>199.0857</v>
+        <v>199.1858</v>
       </c>
     </row>
     <row r="28">
@@ -5151,10 +5031,10 @@
         <v>27</v>
       </c>
       <c r="B28" t="n">
-        <v>201.0628</v>
+        <v>201.1628</v>
       </c>
       <c r="C28" t="n">
-        <v>199.2707</v>
+        <v>199.3979</v>
       </c>
     </row>
     <row r="29">
@@ -5162,10 +5042,10 @@
         <v>28</v>
       </c>
       <c r="B29" t="n">
-        <v>201.0628</v>
+        <v>201.1628</v>
       </c>
       <c r="C29" t="n">
-        <v>199.5397</v>
+        <v>199.6391</v>
       </c>
     </row>
     <row r="30">
@@ -5173,10 +5053,10 @@
         <v>29</v>
       </c>
       <c r="B30" t="n">
-        <v>201.0628</v>
+        <v>201.1628</v>
       </c>
       <c r="C30" t="n">
-        <v>199.6156</v>
+        <v>199.7005</v>
       </c>
     </row>
     <row r="31">
@@ -5184,10 +5064,10 @@
         <v>30</v>
       </c>
       <c r="B31" t="n">
-        <v>201.0628</v>
+        <v>201.1628</v>
       </c>
       <c r="C31" t="n">
-        <v>198.9083</v>
+        <v>199.0174</v>
       </c>
     </row>
     <row r="32">
@@ -5195,10 +5075,10 @@
         <v>31</v>
       </c>
       <c r="B32" t="n">
-        <v>201.0628</v>
+        <v>201.1628</v>
       </c>
       <c r="C32" t="n">
-        <v>199.4584</v>
+        <v>199.5734</v>
       </c>
     </row>
     <row r="33">
@@ -5206,10 +5086,10 @@
         <v>32</v>
       </c>
       <c r="B33" t="n">
-        <v>201.0628</v>
+        <v>201.1628</v>
       </c>
       <c r="C33" t="n">
-        <v>199.1568</v>
+        <v>199.2483</v>
       </c>
     </row>
     <row r="34">
@@ -5217,10 +5097,10 @@
         <v>33</v>
       </c>
       <c r="B34" t="n">
-        <v>201.0628</v>
+        <v>201.1628</v>
       </c>
       <c r="C34" t="n">
-        <v>198.7564</v>
+        <v>198.8576</v>
       </c>
     </row>
     <row r="35">
@@ -5228,10 +5108,10 @@
         <v>34</v>
       </c>
       <c r="B35" t="n">
-        <v>201.0628</v>
+        <v>201.1628</v>
       </c>
       <c r="C35" t="n">
-        <v>199.5506</v>
+        <v>199.6522</v>
       </c>
     </row>
     <row r="36">
@@ -5239,10 +5119,10 @@
         <v>35</v>
       </c>
       <c r="B36" t="n">
-        <v>201.0628</v>
+        <v>201.1628</v>
       </c>
       <c r="C36" t="n">
-        <v>198.7809</v>
+        <v>198.8605</v>
       </c>
     </row>
     <row r="37">
@@ -5250,10 +5130,10 @@
         <v>36</v>
       </c>
       <c r="B37" t="n">
-        <v>201.0628</v>
+        <v>201.1628</v>
       </c>
       <c r="C37" t="n">
-        <v>198.8873</v>
+        <v>198.9881</v>
       </c>
     </row>
     <row r="38">
@@ -5261,10 +5141,10 @@
         <v>37</v>
       </c>
       <c r="B38" t="n">
-        <v>201.0628</v>
+        <v>201.1628</v>
       </c>
       <c r="C38" t="n">
-        <v>199.2874</v>
+        <v>199.3896</v>
       </c>
     </row>
     <row r="39">
@@ -5272,10 +5152,10 @@
         <v>38</v>
       </c>
       <c r="B39" t="n">
-        <v>201.0628</v>
+        <v>201.1628</v>
       </c>
       <c r="C39" t="n">
-        <v>199.117</v>
+        <v>199.2253</v>
       </c>
     </row>
     <row r="40">
@@ -5283,10 +5163,10 @@
         <v>39</v>
       </c>
       <c r="B40" t="n">
-        <v>201.0628</v>
+        <v>201.1628</v>
       </c>
       <c r="C40" t="n">
-        <v>199.1313</v>
+        <v>199.2259</v>
       </c>
     </row>
     <row r="41">
@@ -5294,10 +5174,10 @@
         <v>40</v>
       </c>
       <c r="B41" t="n">
-        <v>201.0628</v>
+        <v>201.1628</v>
       </c>
       <c r="C41" t="n">
-        <v>199.6223</v>
+        <v>199.7308</v>
       </c>
     </row>
     <row r="42">
@@ -5305,10 +5185,10 @@
         <v>41</v>
       </c>
       <c r="B42" t="n">
-        <v>201.0628</v>
+        <v>201.1628</v>
       </c>
       <c r="C42" t="n">
-        <v>198.7013</v>
+        <v>198.7973</v>
       </c>
     </row>
     <row r="43">
@@ -5316,10 +5196,10 @@
         <v>42</v>
       </c>
       <c r="B43" t="n">
-        <v>201.0628</v>
+        <v>201.1628</v>
       </c>
       <c r="C43" t="n">
-        <v>199.2782</v>
+        <v>199.3791</v>
       </c>
     </row>
     <row r="44">
@@ -5327,10 +5207,10 @@
         <v>43</v>
       </c>
       <c r="B44" t="n">
-        <v>201.0628</v>
+        <v>201.1628</v>
       </c>
       <c r="C44" t="n">
-        <v>199.6678</v>
+        <v>199.7679</v>
       </c>
     </row>
     <row r="45">
@@ -5338,10 +5218,10 @@
         <v>44</v>
       </c>
       <c r="B45" t="n">
-        <v>201.0628</v>
+        <v>201.1628</v>
       </c>
       <c r="C45" t="n">
-        <v>199.7717</v>
+        <v>199.8738</v>
       </c>
     </row>
     <row r="46">
@@ -5349,10 +5229,10 @@
         <v>45</v>
       </c>
       <c r="B46" t="n">
-        <v>201.0628</v>
+        <v>201.1628</v>
       </c>
       <c r="C46" t="n">
-        <v>199.5718</v>
+        <v>199.6577</v>
       </c>
     </row>
     <row r="47">
@@ -5360,10 +5240,10 @@
         <v>46</v>
       </c>
       <c r="B47" t="n">
-        <v>201.0628</v>
+        <v>201.1628</v>
       </c>
       <c r="C47" t="n">
-        <v>199.0637</v>
+        <v>199.1745</v>
       </c>
     </row>
     <row r="48">
@@ -5371,10 +5251,10 @@
         <v>47</v>
       </c>
       <c r="B48" t="n">
-        <v>201.0628</v>
+        <v>201.1628</v>
       </c>
       <c r="C48" t="n">
-        <v>199.0506</v>
+        <v>199.1839</v>
       </c>
     </row>
     <row r="49">
@@ -5382,10 +5262,10 @@
         <v>48</v>
       </c>
       <c r="B49" t="n">
-        <v>201.0628</v>
+        <v>201.1628</v>
       </c>
       <c r="C49" t="n">
-        <v>198.8556</v>
+        <v>198.9575</v>
       </c>
     </row>
     <row r="50">
@@ -5393,10 +5273,10 @@
         <v>49</v>
       </c>
       <c r="B50" t="n">
-        <v>201.0628</v>
+        <v>201.1628</v>
       </c>
       <c r="C50" t="n">
-        <v>198.6801</v>
+        <v>198.7833</v>
       </c>
     </row>
     <row r="51">
@@ -5404,10 +5284,10 @@
         <v>50</v>
       </c>
       <c r="B51" t="n">
-        <v>201.0628</v>
+        <v>201.1628</v>
       </c>
       <c r="C51" t="n">
-        <v>199.4379</v>
+        <v>199.5387</v>
       </c>
     </row>
     <row r="52">
@@ -5415,10 +5295,10 @@
         <v>51</v>
       </c>
       <c r="B52" t="n">
-        <v>201.0628</v>
+        <v>201.1628</v>
       </c>
       <c r="C52" t="n">
-        <v>199.7527</v>
+        <v>199.8526</v>
       </c>
     </row>
     <row r="53">
@@ -5426,10 +5306,10 @@
         <v>52</v>
       </c>
       <c r="B53" t="n">
-        <v>201.0628</v>
+        <v>201.1628</v>
       </c>
       <c r="C53" t="n">
-        <v>199.4437</v>
+        <v>199.5449</v>
       </c>
     </row>
     <row r="54">
@@ -5437,10 +5317,10 @@
         <v>53</v>
       </c>
       <c r="B54" t="n">
-        <v>201.0628</v>
+        <v>201.1628</v>
       </c>
       <c r="C54" t="n">
-        <v>198.9938</v>
+        <v>199.1031</v>
       </c>
     </row>
     <row r="55">
@@ -5448,10 +5328,10 @@
         <v>54</v>
       </c>
       <c r="B55" t="n">
-        <v>201.0628</v>
+        <v>201.1628</v>
       </c>
       <c r="C55" t="n">
-        <v>199.1345</v>
+        <v>199.2682</v>
       </c>
     </row>
     <row r="56">
@@ -5459,10 +5339,10 @@
         <v>55</v>
       </c>
       <c r="B56" t="n">
-        <v>201.0628</v>
+        <v>201.1628</v>
       </c>
       <c r="C56" t="n">
-        <v>199.3785</v>
+        <v>199.4864</v>
       </c>
     </row>
     <row r="57">
@@ -5470,10 +5350,10 @@
         <v>56</v>
       </c>
       <c r="B57" t="n">
-        <v>201.0628</v>
+        <v>201.1628</v>
       </c>
       <c r="C57" t="n">
-        <v>199.6699</v>
+        <v>199.7704</v>
       </c>
     </row>
     <row r="58">
@@ -5481,10 +5361,10 @@
         <v>57</v>
       </c>
       <c r="B58" t="n">
-        <v>201.0628</v>
+        <v>201.1628</v>
       </c>
       <c r="C58" t="n">
-        <v>199.0154</v>
+        <v>199.1121</v>
       </c>
     </row>
     <row r="59">
@@ -5492,10 +5372,10 @@
         <v>58</v>
       </c>
       <c r="B59" t="n">
-        <v>201.0628</v>
+        <v>201.1628</v>
       </c>
       <c r="C59" t="n">
-        <v>199.1356</v>
+        <v>199.2367</v>
       </c>
     </row>
     <row r="60">
@@ -5503,10 +5383,10 @@
         <v>59</v>
       </c>
       <c r="B60" t="n">
-        <v>201.0628</v>
+        <v>201.1628</v>
       </c>
       <c r="C60" t="n">
-        <v>198.4903</v>
+        <v>198.592</v>
       </c>
     </row>
     <row r="61">
@@ -5514,10 +5394,10 @@
         <v>60</v>
       </c>
       <c r="B61" t="n">
-        <v>201.0628</v>
+        <v>201.1628</v>
       </c>
       <c r="C61" t="n">
-        <v>199.362</v>
+        <v>199.4795</v>
       </c>
     </row>
   </sheetData>

--- a/data/exports/optimization/uk49s_genetic_optimizer_results.xlsx
+++ b/data/exports/optimization/uk49s_genetic_optimizer_results.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R71"/>
+  <dimension ref="A1:R75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -532,7 +532,7 @@
         <v>49</v>
       </c>
       <c r="H2" t="n">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="I2" t="n">
         <v>148</v>
@@ -556,7 +556,7 @@
         <v>14.7051</v>
       </c>
       <c r="P2" t="n">
-        <v>201.1628</v>
+        <v>201.2628</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -565,7 +565,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:40</t>
+          <t>2026-05-27 14:58:31</t>
         </is>
       </c>
     </row>
@@ -592,7 +592,7 @@
         <v>49</v>
       </c>
       <c r="H3" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="I3" t="n">
         <v>148</v>
@@ -616,7 +616,7 @@
         <v>14.7051</v>
       </c>
       <c r="P3" t="n">
-        <v>201.1628</v>
+        <v>201.2628</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -625,7 +625,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:40</t>
+          <t>2026-05-27 14:58:31</t>
         </is>
       </c>
     </row>
@@ -652,7 +652,7 @@
         <v>49</v>
       </c>
       <c r="H4" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="I4" t="n">
         <v>148</v>
@@ -676,7 +676,7 @@
         <v>14.7051</v>
       </c>
       <c r="P4" t="n">
-        <v>201.1628</v>
+        <v>201.2628</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -685,7 +685,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:40</t>
+          <t>2026-05-27 14:58:31</t>
         </is>
       </c>
     </row>
@@ -712,7 +712,7 @@
         <v>49</v>
       </c>
       <c r="H5" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="I5" t="n">
         <v>148</v>
@@ -736,7 +736,7 @@
         <v>14.7051</v>
       </c>
       <c r="P5" t="n">
-        <v>201.1628</v>
+        <v>201.2628</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -745,7 +745,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:40</t>
+          <t>2026-05-27 14:58:31</t>
         </is>
       </c>
     </row>
@@ -772,7 +772,7 @@
         <v>49</v>
       </c>
       <c r="H6" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="I6" t="n">
         <v>148</v>
@@ -796,7 +796,7 @@
         <v>14.7051</v>
       </c>
       <c r="P6" t="n">
-        <v>201.1628</v>
+        <v>201.2628</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -805,7 +805,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:40</t>
+          <t>2026-05-27 14:58:31</t>
         </is>
       </c>
     </row>
@@ -832,7 +832,7 @@
         <v>49</v>
       </c>
       <c r="H7" t="n">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="I7" t="n">
         <v>148</v>
@@ -856,7 +856,7 @@
         <v>14.7051</v>
       </c>
       <c r="P7" t="n">
-        <v>201.1628</v>
+        <v>201.2628</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
@@ -865,7 +865,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:40</t>
+          <t>2026-05-27 14:58:31</t>
         </is>
       </c>
     </row>
@@ -892,7 +892,7 @@
         <v>49</v>
       </c>
       <c r="H8" t="n">
-        <v>24</v>
+        <v>47</v>
       </c>
       <c r="I8" t="n">
         <v>148</v>
@@ -916,7 +916,7 @@
         <v>14.7051</v>
       </c>
       <c r="P8" t="n">
-        <v>201.1628</v>
+        <v>201.2628</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:40</t>
+          <t>2026-05-27 14:58:31</t>
         </is>
       </c>
     </row>
@@ -976,7 +976,7 @@
         <v>14.7051</v>
       </c>
       <c r="P9" t="n">
-        <v>201.1628</v>
+        <v>201.2628</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
@@ -985,7 +985,7 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:40</t>
+          <t>2026-05-27 14:58:31</t>
         </is>
       </c>
     </row>
@@ -1012,7 +1012,7 @@
         <v>49</v>
       </c>
       <c r="H10" t="n">
-        <v>28</v>
+        <v>48</v>
       </c>
       <c r="I10" t="n">
         <v>148</v>
@@ -1036,7 +1036,7 @@
         <v>14.7051</v>
       </c>
       <c r="P10" t="n">
-        <v>201.1628</v>
+        <v>201.2628</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
@@ -1045,7 +1045,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:40</t>
+          <t>2026-05-27 14:58:31</t>
         </is>
       </c>
     </row>
@@ -1072,7 +1072,7 @@
         <v>49</v>
       </c>
       <c r="H11" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="I11" t="n">
         <v>148</v>
@@ -1096,7 +1096,7 @@
         <v>14.7051</v>
       </c>
       <c r="P11" t="n">
-        <v>201.1628</v>
+        <v>201.2628</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
@@ -1105,7 +1105,7 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:40</t>
+          <t>2026-05-27 14:58:31</t>
         </is>
       </c>
     </row>
@@ -1132,7 +1132,7 @@
         <v>49</v>
       </c>
       <c r="H12" t="n">
-        <v>23</v>
+        <v>41</v>
       </c>
       <c r="I12" t="n">
         <v>148</v>
@@ -1156,7 +1156,7 @@
         <v>14.7051</v>
       </c>
       <c r="P12" t="n">
-        <v>201.1628</v>
+        <v>201.2628</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
@@ -1165,7 +1165,7 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:40</t>
+          <t>2026-05-27 14:58:31</t>
         </is>
       </c>
     </row>
@@ -1192,7 +1192,7 @@
         <v>49</v>
       </c>
       <c r="H13" t="n">
-        <v>16</v>
+        <v>45</v>
       </c>
       <c r="I13" t="n">
         <v>148</v>
@@ -1216,7 +1216,7 @@
         <v>14.7051</v>
       </c>
       <c r="P13" t="n">
-        <v>201.1628</v>
+        <v>201.2628</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
@@ -1225,7 +1225,7 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:40</t>
+          <t>2026-05-27 14:58:31</t>
         </is>
       </c>
     </row>
@@ -1252,7 +1252,7 @@
         <v>49</v>
       </c>
       <c r="H14" t="n">
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="I14" t="n">
         <v>148</v>
@@ -1276,7 +1276,7 @@
         <v>14.7051</v>
       </c>
       <c r="P14" t="n">
-        <v>201.1628</v>
+        <v>201.2628</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
@@ -1285,7 +1285,7 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:40</t>
+          <t>2026-05-27 14:58:31</t>
         </is>
       </c>
     </row>
@@ -1312,7 +1312,7 @@
         <v>49</v>
       </c>
       <c r="H15" t="n">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="I15" t="n">
         <v>148</v>
@@ -1336,7 +1336,7 @@
         <v>14.7051</v>
       </c>
       <c r="P15" t="n">
-        <v>201.1628</v>
+        <v>201.2628</v>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
@@ -1345,7 +1345,7 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:40</t>
+          <t>2026-05-27 14:58:31</t>
         </is>
       </c>
     </row>
@@ -1396,7 +1396,7 @@
         <v>14.7051</v>
       </c>
       <c r="P16" t="n">
-        <v>201.1628</v>
+        <v>201.2628</v>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
@@ -1405,7 +1405,7 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:40</t>
+          <t>2026-05-27 14:58:31</t>
         </is>
       </c>
     </row>
@@ -1432,7 +1432,7 @@
         <v>49</v>
       </c>
       <c r="H17" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="I17" t="n">
         <v>148</v>
@@ -1456,7 +1456,7 @@
         <v>14.7051</v>
       </c>
       <c r="P17" t="n">
-        <v>201.1628</v>
+        <v>201.2628</v>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
@@ -1465,7 +1465,7 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:40</t>
+          <t>2026-05-27 14:58:31</t>
         </is>
       </c>
     </row>
@@ -1492,7 +1492,7 @@
         <v>49</v>
       </c>
       <c r="H18" t="n">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="I18" t="n">
         <v>148</v>
@@ -1516,7 +1516,7 @@
         <v>14.7051</v>
       </c>
       <c r="P18" t="n">
-        <v>201.1628</v>
+        <v>201.2628</v>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
@@ -1525,7 +1525,7 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:40</t>
+          <t>2026-05-27 14:58:31</t>
         </is>
       </c>
     </row>
@@ -1552,7 +1552,7 @@
         <v>49</v>
       </c>
       <c r="H19" t="n">
-        <v>33</v>
+        <v>10</v>
       </c>
       <c r="I19" t="n">
         <v>148</v>
@@ -1576,7 +1576,7 @@
         <v>14.7051</v>
       </c>
       <c r="P19" t="n">
-        <v>201.1628</v>
+        <v>201.2628</v>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
@@ -1585,7 +1585,7 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:40</t>
+          <t>2026-05-27 14:58:31</t>
         </is>
       </c>
     </row>
@@ -1612,7 +1612,7 @@
         <v>49</v>
       </c>
       <c r="H20" t="n">
-        <v>30</v>
+        <v>7</v>
       </c>
       <c r="I20" t="n">
         <v>148</v>
@@ -1636,7 +1636,7 @@
         <v>14.7051</v>
       </c>
       <c r="P20" t="n">
-        <v>201.1628</v>
+        <v>201.2628</v>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
@@ -1645,7 +1645,7 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:40</t>
+          <t>2026-05-27 14:58:31</t>
         </is>
       </c>
     </row>
@@ -1672,7 +1672,7 @@
         <v>49</v>
       </c>
       <c r="H21" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="I21" t="n">
         <v>148</v>
@@ -1696,7 +1696,7 @@
         <v>14.7051</v>
       </c>
       <c r="P21" t="n">
-        <v>201.1628</v>
+        <v>201.2628</v>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
@@ -1705,7 +1705,7 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:40</t>
+          <t>2026-05-27 14:58:31</t>
         </is>
       </c>
     </row>
@@ -1732,7 +1732,7 @@
         <v>49</v>
       </c>
       <c r="H22" t="n">
-        <v>47</v>
+        <v>30</v>
       </c>
       <c r="I22" t="n">
         <v>148</v>
@@ -1756,7 +1756,7 @@
         <v>14.7051</v>
       </c>
       <c r="P22" t="n">
-        <v>201.1628</v>
+        <v>201.2628</v>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
@@ -1765,7 +1765,7 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:40</t>
+          <t>2026-05-27 14:58:31</t>
         </is>
       </c>
     </row>
@@ -1792,7 +1792,7 @@
         <v>49</v>
       </c>
       <c r="H23" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="I23" t="n">
         <v>148</v>
@@ -1816,7 +1816,7 @@
         <v>14.7051</v>
       </c>
       <c r="P23" t="n">
-        <v>201.1628</v>
+        <v>201.2628</v>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
@@ -1825,7 +1825,7 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:40</t>
+          <t>2026-05-27 14:58:31</t>
         </is>
       </c>
     </row>
@@ -1852,7 +1852,7 @@
         <v>49</v>
       </c>
       <c r="H24" t="n">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="I24" t="n">
         <v>148</v>
@@ -1876,7 +1876,7 @@
         <v>14.7051</v>
       </c>
       <c r="P24" t="n">
-        <v>201.1628</v>
+        <v>201.2628</v>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
@@ -1885,7 +1885,7 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:40</t>
+          <t>2026-05-27 14:58:31</t>
         </is>
       </c>
     </row>
@@ -1912,7 +1912,7 @@
         <v>49</v>
       </c>
       <c r="H25" t="n">
-        <v>42</v>
+        <v>15</v>
       </c>
       <c r="I25" t="n">
         <v>148</v>
@@ -1936,7 +1936,7 @@
         <v>14.7051</v>
       </c>
       <c r="P25" t="n">
-        <v>201.1628</v>
+        <v>201.2628</v>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
@@ -1945,7 +1945,7 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:40</t>
+          <t>2026-05-27 14:58:31</t>
         </is>
       </c>
     </row>
@@ -1972,7 +1972,7 @@
         <v>49</v>
       </c>
       <c r="H26" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="I26" t="n">
         <v>148</v>
@@ -1996,7 +1996,7 @@
         <v>14.7051</v>
       </c>
       <c r="P26" t="n">
-        <v>201.1628</v>
+        <v>201.2628</v>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
@@ -2005,7 +2005,7 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:40</t>
+          <t>2026-05-27 14:58:31</t>
         </is>
       </c>
     </row>
@@ -2032,7 +2032,7 @@
         <v>49</v>
       </c>
       <c r="H27" t="n">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="I27" t="n">
         <v>148</v>
@@ -2056,7 +2056,7 @@
         <v>14.7051</v>
       </c>
       <c r="P27" t="n">
-        <v>201.1628</v>
+        <v>201.2628</v>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
@@ -2065,7 +2065,7 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:40</t>
+          <t>2026-05-27 14:58:31</t>
         </is>
       </c>
     </row>
@@ -2092,7 +2092,7 @@
         <v>49</v>
       </c>
       <c r="H28" t="n">
-        <v>19</v>
+        <v>42</v>
       </c>
       <c r="I28" t="n">
         <v>148</v>
@@ -2116,7 +2116,7 @@
         <v>14.7051</v>
       </c>
       <c r="P28" t="n">
-        <v>201.1628</v>
+        <v>201.2628</v>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
@@ -2125,7 +2125,7 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:40</t>
+          <t>2026-05-27 14:58:31</t>
         </is>
       </c>
     </row>
@@ -2152,7 +2152,7 @@
         <v>49</v>
       </c>
       <c r="H29" t="n">
-        <v>2</v>
+        <v>23</v>
       </c>
       <c r="I29" t="n">
         <v>148</v>
@@ -2176,7 +2176,7 @@
         <v>14.7051</v>
       </c>
       <c r="P29" t="n">
-        <v>201.1628</v>
+        <v>201.2628</v>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
@@ -2185,7 +2185,7 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:40</t>
+          <t>2026-05-27 14:58:31</t>
         </is>
       </c>
     </row>
@@ -2212,7 +2212,7 @@
         <v>49</v>
       </c>
       <c r="H30" t="n">
-        <v>40</v>
+        <v>22</v>
       </c>
       <c r="I30" t="n">
         <v>148</v>
@@ -2236,7 +2236,7 @@
         <v>14.7051</v>
       </c>
       <c r="P30" t="n">
-        <v>201.1628</v>
+        <v>201.2628</v>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
@@ -2245,7 +2245,7 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:40</t>
+          <t>2026-05-27 14:58:31</t>
         </is>
       </c>
     </row>
@@ -2257,10 +2257,10 @@
         <v>1</v>
       </c>
       <c r="C31" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D31" t="n">
-        <v>42</v>
+        <v>5</v>
       </c>
       <c r="E31" t="n">
         <v>44</v>
@@ -2272,31 +2272,31 @@
         <v>49</v>
       </c>
       <c r="H31" t="n">
-        <v>41</v>
+        <v>24</v>
       </c>
       <c r="I31" t="n">
-        <v>187</v>
+        <v>148</v>
       </c>
       <c r="J31" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L31" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M31" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N31" t="n">
         <v>0</v>
       </c>
       <c r="O31" t="n">
-        <v>13.7201</v>
+        <v>14.7051</v>
       </c>
       <c r="P31" t="n">
-        <v>197.9001</v>
+        <v>201.2628</v>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
@@ -2305,7 +2305,7 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:40</t>
+          <t>2026-05-27 14:58:31</t>
         </is>
       </c>
     </row>
@@ -2314,7 +2314,7 @@
         <v>31</v>
       </c>
       <c r="B32" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C32" t="n">
         <v>3</v>
@@ -2332,10 +2332,10 @@
         <v>49</v>
       </c>
       <c r="H32" t="n">
-        <v>41</v>
+        <v>19</v>
       </c>
       <c r="I32" t="n">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="J32" t="n">
         <v>3</v>
@@ -2344,19 +2344,19 @@
         <v>3</v>
       </c>
       <c r="L32" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M32" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O32" t="n">
-        <v>14.8135</v>
+        <v>14.7051</v>
       </c>
       <c r="P32" t="n">
-        <v>197.3138</v>
+        <v>201.2628</v>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
@@ -2365,7 +2365,7 @@
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:40</t>
+          <t>2026-05-27 14:58:31</t>
         </is>
       </c>
     </row>
@@ -2374,13 +2374,13 @@
         <v>32</v>
       </c>
       <c r="B33" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C33" t="n">
         <v>5</v>
       </c>
       <c r="D33" t="n">
-        <v>6</v>
+        <v>42</v>
       </c>
       <c r="E33" t="n">
         <v>44</v>
@@ -2392,16 +2392,16 @@
         <v>49</v>
       </c>
       <c r="H33" t="n">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="I33" t="n">
-        <v>153</v>
+        <v>187</v>
       </c>
       <c r="J33" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K33" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L33" t="n">
         <v>3</v>
@@ -2410,13 +2410,13 @@
         <v>3</v>
       </c>
       <c r="N33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O33" t="n">
-        <v>14.4139</v>
+        <v>13.7201</v>
       </c>
       <c r="P33" t="n">
-        <v>196.9547</v>
+        <v>198.0001</v>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
@@ -2425,7 +2425,7 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:40</t>
+          <t>2026-05-27 14:58:31</t>
         </is>
       </c>
     </row>
@@ -2434,7 +2434,7 @@
         <v>33</v>
       </c>
       <c r="B34" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C34" t="n">
         <v>3</v>
@@ -2443,40 +2443,40 @@
         <v>5</v>
       </c>
       <c r="E34" t="n">
-        <v>8</v>
+        <v>44</v>
       </c>
       <c r="F34" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="G34" t="n">
         <v>49</v>
       </c>
       <c r="H34" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="I34" t="n">
-        <v>110</v>
+        <v>149</v>
       </c>
       <c r="J34" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K34" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L34" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M34" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O34" t="n">
-        <v>13.2454</v>
+        <v>14.8135</v>
       </c>
       <c r="P34" t="n">
-        <v>196.5934</v>
+        <v>197.4138</v>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
@@ -2485,7 +2485,7 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:40</t>
+          <t>2026-05-27 14:58:31</t>
         </is>
       </c>
     </row>
@@ -2494,34 +2494,34 @@
         <v>34</v>
       </c>
       <c r="B35" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C35" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D35" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E35" t="n">
-        <v>6</v>
+        <v>44</v>
       </c>
       <c r="F35" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="G35" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="H35" t="n">
         <v>41</v>
       </c>
       <c r="I35" t="n">
-        <v>105</v>
+        <v>153</v>
       </c>
       <c r="J35" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K35" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L35" t="n">
         <v>3</v>
@@ -2533,10 +2533,10 @@
         <v>1</v>
       </c>
       <c r="O35" t="n">
-        <v>14.5052</v>
+        <v>14.4139</v>
       </c>
       <c r="P35" t="n">
-        <v>196.3829</v>
+        <v>197.0547</v>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
@@ -2545,7 +2545,7 @@
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:40</t>
+          <t>2026-05-27 14:58:31</t>
         </is>
       </c>
     </row>
@@ -2560,43 +2560,43 @@
         <v>3</v>
       </c>
       <c r="D36" t="n">
-        <v>5</v>
+        <v>40</v>
       </c>
       <c r="E36" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="F36" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="G36" t="n">
         <v>49</v>
       </c>
       <c r="H36" t="n">
-        <v>41</v>
+        <v>21</v>
       </c>
       <c r="I36" t="n">
-        <v>142</v>
+        <v>183</v>
       </c>
       <c r="J36" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K36" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L36" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M36" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N36" t="n">
         <v>0</v>
       </c>
       <c r="O36" t="n">
-        <v>12.753</v>
+        <v>13.7201</v>
       </c>
       <c r="P36" t="n">
-        <v>196.3826</v>
+        <v>196.8401</v>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
@@ -2605,7 +2605,7 @@
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:40</t>
+          <t>2026-05-27 14:58:31</t>
         </is>
       </c>
     </row>
@@ -2620,43 +2620,43 @@
         <v>3</v>
       </c>
       <c r="D37" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E37" t="n">
-        <v>44</v>
+        <v>8</v>
       </c>
       <c r="F37" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="G37" t="n">
         <v>49</v>
       </c>
       <c r="H37" t="n">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="I37" t="n">
-        <v>147</v>
+        <v>110</v>
       </c>
       <c r="J37" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K37" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L37" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M37" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O37" t="n">
-        <v>15.2132</v>
+        <v>13.2454</v>
       </c>
       <c r="P37" t="n">
-        <v>195.9929</v>
+        <v>196.7934</v>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
@@ -2665,7 +2665,7 @@
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:40</t>
+          <t>2026-05-27 14:58:31</t>
         </is>
       </c>
     </row>
@@ -2680,28 +2680,28 @@
         <v>3</v>
       </c>
       <c r="D38" t="n">
-        <v>44</v>
+        <v>5</v>
       </c>
       <c r="E38" t="n">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="F38" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="G38" t="n">
         <v>49</v>
       </c>
       <c r="H38" t="n">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="I38" t="n">
-        <v>188</v>
+        <v>142</v>
       </c>
       <c r="J38" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K38" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L38" t="n">
         <v>4</v>
@@ -2710,13 +2710,13 @@
         <v>2</v>
       </c>
       <c r="N38" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O38" t="n">
-        <v>15.7175</v>
+        <v>12.753</v>
       </c>
       <c r="P38" t="n">
-        <v>195.3938</v>
+        <v>196.5826</v>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
@@ -2725,7 +2725,7 @@
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:40</t>
+          <t>2026-05-27 14:58:31</t>
         </is>
       </c>
     </row>
@@ -2737,31 +2737,31 @@
         <v>1</v>
       </c>
       <c r="C39" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D39" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E39" t="n">
-        <v>44</v>
+        <v>6</v>
       </c>
       <c r="F39" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="G39" t="n">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="H39" t="n">
-        <v>23</v>
+        <v>48</v>
       </c>
       <c r="I39" t="n">
-        <v>145</v>
+        <v>105</v>
       </c>
       <c r="J39" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K39" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L39" t="n">
         <v>3</v>
@@ -2770,13 +2770,13 @@
         <v>3</v>
       </c>
       <c r="N39" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O39" t="n">
-        <v>15.7175</v>
+        <v>14.5052</v>
       </c>
       <c r="P39" t="n">
-        <v>195.3938</v>
+        <v>196.4829</v>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
@@ -2785,7 +2785,7 @@
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:40</t>
+          <t>2026-05-27 14:58:31</t>
         </is>
       </c>
     </row>
@@ -2800,43 +2800,43 @@
         <v>3</v>
       </c>
       <c r="D40" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E40" t="n">
-        <v>9</v>
+        <v>44</v>
       </c>
       <c r="F40" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="G40" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="H40" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="I40" t="n">
-        <v>108</v>
+        <v>147</v>
       </c>
       <c r="J40" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K40" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L40" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M40" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O40" t="n">
-        <v>13.0231</v>
+        <v>15.2132</v>
       </c>
       <c r="P40" t="n">
-        <v>195.3576</v>
+        <v>195.9929</v>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
@@ -2845,7 +2845,7 @@
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:40</t>
+          <t>2026-05-27 14:58:31</t>
         </is>
       </c>
     </row>
@@ -2857,31 +2857,31 @@
         <v>1</v>
       </c>
       <c r="C41" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D41" t="n">
+        <v>5</v>
+      </c>
+      <c r="E41" t="n">
         <v>9</v>
       </c>
-      <c r="E41" t="n">
-        <v>44</v>
-      </c>
       <c r="F41" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="G41" t="n">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="H41" t="n">
-        <v>6</v>
+        <v>34</v>
       </c>
       <c r="I41" t="n">
-        <v>154</v>
+        <v>108</v>
       </c>
       <c r="J41" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K41" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L41" t="n">
         <v>4</v>
@@ -2893,10 +2893,10 @@
         <v>0</v>
       </c>
       <c r="O41" t="n">
-        <v>12.7216</v>
+        <v>13.0231</v>
       </c>
       <c r="P41" t="n">
-        <v>194.9841</v>
+        <v>195.4576</v>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
@@ -2905,7 +2905,7 @@
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:40</t>
+          <t>2026-05-27 14:58:31</t>
         </is>
       </c>
     </row>
@@ -2920,28 +2920,28 @@
         <v>3</v>
       </c>
       <c r="D42" t="n">
-        <v>5</v>
+        <v>44</v>
       </c>
       <c r="E42" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="F42" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="G42" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="H42" t="n">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="I42" t="n">
-        <v>142</v>
+        <v>188</v>
       </c>
       <c r="J42" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K42" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L42" t="n">
         <v>4</v>
@@ -2950,13 +2950,13 @@
         <v>2</v>
       </c>
       <c r="N42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O42" t="n">
-        <v>14.5052</v>
+        <v>15.7175</v>
       </c>
       <c r="P42" t="n">
-        <v>194.7229</v>
+        <v>195.3938</v>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
@@ -2965,7 +2965,7 @@
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:40</t>
+          <t>2026-05-27 14:58:31</t>
         </is>
       </c>
     </row>
@@ -2977,10 +2977,10 @@
         <v>1</v>
       </c>
       <c r="C43" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D43" t="n">
-        <v>43</v>
+        <v>3</v>
       </c>
       <c r="E43" t="n">
         <v>44</v>
@@ -2992,31 +2992,31 @@
         <v>49</v>
       </c>
       <c r="H43" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="I43" t="n">
-        <v>188</v>
+        <v>145</v>
       </c>
       <c r="J43" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K43" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L43" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M43" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N43" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O43" t="n">
-        <v>14.2352</v>
+        <v>15.7175</v>
       </c>
       <c r="P43" t="n">
-        <v>194.1079</v>
+        <v>195.3938</v>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
@@ -3025,7 +3025,7 @@
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:40</t>
+          <t>2026-05-27 14:58:31</t>
         </is>
       </c>
     </row>
@@ -3034,13 +3034,13 @@
         <v>43</v>
       </c>
       <c r="B44" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C44" t="n">
         <v>5</v>
       </c>
       <c r="D44" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E44" t="n">
         <v>44</v>
@@ -3052,10 +3052,10 @@
         <v>49</v>
       </c>
       <c r="H44" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="I44" t="n">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="J44" t="n">
         <v>3</v>
@@ -3064,19 +3064,19 @@
         <v>3</v>
       </c>
       <c r="L44" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M44" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N44" t="n">
         <v>0</v>
       </c>
       <c r="O44" t="n">
-        <v>12.4483</v>
+        <v>12.7216</v>
       </c>
       <c r="P44" t="n">
-        <v>193.3807</v>
+        <v>195.0841</v>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
@@ -3085,7 +3085,7 @@
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:40</t>
+          <t>2026-05-27 14:58:31</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
         <v>5</v>
       </c>
       <c r="E45" t="n">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F45" t="n">
         <v>44</v>
@@ -3112,10 +3112,10 @@
         <v>46</v>
       </c>
       <c r="H45" t="n">
-        <v>41</v>
+        <v>29</v>
       </c>
       <c r="I45" t="n">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="J45" t="n">
         <v>3</v>
@@ -3124,19 +3124,19 @@
         <v>3</v>
       </c>
       <c r="L45" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M45" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O45" t="n">
-        <v>12.0996</v>
+        <v>14.5052</v>
       </c>
       <c r="P45" t="n">
-        <v>193.109</v>
+        <v>194.8229</v>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
@@ -3145,7 +3145,7 @@
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:40</t>
+          <t>2026-05-27 14:58:31</t>
         </is>
       </c>
     </row>
@@ -3157,13 +3157,13 @@
         <v>1</v>
       </c>
       <c r="C46" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D46" t="n">
-        <v>5</v>
+        <v>43</v>
       </c>
       <c r="E46" t="n">
-        <v>12</v>
+        <v>44</v>
       </c>
       <c r="F46" t="n">
         <v>46</v>
@@ -3172,16 +3172,16 @@
         <v>49</v>
       </c>
       <c r="H46" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="I46" t="n">
-        <v>116</v>
+        <v>188</v>
       </c>
       <c r="J46" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K46" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L46" t="n">
         <v>4</v>
@@ -3190,13 +3190,13 @@
         <v>2</v>
       </c>
       <c r="N46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O46" t="n">
-        <v>12.3386</v>
+        <v>14.2352</v>
       </c>
       <c r="P46" t="n">
-        <v>193.0464</v>
+        <v>194.2079</v>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
@@ -3205,7 +3205,7 @@
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:40</t>
+          <t>2026-05-27 14:58:31</t>
         </is>
       </c>
     </row>
@@ -3214,34 +3214,34 @@
         <v>46</v>
       </c>
       <c r="B47" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C47" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D47" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E47" t="n">
-        <v>10</v>
+        <v>44</v>
       </c>
       <c r="F47" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="G47" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="H47" t="n">
-        <v>41</v>
+        <v>29</v>
       </c>
       <c r="I47" t="n">
-        <v>109</v>
+        <v>157</v>
       </c>
       <c r="J47" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K47" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L47" t="n">
         <v>3</v>
@@ -3253,10 +3253,10 @@
         <v>0</v>
       </c>
       <c r="O47" t="n">
-        <v>12.5539</v>
+        <v>12.4483</v>
       </c>
       <c r="P47" t="n">
-        <v>192.9247</v>
+        <v>193.6207</v>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
@@ -3265,7 +3265,7 @@
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:40</t>
+          <t>2026-05-27 14:58:31</t>
         </is>
       </c>
     </row>
@@ -3280,43 +3280,43 @@
         <v>3</v>
       </c>
       <c r="D48" t="n">
-        <v>37</v>
+        <v>5</v>
       </c>
       <c r="E48" t="n">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="F48" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="G48" t="n">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="H48" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="I48" t="n">
-        <v>180</v>
+        <v>137</v>
       </c>
       <c r="J48" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K48" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L48" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M48" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N48" t="n">
         <v>0</v>
       </c>
       <c r="O48" t="n">
-        <v>12.3386</v>
+        <v>12.0996</v>
       </c>
       <c r="P48" t="n">
-        <v>192.6864</v>
+        <v>193.309</v>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
@@ -3325,7 +3325,7 @@
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:40</t>
+          <t>2026-05-27 14:58:31</t>
         </is>
       </c>
     </row>
@@ -3343,19 +3343,19 @@
         <v>5</v>
       </c>
       <c r="E49" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="F49" t="n">
         <v>44</v>
       </c>
       <c r="G49" t="n">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="H49" t="n">
-        <v>41</v>
+        <v>21</v>
       </c>
       <c r="I49" t="n">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="J49" t="n">
         <v>2</v>
@@ -3364,19 +3364,19 @@
         <v>4</v>
       </c>
       <c r="L49" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M49" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N49" t="n">
         <v>0</v>
       </c>
       <c r="O49" t="n">
-        <v>10.5186</v>
+        <v>12.5539</v>
       </c>
       <c r="P49" t="n">
-        <v>192.0364</v>
+        <v>193.1647</v>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
@@ -3385,7 +3385,7 @@
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:40</t>
+          <t>2026-05-27 14:58:31</t>
         </is>
       </c>
     </row>
@@ -3403,40 +3403,40 @@
         <v>5</v>
       </c>
       <c r="E50" t="n">
-        <v>44</v>
+        <v>12</v>
       </c>
       <c r="F50" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G50" t="n">
         <v>49</v>
       </c>
       <c r="H50" t="n">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="I50" t="n">
-        <v>147</v>
+        <v>116</v>
       </c>
       <c r="J50" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K50" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L50" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M50" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O50" t="n">
-        <v>14.7323</v>
+        <v>12.3386</v>
       </c>
       <c r="P50" t="n">
-        <v>191.8707</v>
+        <v>193.1464</v>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
@@ -3445,7 +3445,7 @@
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:40</t>
+          <t>2026-05-27 14:58:31</t>
         </is>
       </c>
     </row>
@@ -3457,31 +3457,31 @@
         <v>1</v>
       </c>
       <c r="C51" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D51" t="n">
-        <v>5</v>
+        <v>39</v>
       </c>
       <c r="E51" t="n">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="F51" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="G51" t="n">
         <v>49</v>
       </c>
       <c r="H51" t="n">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="I51" t="n">
-        <v>136</v>
+        <v>184</v>
       </c>
       <c r="J51" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K51" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L51" t="n">
         <v>4</v>
@@ -3493,10 +3493,10 @@
         <v>0</v>
       </c>
       <c r="O51" t="n">
-        <v>10.1311</v>
+        <v>12.2409</v>
       </c>
       <c r="P51" t="n">
-        <v>191.5679</v>
+        <v>193.0223</v>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
@@ -3505,7 +3505,7 @@
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:40</t>
+          <t>2026-05-27 14:58:31</t>
         </is>
       </c>
     </row>
@@ -3520,28 +3520,28 @@
         <v>3</v>
       </c>
       <c r="D52" t="n">
-        <v>5</v>
+        <v>37</v>
       </c>
       <c r="E52" t="n">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="F52" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="G52" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="H52" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="I52" t="n">
-        <v>136</v>
+        <v>180</v>
       </c>
       <c r="J52" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K52" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L52" t="n">
         <v>4</v>
@@ -3553,10 +3553,10 @@
         <v>0</v>
       </c>
       <c r="O52" t="n">
-        <v>11.6619</v>
+        <v>12.3386</v>
       </c>
       <c r="P52" t="n">
-        <v>190.2548</v>
+        <v>192.6864</v>
       </c>
       <c r="Q52" t="inlineStr">
         <is>
@@ -3565,7 +3565,7 @@
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:40</t>
+          <t>2026-05-27 14:58:31</t>
         </is>
       </c>
     </row>
@@ -3577,10 +3577,10 @@
         <v>1</v>
       </c>
       <c r="C53" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D53" t="n">
-        <v>31</v>
+        <v>10</v>
       </c>
       <c r="E53" t="n">
         <v>44</v>
@@ -3592,31 +3592,31 @@
         <v>49</v>
       </c>
       <c r="H53" t="n">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="I53" t="n">
-        <v>174</v>
+        <v>155</v>
       </c>
       <c r="J53" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K53" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L53" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M53" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N53" t="n">
         <v>0</v>
       </c>
       <c r="O53" t="n">
-        <v>10.0916</v>
+        <v>12.2409</v>
       </c>
       <c r="P53" t="n">
-        <v>189.549</v>
+        <v>192.2823</v>
       </c>
       <c r="Q53" t="inlineStr">
         <is>
@@ -3625,7 +3625,7 @@
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:40</t>
+          <t>2026-05-27 14:58:31</t>
         </is>
       </c>
     </row>
@@ -3643,40 +3643,40 @@
         <v>5</v>
       </c>
       <c r="E54" t="n">
-        <v>36</v>
+        <v>14</v>
       </c>
       <c r="F54" t="n">
         <v>44</v>
       </c>
       <c r="G54" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="H54" t="n">
-        <v>10</v>
+        <v>48</v>
       </c>
       <c r="I54" t="n">
-        <v>135</v>
+        <v>116</v>
       </c>
       <c r="J54" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K54" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L54" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M54" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N54" t="n">
         <v>0</v>
       </c>
       <c r="O54" t="n">
-        <v>11.2428</v>
+        <v>10.5186</v>
       </c>
       <c r="P54" t="n">
-        <v>188.5469</v>
+        <v>192.1364</v>
       </c>
       <c r="Q54" t="inlineStr">
         <is>
@@ -3685,7 +3685,7 @@
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:40</t>
+          <t>2026-05-27 14:58:31</t>
         </is>
       </c>
     </row>
@@ -3703,19 +3703,19 @@
         <v>5</v>
       </c>
       <c r="E55" t="n">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="F55" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G55" t="n">
         <v>49</v>
       </c>
       <c r="H55" t="n">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="I55" t="n">
-        <v>136</v>
+        <v>147</v>
       </c>
       <c r="J55" t="n">
         <v>3</v>
@@ -3724,19 +3724,19 @@
         <v>3</v>
       </c>
       <c r="L55" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M55" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O55" t="n">
-        <v>9.8102</v>
+        <v>14.7323</v>
       </c>
       <c r="P55" t="n">
-        <v>188.5255</v>
+        <v>191.9707</v>
       </c>
       <c r="Q55" t="inlineStr">
         <is>
@@ -3745,7 +3745,7 @@
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:40</t>
+          <t>2026-05-27 14:58:31</t>
         </is>
       </c>
     </row>
@@ -3760,28 +3760,28 @@
         <v>3</v>
       </c>
       <c r="D56" t="n">
-        <v>33</v>
+        <v>5</v>
       </c>
       <c r="E56" t="n">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="F56" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="G56" t="n">
         <v>49</v>
       </c>
       <c r="H56" t="n">
-        <v>41</v>
+        <v>29</v>
       </c>
       <c r="I56" t="n">
-        <v>176</v>
+        <v>136</v>
       </c>
       <c r="J56" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K56" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L56" t="n">
         <v>4</v>
@@ -3793,10 +3793,10 @@
         <v>0</v>
       </c>
       <c r="O56" t="n">
-        <v>10.7443</v>
+        <v>10.1311</v>
       </c>
       <c r="P56" t="n">
-        <v>188.2808</v>
+        <v>191.6679</v>
       </c>
       <c r="Q56" t="inlineStr">
         <is>
@@ -3805,7 +3805,7 @@
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:40</t>
+          <t>2026-05-27 14:58:31</t>
         </is>
       </c>
     </row>
@@ -3814,34 +3814,34 @@
         <v>56</v>
       </c>
       <c r="B57" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C57" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D57" t="n">
-        <v>44</v>
+        <v>5</v>
       </c>
       <c r="E57" t="n">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="F57" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="G57" t="n">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="H57" t="n">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="I57" t="n">
-        <v>192</v>
+        <v>136</v>
       </c>
       <c r="J57" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K57" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L57" t="n">
         <v>4</v>
@@ -3850,13 +3850,13 @@
         <v>2</v>
       </c>
       <c r="N57" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O57" t="n">
-        <v>14.9184</v>
+        <v>11.6619</v>
       </c>
       <c r="P57" t="n">
-        <v>187.4961</v>
+        <v>190.3548</v>
       </c>
       <c r="Q57" t="inlineStr">
         <is>
@@ -3865,7 +3865,7 @@
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:40</t>
+          <t>2026-05-27 14:58:31</t>
         </is>
       </c>
     </row>
@@ -3880,10 +3880,10 @@
         <v>3</v>
       </c>
       <c r="D58" t="n">
-        <v>5</v>
+        <v>31</v>
       </c>
       <c r="E58" t="n">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="F58" t="n">
         <v>46</v>
@@ -3892,31 +3892,31 @@
         <v>49</v>
       </c>
       <c r="H58" t="n">
-        <v>41</v>
+        <v>21</v>
       </c>
       <c r="I58" t="n">
-        <v>143</v>
+        <v>174</v>
       </c>
       <c r="J58" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K58" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L58" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M58" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N58" t="n">
         <v>0</v>
       </c>
       <c r="O58" t="n">
-        <v>12.3386</v>
+        <v>10.0916</v>
       </c>
       <c r="P58" t="n">
-        <v>187.4264</v>
+        <v>189.649</v>
       </c>
       <c r="Q58" t="inlineStr">
         <is>
@@ -3925,7 +3925,7 @@
       </c>
       <c r="R58" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:40</t>
+          <t>2026-05-27 14:58:31</t>
         </is>
       </c>
     </row>
@@ -3943,7 +3943,7 @@
         <v>5</v>
       </c>
       <c r="E59" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F59" t="n">
         <v>44</v>
@@ -3952,10 +3952,10 @@
         <v>46</v>
       </c>
       <c r="H59" t="n">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="I59" t="n">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="J59" t="n">
         <v>3</v>
@@ -3964,19 +3964,19 @@
         <v>3</v>
       </c>
       <c r="L59" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M59" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N59" t="n">
         <v>0</v>
       </c>
       <c r="O59" t="n">
-        <v>10.8444</v>
+        <v>11.2428</v>
       </c>
       <c r="P59" t="n">
-        <v>187.3909</v>
+        <v>188.8869</v>
       </c>
       <c r="Q59" t="inlineStr">
         <is>
@@ -3985,7 +3985,7 @@
       </c>
       <c r="R59" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:40</t>
+          <t>2026-05-27 14:58:31</t>
         </is>
       </c>
     </row>
@@ -4003,40 +4003,40 @@
         <v>5</v>
       </c>
       <c r="E60" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="F60" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="G60" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="H60" t="n">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="I60" t="n">
-        <v>123</v>
+        <v>136</v>
       </c>
       <c r="J60" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K60" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L60" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M60" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N60" t="n">
         <v>0</v>
       </c>
       <c r="O60" t="n">
-        <v>8.579000000000001</v>
+        <v>9.8102</v>
       </c>
       <c r="P60" t="n">
-        <v>186.4476</v>
+        <v>188.6255</v>
       </c>
       <c r="Q60" t="inlineStr">
         <is>
@@ -4045,7 +4045,7 @@
       </c>
       <c r="R60" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:40</t>
+          <t>2026-05-27 14:58:31</t>
         </is>
       </c>
     </row>
@@ -4060,7 +4060,7 @@
         <v>3</v>
       </c>
       <c r="D61" t="n">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="E61" t="n">
         <v>44</v>
@@ -4072,16 +4072,16 @@
         <v>49</v>
       </c>
       <c r="H61" t="n">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="I61" t="n">
-        <v>164</v>
+        <v>176</v>
       </c>
       <c r="J61" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K61" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L61" t="n">
         <v>4</v>
@@ -4093,10 +4093,10 @@
         <v>0</v>
       </c>
       <c r="O61" t="n">
-        <v>9.0465</v>
+        <v>10.7443</v>
       </c>
       <c r="P61" t="n">
-        <v>185.5164</v>
+        <v>188.2808</v>
       </c>
       <c r="Q61" t="inlineStr">
         <is>
@@ -4105,7 +4105,7 @@
       </c>
       <c r="R61" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:40</t>
+          <t>2026-05-27 14:58:31</t>
         </is>
       </c>
     </row>
@@ -4114,34 +4114,34 @@
         <v>61</v>
       </c>
       <c r="B62" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C62" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D62" t="n">
-        <v>5</v>
+        <v>44</v>
       </c>
       <c r="E62" t="n">
-        <v>21</v>
+        <v>45</v>
       </c>
       <c r="F62" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="G62" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="H62" t="n">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="I62" t="n">
-        <v>120</v>
+        <v>192</v>
       </c>
       <c r="J62" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K62" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L62" t="n">
         <v>4</v>
@@ -4150,13 +4150,13 @@
         <v>2</v>
       </c>
       <c r="N62" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O62" t="n">
-        <v>8.8544</v>
+        <v>14.9184</v>
       </c>
       <c r="P62" t="n">
-        <v>184.6559</v>
+        <v>187.5961</v>
       </c>
       <c r="Q62" t="inlineStr">
         <is>
@@ -4165,7 +4165,7 @@
       </c>
       <c r="R62" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:40</t>
+          <t>2026-05-27 14:58:31</t>
         </is>
       </c>
     </row>
@@ -4174,16 +4174,16 @@
         <v>62</v>
       </c>
       <c r="B63" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C63" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D63" t="n">
-        <v>28</v>
+        <v>5</v>
       </c>
       <c r="E63" t="n">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="F63" t="n">
         <v>46</v>
@@ -4192,31 +4192,31 @@
         <v>49</v>
       </c>
       <c r="H63" t="n">
-        <v>41</v>
+        <v>18</v>
       </c>
       <c r="I63" t="n">
-        <v>175</v>
+        <v>143</v>
       </c>
       <c r="J63" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K63" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L63" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M63" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N63" t="n">
         <v>0</v>
       </c>
       <c r="O63" t="n">
-        <v>8.704000000000001</v>
+        <v>12.3386</v>
       </c>
       <c r="P63" t="n">
-        <v>184.5001</v>
+        <v>187.5264</v>
       </c>
       <c r="Q63" t="inlineStr">
         <is>
@@ -4225,7 +4225,7 @@
       </c>
       <c r="R63" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:40</t>
+          <t>2026-05-27 14:58:31</t>
         </is>
       </c>
     </row>
@@ -4237,46 +4237,46 @@
         <v>1</v>
       </c>
       <c r="C64" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D64" t="n">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="E64" t="n">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="F64" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="G64" t="n">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="H64" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I64" t="n">
-        <v>175</v>
+        <v>134</v>
       </c>
       <c r="J64" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K64" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L64" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M64" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N64" t="n">
         <v>0</v>
       </c>
       <c r="O64" t="n">
-        <v>8.822699999999999</v>
+        <v>10.8444</v>
       </c>
       <c r="P64" t="n">
-        <v>184.1567</v>
+        <v>187.4909</v>
       </c>
       <c r="Q64" t="inlineStr">
         <is>
@@ -4285,7 +4285,7 @@
       </c>
       <c r="R64" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:40</t>
+          <t>2026-05-27 14:58:31</t>
         </is>
       </c>
     </row>
@@ -4303,7 +4303,7 @@
         <v>5</v>
       </c>
       <c r="E65" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="F65" t="n">
         <v>44</v>
@@ -4312,16 +4312,16 @@
         <v>46</v>
       </c>
       <c r="H65" t="n">
-        <v>49</v>
+        <v>12</v>
       </c>
       <c r="I65" t="n">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="J65" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K65" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L65" t="n">
         <v>3</v>
@@ -4333,10 +4333,10 @@
         <v>0</v>
       </c>
       <c r="O65" t="n">
-        <v>8.8544</v>
+        <v>8.579000000000001</v>
       </c>
       <c r="P65" t="n">
-        <v>184.0359</v>
+        <v>186.6876</v>
       </c>
       <c r="Q65" t="inlineStr">
         <is>
@@ -4345,7 +4345,7 @@
       </c>
       <c r="R65" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:40</t>
+          <t>2026-05-27 14:58:31</t>
         </is>
       </c>
     </row>
@@ -4354,7 +4354,7 @@
         <v>65</v>
       </c>
       <c r="B66" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C66" t="n">
         <v>5</v>
@@ -4372,10 +4372,10 @@
         <v>49</v>
       </c>
       <c r="H66" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="I66" t="n">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="J66" t="n">
         <v>3</v>
@@ -4393,10 +4393,10 @@
         <v>0</v>
       </c>
       <c r="O66" t="n">
-        <v>8.4048</v>
+        <v>8.704000000000001</v>
       </c>
       <c r="P66" t="n">
-        <v>183.5119</v>
+        <v>185.1401</v>
       </c>
       <c r="Q66" t="inlineStr">
         <is>
@@ -4405,7 +4405,7 @@
       </c>
       <c r="R66" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:40</t>
+          <t>2026-05-27 14:58:31</t>
         </is>
       </c>
     </row>
@@ -4423,7 +4423,7 @@
         <v>5</v>
       </c>
       <c r="E67" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="F67" t="n">
         <v>44</v>
@@ -4432,16 +4432,16 @@
         <v>46</v>
       </c>
       <c r="H67" t="n">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="I67" t="n">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="J67" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K67" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L67" t="n">
         <v>4</v>
@@ -4453,10 +4453,10 @@
         <v>0</v>
       </c>
       <c r="O67" t="n">
-        <v>8.7178</v>
+        <v>8.8544</v>
       </c>
       <c r="P67" t="n">
-        <v>181.7945</v>
+        <v>184.7559</v>
       </c>
       <c r="Q67" t="inlineStr">
         <is>
@@ -4465,7 +4465,7 @@
       </c>
       <c r="R67" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:40</t>
+          <t>2026-05-27 14:58:31</t>
         </is>
       </c>
     </row>
@@ -4474,13 +4474,13 @@
         <v>67</v>
       </c>
       <c r="B68" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C68" t="n">
         <v>5</v>
       </c>
       <c r="D68" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="E68" t="n">
         <v>44</v>
@@ -4492,10 +4492,10 @@
         <v>49</v>
       </c>
       <c r="H68" t="n">
-        <v>15</v>
+        <v>45</v>
       </c>
       <c r="I68" t="n">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="J68" t="n">
         <v>4</v>
@@ -4504,19 +4504,19 @@
         <v>2</v>
       </c>
       <c r="L68" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M68" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N68" t="n">
         <v>0</v>
       </c>
       <c r="O68" t="n">
-        <v>8.1142</v>
+        <v>8.704000000000001</v>
       </c>
       <c r="P68" t="n">
-        <v>181.6855</v>
+        <v>184.6001</v>
       </c>
       <c r="Q68" t="inlineStr">
         <is>
@@ -4525,7 +4525,7 @@
       </c>
       <c r="R68" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:40</t>
+          <t>2026-05-27 14:58:31</t>
         </is>
       </c>
     </row>
@@ -4537,13 +4537,13 @@
         <v>1</v>
       </c>
       <c r="C69" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D69" t="n">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="E69" t="n">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="F69" t="n">
         <v>46</v>
@@ -4552,31 +4552,31 @@
         <v>49</v>
       </c>
       <c r="H69" t="n">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="I69" t="n">
-        <v>135</v>
+        <v>175</v>
       </c>
       <c r="J69" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K69" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L69" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M69" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N69" t="n">
         <v>0</v>
       </c>
       <c r="O69" t="n">
-        <v>9.5624</v>
+        <v>8.822699999999999</v>
       </c>
       <c r="P69" t="n">
-        <v>181.5261</v>
+        <v>184.2567</v>
       </c>
       <c r="Q69" t="inlineStr">
         <is>
@@ -4585,7 +4585,7 @@
       </c>
       <c r="R69" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:40</t>
+          <t>2026-05-27 14:58:31</t>
         </is>
       </c>
     </row>
@@ -4597,46 +4597,46 @@
         <v>1</v>
       </c>
       <c r="C70" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D70" t="n">
-        <v>27</v>
+        <v>5</v>
       </c>
       <c r="E70" t="n">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="F70" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="G70" t="n">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="H70" t="n">
-        <v>24</v>
+        <v>49</v>
       </c>
       <c r="I70" t="n">
-        <v>172</v>
+        <v>127</v>
       </c>
       <c r="J70" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K70" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L70" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M70" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N70" t="n">
         <v>0</v>
       </c>
       <c r="O70" t="n">
-        <v>8.2608</v>
+        <v>8.8544</v>
       </c>
       <c r="P70" t="n">
-        <v>180.4719</v>
+        <v>184.1359</v>
       </c>
       <c r="Q70" t="inlineStr">
         <is>
@@ -4645,7 +4645,7 @@
       </c>
       <c r="R70" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:40</t>
+          <t>2026-05-27 14:58:31</t>
         </is>
       </c>
     </row>
@@ -4657,55 +4657,295 @@
         <v>1</v>
       </c>
       <c r="C71" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D71" t="n">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="E71" t="n">
+        <v>44</v>
+      </c>
+      <c r="F71" t="n">
+        <v>46</v>
+      </c>
+      <c r="G71" t="n">
+        <v>49</v>
+      </c>
+      <c r="H71" t="n">
+        <v>39</v>
+      </c>
+      <c r="I71" t="n">
+        <v>166</v>
+      </c>
+      <c r="J71" t="n">
+        <v>3</v>
+      </c>
+      <c r="K71" t="n">
+        <v>3</v>
+      </c>
+      <c r="L71" t="n">
+        <v>4</v>
+      </c>
+      <c r="M71" t="n">
+        <v>2</v>
+      </c>
+      <c r="N71" t="n">
+        <v>0</v>
+      </c>
+      <c r="O71" t="n">
+        <v>8.4048</v>
+      </c>
+      <c r="P71" t="n">
+        <v>183.6119</v>
+      </c>
+      <c r="Q71" t="inlineStr">
+        <is>
+          <t>UK49sGeneticOptimizer_v1</t>
+        </is>
+      </c>
+      <c r="R71" t="inlineStr">
+        <is>
+          <t>2026-05-27 14:58:31</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>71</v>
+      </c>
+      <c r="B72" t="n">
+        <v>1</v>
+      </c>
+      <c r="C72" t="n">
+        <v>3</v>
+      </c>
+      <c r="D72" t="n">
+        <v>5</v>
+      </c>
+      <c r="E72" t="n">
+        <v>27</v>
+      </c>
+      <c r="F72" t="n">
+        <v>44</v>
+      </c>
+      <c r="G72" t="n">
+        <v>46</v>
+      </c>
+      <c r="H72" t="n">
+        <v>25</v>
+      </c>
+      <c r="I72" t="n">
+        <v>126</v>
+      </c>
+      <c r="J72" t="n">
+        <v>3</v>
+      </c>
+      <c r="K72" t="n">
+        <v>3</v>
+      </c>
+      <c r="L72" t="n">
+        <v>4</v>
+      </c>
+      <c r="M72" t="n">
+        <v>2</v>
+      </c>
+      <c r="N72" t="n">
+        <v>0</v>
+      </c>
+      <c r="O72" t="n">
+        <v>8.7178</v>
+      </c>
+      <c r="P72" t="n">
+        <v>181.8945</v>
+      </c>
+      <c r="Q72" t="inlineStr">
+        <is>
+          <t>UK49sGeneticOptimizer_v1</t>
+        </is>
+      </c>
+      <c r="R72" t="inlineStr">
+        <is>
+          <t>2026-05-27 14:58:31</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>72</v>
+      </c>
+      <c r="B73" t="n">
+        <v>1</v>
+      </c>
+      <c r="C73" t="n">
+        <v>5</v>
+      </c>
+      <c r="D73" t="n">
+        <v>25</v>
+      </c>
+      <c r="E73" t="n">
+        <v>44</v>
+      </c>
+      <c r="F73" t="n">
+        <v>46</v>
+      </c>
+      <c r="G73" t="n">
+        <v>49</v>
+      </c>
+      <c r="H73" t="n">
+        <v>29</v>
+      </c>
+      <c r="I73" t="n">
+        <v>170</v>
+      </c>
+      <c r="J73" t="n">
+        <v>4</v>
+      </c>
+      <c r="K73" t="n">
+        <v>2</v>
+      </c>
+      <c r="L73" t="n">
+        <v>4</v>
+      </c>
+      <c r="M73" t="n">
+        <v>2</v>
+      </c>
+      <c r="N73" t="n">
+        <v>0</v>
+      </c>
+      <c r="O73" t="n">
+        <v>8.1142</v>
+      </c>
+      <c r="P73" t="n">
+        <v>181.7855</v>
+      </c>
+      <c r="Q73" t="inlineStr">
+        <is>
+          <t>UK49sGeneticOptimizer_v1</t>
+        </is>
+      </c>
+      <c r="R73" t="inlineStr">
+        <is>
+          <t>2026-05-27 14:58:31</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>73</v>
+      </c>
+      <c r="B74" t="n">
+        <v>1</v>
+      </c>
+      <c r="C74" t="n">
+        <v>5</v>
+      </c>
+      <c r="D74" t="n">
+        <v>27</v>
+      </c>
+      <c r="E74" t="n">
+        <v>44</v>
+      </c>
+      <c r="F74" t="n">
+        <v>46</v>
+      </c>
+      <c r="G74" t="n">
+        <v>49</v>
+      </c>
+      <c r="H74" t="n">
+        <v>24</v>
+      </c>
+      <c r="I74" t="n">
+        <v>172</v>
+      </c>
+      <c r="J74" t="n">
+        <v>4</v>
+      </c>
+      <c r="K74" t="n">
+        <v>2</v>
+      </c>
+      <c r="L74" t="n">
+        <v>4</v>
+      </c>
+      <c r="M74" t="n">
+        <v>2</v>
+      </c>
+      <c r="N74" t="n">
+        <v>0</v>
+      </c>
+      <c r="O74" t="n">
+        <v>8.2608</v>
+      </c>
+      <c r="P74" t="n">
+        <v>180.5719</v>
+      </c>
+      <c r="Q74" t="inlineStr">
+        <is>
+          <t>UK49sGeneticOptimizer_v1</t>
+        </is>
+      </c>
+      <c r="R74" t="inlineStr">
+        <is>
+          <t>2026-05-27 14:58:31</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>74</v>
+      </c>
+      <c r="B75" t="n">
+        <v>1</v>
+      </c>
+      <c r="C75" t="n">
+        <v>3</v>
+      </c>
+      <c r="D75" t="n">
+        <v>5</v>
+      </c>
+      <c r="E75" t="n">
         <v>23</v>
       </c>
-      <c r="F71" t="n">
-        <v>46</v>
-      </c>
-      <c r="G71" t="n">
-        <v>49</v>
-      </c>
-      <c r="H71" t="n">
-        <v>25</v>
-      </c>
-      <c r="I71" t="n">
+      <c r="F75" t="n">
+        <v>46</v>
+      </c>
+      <c r="G75" t="n">
+        <v>49</v>
+      </c>
+      <c r="H75" t="n">
+        <v>34</v>
+      </c>
+      <c r="I75" t="n">
         <v>127</v>
       </c>
-      <c r="J71" t="n">
-        <v>2</v>
-      </c>
-      <c r="K71" t="n">
-        <v>4</v>
-      </c>
-      <c r="L71" t="n">
-        <v>5</v>
-      </c>
-      <c r="M71" t="n">
-        <v>1</v>
-      </c>
-      <c r="N71" t="n">
-        <v>0</v>
-      </c>
-      <c r="O71" t="n">
+      <c r="J75" t="n">
+        <v>2</v>
+      </c>
+      <c r="K75" t="n">
+        <v>4</v>
+      </c>
+      <c r="L75" t="n">
+        <v>5</v>
+      </c>
+      <c r="M75" t="n">
+        <v>1</v>
+      </c>
+      <c r="N75" t="n">
+        <v>0</v>
+      </c>
+      <c r="O75" t="n">
         <v>9.0465</v>
       </c>
-      <c r="P71" t="n">
-        <v>178.1364</v>
-      </c>
-      <c r="Q71" t="inlineStr">
-        <is>
-          <t>UK49sGeneticOptimizer_v1</t>
-        </is>
-      </c>
-      <c r="R71" t="inlineStr">
-        <is>
-          <t>2026-05-26 14:23:40</t>
+      <c r="P75" t="n">
+        <v>178.3364</v>
+      </c>
+      <c r="Q75" t="inlineStr">
+        <is>
+          <t>UK49sGeneticOptimizer_v1</t>
+        </is>
+      </c>
+      <c r="R75" t="inlineStr">
+        <is>
+          <t>2026-05-27 14:58:31</t>
         </is>
       </c>
     </row>
@@ -4748,7 +4988,7 @@
         <v>187.9364</v>
       </c>
       <c r="C2" t="n">
-        <v>163.7456</v>
+        <v>163.9126</v>
       </c>
     </row>
     <row r="3">
@@ -4756,10 +4996,10 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>188.7857</v>
+        <v>190.279</v>
       </c>
       <c r="C3" t="n">
-        <v>171.2047</v>
+        <v>173.0252</v>
       </c>
     </row>
     <row r="4">
@@ -4767,10 +5007,10 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>194.0009</v>
+        <v>195.2433</v>
       </c>
       <c r="C4" t="n">
-        <v>177.2654</v>
+        <v>177.8129</v>
       </c>
     </row>
     <row r="5">
@@ -4778,10 +5018,10 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>196.1534</v>
+        <v>198.0129</v>
       </c>
       <c r="C5" t="n">
-        <v>183.3124</v>
+        <v>183.5204</v>
       </c>
     </row>
     <row r="6">
@@ -4789,10 +5029,10 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>197.5781</v>
+        <v>199.4529</v>
       </c>
       <c r="C6" t="n">
-        <v>186.0474</v>
+        <v>187.1388</v>
       </c>
     </row>
     <row r="7">
@@ -4800,10 +5040,10 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>199.3828</v>
+        <v>201.2628</v>
       </c>
       <c r="C7" t="n">
-        <v>187.6509</v>
+        <v>188.0443</v>
       </c>
     </row>
     <row r="8">
@@ -4811,10 +5051,10 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>200.073</v>
+        <v>201.2628</v>
       </c>
       <c r="C8" t="n">
-        <v>189.4962</v>
+        <v>191.3488</v>
       </c>
     </row>
     <row r="9">
@@ -4822,10 +5062,10 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>200.7228</v>
+        <v>201.2628</v>
       </c>
       <c r="C9" t="n">
-        <v>193.3432</v>
+        <v>195.9746</v>
       </c>
     </row>
     <row r="10">
@@ -4833,10 +5073,10 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>201.1628</v>
+        <v>201.2628</v>
       </c>
       <c r="C10" t="n">
-        <v>195.8227</v>
+        <v>198.8773</v>
       </c>
     </row>
     <row r="11">
@@ -4844,10 +5084,10 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>201.1628</v>
+        <v>201.2628</v>
       </c>
       <c r="C11" t="n">
-        <v>195.7128</v>
+        <v>199.6751</v>
       </c>
     </row>
     <row r="12">
@@ -4855,10 +5095,10 @@
         <v>11</v>
       </c>
       <c r="B12" t="n">
-        <v>201.1628</v>
+        <v>201.2628</v>
       </c>
       <c r="C12" t="n">
-        <v>197.9913</v>
+        <v>199.0778</v>
       </c>
     </row>
     <row r="13">
@@ -4866,10 +5106,10 @@
         <v>12</v>
       </c>
       <c r="B13" t="n">
-        <v>201.1628</v>
+        <v>201.2628</v>
       </c>
       <c r="C13" t="n">
-        <v>198.2188</v>
+        <v>199.0502</v>
       </c>
     </row>
     <row r="14">
@@ -4877,10 +5117,10 @@
         <v>13</v>
       </c>
       <c r="B14" t="n">
-        <v>201.1628</v>
+        <v>201.2628</v>
       </c>
       <c r="C14" t="n">
-        <v>198.5954</v>
+        <v>198.9393</v>
       </c>
     </row>
     <row r="15">
@@ -4888,10 +5128,10 @@
         <v>14</v>
       </c>
       <c r="B15" t="n">
-        <v>201.1628</v>
+        <v>201.2628</v>
       </c>
       <c r="C15" t="n">
-        <v>199.6283</v>
+        <v>199.586</v>
       </c>
     </row>
     <row r="16">
@@ -4899,10 +5139,10 @@
         <v>15</v>
       </c>
       <c r="B16" t="n">
-        <v>201.1628</v>
+        <v>201.2628</v>
       </c>
       <c r="C16" t="n">
-        <v>199.2441</v>
+        <v>199.5192</v>
       </c>
     </row>
     <row r="17">
@@ -4910,10 +5150,10 @@
         <v>16</v>
       </c>
       <c r="B17" t="n">
-        <v>201.1628</v>
+        <v>201.2628</v>
       </c>
       <c r="C17" t="n">
-        <v>199.5706</v>
+        <v>199.4018</v>
       </c>
     </row>
     <row r="18">
@@ -4921,10 +5161,10 @@
         <v>17</v>
       </c>
       <c r="B18" t="n">
-        <v>201.1628</v>
+        <v>201.2628</v>
       </c>
       <c r="C18" t="n">
-        <v>199.4644</v>
+        <v>199.7751</v>
       </c>
     </row>
     <row r="19">
@@ -4932,10 +5172,10 @@
         <v>18</v>
       </c>
       <c r="B19" t="n">
-        <v>201.1628</v>
+        <v>201.2628</v>
       </c>
       <c r="C19" t="n">
-        <v>199.1622</v>
+        <v>199.2204</v>
       </c>
     </row>
     <row r="20">
@@ -4943,10 +5183,10 @@
         <v>19</v>
       </c>
       <c r="B20" t="n">
-        <v>201.1628</v>
+        <v>201.2628</v>
       </c>
       <c r="C20" t="n">
-        <v>198.9106</v>
+        <v>198.9298</v>
       </c>
     </row>
     <row r="21">
@@ -4954,10 +5194,10 @@
         <v>20</v>
       </c>
       <c r="B21" t="n">
-        <v>201.1628</v>
+        <v>201.2628</v>
       </c>
       <c r="C21" t="n">
-        <v>199.4692</v>
+        <v>199.6809</v>
       </c>
     </row>
     <row r="22">
@@ -4965,10 +5205,10 @@
         <v>21</v>
       </c>
       <c r="B22" t="n">
-        <v>201.1628</v>
+        <v>201.2628</v>
       </c>
       <c r="C22" t="n">
-        <v>199.8183</v>
+        <v>199.9409</v>
       </c>
     </row>
     <row r="23">
@@ -4976,10 +5216,10 @@
         <v>22</v>
       </c>
       <c r="B23" t="n">
-        <v>201.1628</v>
+        <v>201.2628</v>
       </c>
       <c r="C23" t="n">
-        <v>199.3764</v>
+        <v>199.3572</v>
       </c>
     </row>
     <row r="24">
@@ -4987,10 +5227,10 @@
         <v>23</v>
       </c>
       <c r="B24" t="n">
-        <v>201.1628</v>
+        <v>201.2628</v>
       </c>
       <c r="C24" t="n">
-        <v>199.4304</v>
+        <v>199.6378</v>
       </c>
     </row>
     <row r="25">
@@ -4998,10 +5238,10 @@
         <v>24</v>
       </c>
       <c r="B25" t="n">
-        <v>201.1628</v>
+        <v>201.2628</v>
       </c>
       <c r="C25" t="n">
-        <v>199.5798</v>
+        <v>199.824</v>
       </c>
     </row>
     <row r="26">
@@ -5009,10 +5249,10 @@
         <v>25</v>
       </c>
       <c r="B26" t="n">
-        <v>201.1628</v>
+        <v>201.2628</v>
       </c>
       <c r="C26" t="n">
-        <v>199.4962</v>
+        <v>199.3356</v>
       </c>
     </row>
     <row r="27">
@@ -5020,10 +5260,10 @@
         <v>26</v>
       </c>
       <c r="B27" t="n">
-        <v>201.1628</v>
+        <v>201.2628</v>
       </c>
       <c r="C27" t="n">
-        <v>199.1858</v>
+        <v>199.5197</v>
       </c>
     </row>
     <row r="28">
@@ -5031,10 +5271,10 @@
         <v>27</v>
       </c>
       <c r="B28" t="n">
-        <v>201.1628</v>
+        <v>201.2628</v>
       </c>
       <c r="C28" t="n">
-        <v>199.3979</v>
+        <v>199.5661</v>
       </c>
     </row>
     <row r="29">
@@ -5042,10 +5282,10 @@
         <v>28</v>
       </c>
       <c r="B29" t="n">
-        <v>201.1628</v>
+        <v>201.2628</v>
       </c>
       <c r="C29" t="n">
-        <v>199.6391</v>
+        <v>199.4347</v>
       </c>
     </row>
     <row r="30">
@@ -5053,10 +5293,10 @@
         <v>29</v>
       </c>
       <c r="B30" t="n">
-        <v>201.1628</v>
+        <v>201.2628</v>
       </c>
       <c r="C30" t="n">
-        <v>199.7005</v>
+        <v>199.863</v>
       </c>
     </row>
     <row r="31">
@@ -5064,10 +5304,10 @@
         <v>30</v>
       </c>
       <c r="B31" t="n">
-        <v>201.1628</v>
+        <v>201.2628</v>
       </c>
       <c r="C31" t="n">
-        <v>199.0174</v>
+        <v>199.2455</v>
       </c>
     </row>
     <row r="32">
@@ -5075,10 +5315,10 @@
         <v>31</v>
       </c>
       <c r="B32" t="n">
-        <v>201.1628</v>
+        <v>201.2628</v>
       </c>
       <c r="C32" t="n">
-        <v>199.5734</v>
+        <v>199.5549</v>
       </c>
     </row>
     <row r="33">
@@ -5086,10 +5326,10 @@
         <v>32</v>
       </c>
       <c r="B33" t="n">
-        <v>201.1628</v>
+        <v>201.2628</v>
       </c>
       <c r="C33" t="n">
-        <v>199.2483</v>
+        <v>199.3385</v>
       </c>
     </row>
     <row r="34">
@@ -5097,10 +5337,10 @@
         <v>33</v>
       </c>
       <c r="B34" t="n">
-        <v>201.1628</v>
+        <v>201.2628</v>
       </c>
       <c r="C34" t="n">
-        <v>198.8576</v>
+        <v>199.04</v>
       </c>
     </row>
     <row r="35">
@@ -5108,10 +5348,10 @@
         <v>34</v>
       </c>
       <c r="B35" t="n">
-        <v>201.1628</v>
+        <v>201.2628</v>
       </c>
       <c r="C35" t="n">
-        <v>199.6522</v>
+        <v>199.6269</v>
       </c>
     </row>
     <row r="36">
@@ -5119,10 +5359,10 @@
         <v>35</v>
       </c>
       <c r="B36" t="n">
-        <v>201.1628</v>
+        <v>201.2628</v>
       </c>
       <c r="C36" t="n">
-        <v>198.8605</v>
+        <v>199.1968</v>
       </c>
     </row>
     <row r="37">
@@ -5130,10 +5370,10 @@
         <v>36</v>
       </c>
       <c r="B37" t="n">
-        <v>201.1628</v>
+        <v>201.2628</v>
       </c>
       <c r="C37" t="n">
-        <v>198.9881</v>
+        <v>198.9083</v>
       </c>
     </row>
     <row r="38">
@@ -5141,10 +5381,10 @@
         <v>37</v>
       </c>
       <c r="B38" t="n">
-        <v>201.1628</v>
+        <v>201.2628</v>
       </c>
       <c r="C38" t="n">
-        <v>199.3896</v>
+        <v>199.4188</v>
       </c>
     </row>
     <row r="39">
@@ -5152,10 +5392,10 @@
         <v>38</v>
       </c>
       <c r="B39" t="n">
-        <v>201.1628</v>
+        <v>201.2628</v>
       </c>
       <c r="C39" t="n">
-        <v>199.2253</v>
+        <v>199.5879</v>
       </c>
     </row>
     <row r="40">
@@ -5163,10 +5403,10 @@
         <v>39</v>
       </c>
       <c r="B40" t="n">
-        <v>201.1628</v>
+        <v>201.2628</v>
       </c>
       <c r="C40" t="n">
-        <v>199.2259</v>
+        <v>199.0694</v>
       </c>
     </row>
     <row r="41">
@@ -5174,10 +5414,10 @@
         <v>40</v>
       </c>
       <c r="B41" t="n">
-        <v>201.1628</v>
+        <v>201.2628</v>
       </c>
       <c r="C41" t="n">
-        <v>199.7308</v>
+        <v>199.9921</v>
       </c>
     </row>
     <row r="42">
@@ -5185,10 +5425,10 @@
         <v>41</v>
       </c>
       <c r="B42" t="n">
-        <v>201.1628</v>
+        <v>201.2628</v>
       </c>
       <c r="C42" t="n">
-        <v>198.7973</v>
+        <v>198.8261</v>
       </c>
     </row>
     <row r="43">
@@ -5196,10 +5436,10 @@
         <v>42</v>
       </c>
       <c r="B43" t="n">
-        <v>201.1628</v>
+        <v>201.2628</v>
       </c>
       <c r="C43" t="n">
-        <v>199.3791</v>
+        <v>199.4449</v>
       </c>
     </row>
     <row r="44">
@@ -5207,10 +5447,10 @@
         <v>43</v>
       </c>
       <c r="B44" t="n">
-        <v>201.1628</v>
+        <v>201.2628</v>
       </c>
       <c r="C44" t="n">
-        <v>199.7679</v>
+        <v>200.0567</v>
       </c>
     </row>
     <row r="45">
@@ -5218,10 +5458,10 @@
         <v>44</v>
       </c>
       <c r="B45" t="n">
-        <v>201.1628</v>
+        <v>201.2628</v>
       </c>
       <c r="C45" t="n">
-        <v>199.8738</v>
+        <v>199.9009</v>
       </c>
     </row>
     <row r="46">
@@ -5229,10 +5469,10 @@
         <v>45</v>
       </c>
       <c r="B46" t="n">
-        <v>201.1628</v>
+        <v>201.2628</v>
       </c>
       <c r="C46" t="n">
-        <v>199.6577</v>
+        <v>199.5761</v>
       </c>
     </row>
     <row r="47">
@@ -5240,10 +5480,10 @@
         <v>46</v>
       </c>
       <c r="B47" t="n">
-        <v>201.1628</v>
+        <v>201.2628</v>
       </c>
       <c r="C47" t="n">
-        <v>199.1745</v>
+        <v>199.4746</v>
       </c>
     </row>
     <row r="48">
@@ -5251,10 +5491,10 @@
         <v>47</v>
       </c>
       <c r="B48" t="n">
-        <v>201.1628</v>
+        <v>201.2628</v>
       </c>
       <c r="C48" t="n">
-        <v>199.1839</v>
+        <v>199.0522</v>
       </c>
     </row>
     <row r="49">
@@ -5262,10 +5502,10 @@
         <v>48</v>
       </c>
       <c r="B49" t="n">
-        <v>201.1628</v>
+        <v>201.2628</v>
       </c>
       <c r="C49" t="n">
-        <v>198.9575</v>
+        <v>199.2388</v>
       </c>
     </row>
     <row r="50">
@@ -5273,10 +5513,10 @@
         <v>49</v>
       </c>
       <c r="B50" t="n">
-        <v>201.1628</v>
+        <v>201.2628</v>
       </c>
       <c r="C50" t="n">
-        <v>198.7833</v>
+        <v>198.8852</v>
       </c>
     </row>
     <row r="51">
@@ -5284,10 +5524,10 @@
         <v>50</v>
       </c>
       <c r="B51" t="n">
-        <v>201.1628</v>
+        <v>201.2628</v>
       </c>
       <c r="C51" t="n">
-        <v>199.5387</v>
+        <v>199.5056</v>
       </c>
     </row>
     <row r="52">
@@ -5295,10 +5535,10 @@
         <v>51</v>
       </c>
       <c r="B52" t="n">
-        <v>201.1628</v>
+        <v>201.2628</v>
       </c>
       <c r="C52" t="n">
-        <v>199.8526</v>
+        <v>200.0238</v>
       </c>
     </row>
     <row r="53">
@@ -5306,10 +5546,10 @@
         <v>52</v>
       </c>
       <c r="B53" t="n">
-        <v>201.1628</v>
+        <v>201.2628</v>
       </c>
       <c r="C53" t="n">
-        <v>199.5449</v>
+        <v>199.6758</v>
       </c>
     </row>
     <row r="54">
@@ -5317,10 +5557,10 @@
         <v>53</v>
       </c>
       <c r="B54" t="n">
-        <v>201.1628</v>
+        <v>201.2628</v>
       </c>
       <c r="C54" t="n">
-        <v>199.1031</v>
+        <v>199.2359</v>
       </c>
     </row>
     <row r="55">
@@ -5328,10 +5568,10 @@
         <v>54</v>
       </c>
       <c r="B55" t="n">
-        <v>201.1628</v>
+        <v>201.2628</v>
       </c>
       <c r="C55" t="n">
-        <v>199.2682</v>
+        <v>199.3715</v>
       </c>
     </row>
     <row r="56">
@@ -5339,10 +5579,10 @@
         <v>55</v>
       </c>
       <c r="B56" t="n">
-        <v>201.1628</v>
+        <v>201.2628</v>
       </c>
       <c r="C56" t="n">
-        <v>199.4864</v>
+        <v>199.5646</v>
       </c>
     </row>
     <row r="57">
@@ -5350,10 +5590,10 @@
         <v>56</v>
       </c>
       <c r="B57" t="n">
-        <v>201.1628</v>
+        <v>201.2628</v>
       </c>
       <c r="C57" t="n">
-        <v>199.7704</v>
+        <v>199.8436</v>
       </c>
     </row>
     <row r="58">
@@ -5361,10 +5601,10 @@
         <v>57</v>
       </c>
       <c r="B58" t="n">
-        <v>201.1628</v>
+        <v>201.2628</v>
       </c>
       <c r="C58" t="n">
-        <v>199.1121</v>
+        <v>199.2067</v>
       </c>
     </row>
     <row r="59">
@@ -5372,10 +5612,10 @@
         <v>58</v>
       </c>
       <c r="B59" t="n">
-        <v>201.1628</v>
+        <v>201.2628</v>
       </c>
       <c r="C59" t="n">
-        <v>199.2367</v>
+        <v>199.5053</v>
       </c>
     </row>
     <row r="60">
@@ -5383,10 +5623,10 @@
         <v>59</v>
       </c>
       <c r="B60" t="n">
-        <v>201.1628</v>
+        <v>201.2628</v>
       </c>
       <c r="C60" t="n">
-        <v>198.592</v>
+        <v>198.8133</v>
       </c>
     </row>
     <row r="61">
@@ -5394,10 +5634,10 @@
         <v>60</v>
       </c>
       <c r="B61" t="n">
-        <v>201.1628</v>
+        <v>201.2628</v>
       </c>
       <c r="C61" t="n">
-        <v>199.4795</v>
+        <v>199.3326</v>
       </c>
     </row>
   </sheetData>

--- a/data/exports/optimization/uk49s_genetic_optimizer_results.xlsx
+++ b/data/exports/optimization/uk49s_genetic_optimizer_results.xlsx
@@ -565,7 +565,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:31</t>
+          <t>2026-05-28 08:54:36</t>
         </is>
       </c>
     </row>
@@ -625,7 +625,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:31</t>
+          <t>2026-05-28 08:54:36</t>
         </is>
       </c>
     </row>
@@ -685,7 +685,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:31</t>
+          <t>2026-05-28 08:54:36</t>
         </is>
       </c>
     </row>
@@ -745,7 +745,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:31</t>
+          <t>2026-05-28 08:54:36</t>
         </is>
       </c>
     </row>
@@ -805,7 +805,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:31</t>
+          <t>2026-05-28 08:54:36</t>
         </is>
       </c>
     </row>
@@ -865,7 +865,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:31</t>
+          <t>2026-05-28 08:54:36</t>
         </is>
       </c>
     </row>
@@ -925,7 +925,7 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:31</t>
+          <t>2026-05-28 08:54:36</t>
         </is>
       </c>
     </row>
@@ -985,7 +985,7 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:31</t>
+          <t>2026-05-28 08:54:36</t>
         </is>
       </c>
     </row>
@@ -1045,7 +1045,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:31</t>
+          <t>2026-05-28 08:54:36</t>
         </is>
       </c>
     </row>
@@ -1105,7 +1105,7 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:31</t>
+          <t>2026-05-28 08:54:36</t>
         </is>
       </c>
     </row>
@@ -1165,7 +1165,7 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:31</t>
+          <t>2026-05-28 08:54:36</t>
         </is>
       </c>
     </row>
@@ -1225,7 +1225,7 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:31</t>
+          <t>2026-05-28 08:54:36</t>
         </is>
       </c>
     </row>
@@ -1285,7 +1285,7 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:31</t>
+          <t>2026-05-28 08:54:36</t>
         </is>
       </c>
     </row>
@@ -1345,7 +1345,7 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:31</t>
+          <t>2026-05-28 08:54:36</t>
         </is>
       </c>
     </row>
@@ -1405,7 +1405,7 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:31</t>
+          <t>2026-05-28 08:54:36</t>
         </is>
       </c>
     </row>
@@ -1465,7 +1465,7 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:31</t>
+          <t>2026-05-28 08:54:36</t>
         </is>
       </c>
     </row>
@@ -1525,7 +1525,7 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:31</t>
+          <t>2026-05-28 08:54:36</t>
         </is>
       </c>
     </row>
@@ -1585,7 +1585,7 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:31</t>
+          <t>2026-05-28 08:54:36</t>
         </is>
       </c>
     </row>
@@ -1645,7 +1645,7 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:31</t>
+          <t>2026-05-28 08:54:36</t>
         </is>
       </c>
     </row>
@@ -1705,7 +1705,7 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:31</t>
+          <t>2026-05-28 08:54:36</t>
         </is>
       </c>
     </row>
@@ -1765,7 +1765,7 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:31</t>
+          <t>2026-05-28 08:54:36</t>
         </is>
       </c>
     </row>
@@ -1825,7 +1825,7 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:31</t>
+          <t>2026-05-28 08:54:36</t>
         </is>
       </c>
     </row>
@@ -1885,7 +1885,7 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:31</t>
+          <t>2026-05-28 08:54:36</t>
         </is>
       </c>
     </row>
@@ -1945,7 +1945,7 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:31</t>
+          <t>2026-05-28 08:54:36</t>
         </is>
       </c>
     </row>
@@ -2005,7 +2005,7 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:31</t>
+          <t>2026-05-28 08:54:36</t>
         </is>
       </c>
     </row>
@@ -2065,7 +2065,7 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:31</t>
+          <t>2026-05-28 08:54:36</t>
         </is>
       </c>
     </row>
@@ -2125,7 +2125,7 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:31</t>
+          <t>2026-05-28 08:54:36</t>
         </is>
       </c>
     </row>
@@ -2185,7 +2185,7 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:31</t>
+          <t>2026-05-28 08:54:36</t>
         </is>
       </c>
     </row>
@@ -2245,7 +2245,7 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:31</t>
+          <t>2026-05-28 08:54:36</t>
         </is>
       </c>
     </row>
@@ -2305,7 +2305,7 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:31</t>
+          <t>2026-05-28 08:54:36</t>
         </is>
       </c>
     </row>
@@ -2365,7 +2365,7 @@
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:31</t>
+          <t>2026-05-28 08:54:36</t>
         </is>
       </c>
     </row>
@@ -2425,7 +2425,7 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:31</t>
+          <t>2026-05-28 08:54:36</t>
         </is>
       </c>
     </row>
@@ -2485,7 +2485,7 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:31</t>
+          <t>2026-05-28 08:54:36</t>
         </is>
       </c>
     </row>
@@ -2545,7 +2545,7 @@
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:31</t>
+          <t>2026-05-28 08:54:36</t>
         </is>
       </c>
     </row>
@@ -2605,7 +2605,7 @@
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:31</t>
+          <t>2026-05-28 08:54:36</t>
         </is>
       </c>
     </row>
@@ -2665,7 +2665,7 @@
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:31</t>
+          <t>2026-05-28 08:54:36</t>
         </is>
       </c>
     </row>
@@ -2725,7 +2725,7 @@
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:31</t>
+          <t>2026-05-28 08:54:36</t>
         </is>
       </c>
     </row>
@@ -2785,7 +2785,7 @@
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:31</t>
+          <t>2026-05-28 08:54:36</t>
         </is>
       </c>
     </row>
@@ -2845,7 +2845,7 @@
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:31</t>
+          <t>2026-05-28 08:54:36</t>
         </is>
       </c>
     </row>
@@ -2905,7 +2905,7 @@
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:31</t>
+          <t>2026-05-28 08:54:36</t>
         </is>
       </c>
     </row>
@@ -2965,7 +2965,7 @@
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:31</t>
+          <t>2026-05-28 08:54:36</t>
         </is>
       </c>
     </row>
@@ -3025,7 +3025,7 @@
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:31</t>
+          <t>2026-05-28 08:54:36</t>
         </is>
       </c>
     </row>
@@ -3085,7 +3085,7 @@
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:31</t>
+          <t>2026-05-28 08:54:36</t>
         </is>
       </c>
     </row>
@@ -3145,7 +3145,7 @@
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:31</t>
+          <t>2026-05-28 08:54:36</t>
         </is>
       </c>
     </row>
@@ -3205,7 +3205,7 @@
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:31</t>
+          <t>2026-05-28 08:54:36</t>
         </is>
       </c>
     </row>
@@ -3265,7 +3265,7 @@
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:31</t>
+          <t>2026-05-28 08:54:36</t>
         </is>
       </c>
     </row>
@@ -3325,7 +3325,7 @@
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:31</t>
+          <t>2026-05-28 08:54:36</t>
         </is>
       </c>
     </row>
@@ -3385,7 +3385,7 @@
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:31</t>
+          <t>2026-05-28 08:54:36</t>
         </is>
       </c>
     </row>
@@ -3445,7 +3445,7 @@
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:31</t>
+          <t>2026-05-28 08:54:36</t>
         </is>
       </c>
     </row>
@@ -3505,7 +3505,7 @@
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:31</t>
+          <t>2026-05-28 08:54:36</t>
         </is>
       </c>
     </row>
@@ -3565,7 +3565,7 @@
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:31</t>
+          <t>2026-05-28 08:54:36</t>
         </is>
       </c>
     </row>
@@ -3625,7 +3625,7 @@
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:31</t>
+          <t>2026-05-28 08:54:36</t>
         </is>
       </c>
     </row>
@@ -3685,7 +3685,7 @@
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:31</t>
+          <t>2026-05-28 08:54:36</t>
         </is>
       </c>
     </row>
@@ -3745,7 +3745,7 @@
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:31</t>
+          <t>2026-05-28 08:54:36</t>
         </is>
       </c>
     </row>
@@ -3805,7 +3805,7 @@
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:31</t>
+          <t>2026-05-28 08:54:36</t>
         </is>
       </c>
     </row>
@@ -3865,7 +3865,7 @@
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:31</t>
+          <t>2026-05-28 08:54:36</t>
         </is>
       </c>
     </row>
@@ -3925,7 +3925,7 @@
       </c>
       <c r="R58" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:31</t>
+          <t>2026-05-28 08:54:36</t>
         </is>
       </c>
     </row>
@@ -3985,7 +3985,7 @@
       </c>
       <c r="R59" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:31</t>
+          <t>2026-05-28 08:54:36</t>
         </is>
       </c>
     </row>
@@ -4045,7 +4045,7 @@
       </c>
       <c r="R60" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:31</t>
+          <t>2026-05-28 08:54:36</t>
         </is>
       </c>
     </row>
@@ -4105,7 +4105,7 @@
       </c>
       <c r="R61" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:31</t>
+          <t>2026-05-28 08:54:36</t>
         </is>
       </c>
     </row>
@@ -4165,7 +4165,7 @@
       </c>
       <c r="R62" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:31</t>
+          <t>2026-05-28 08:54:36</t>
         </is>
       </c>
     </row>
@@ -4225,7 +4225,7 @@
       </c>
       <c r="R63" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:31</t>
+          <t>2026-05-28 08:54:36</t>
         </is>
       </c>
     </row>
@@ -4285,7 +4285,7 @@
       </c>
       <c r="R64" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:31</t>
+          <t>2026-05-28 08:54:36</t>
         </is>
       </c>
     </row>
@@ -4345,7 +4345,7 @@
       </c>
       <c r="R65" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:31</t>
+          <t>2026-05-28 08:54:36</t>
         </is>
       </c>
     </row>
@@ -4405,7 +4405,7 @@
       </c>
       <c r="R66" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:31</t>
+          <t>2026-05-28 08:54:36</t>
         </is>
       </c>
     </row>
@@ -4465,7 +4465,7 @@
       </c>
       <c r="R67" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:31</t>
+          <t>2026-05-28 08:54:36</t>
         </is>
       </c>
     </row>
@@ -4525,7 +4525,7 @@
       </c>
       <c r="R68" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:31</t>
+          <t>2026-05-28 08:54:36</t>
         </is>
       </c>
     </row>
@@ -4585,7 +4585,7 @@
       </c>
       <c r="R69" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:31</t>
+          <t>2026-05-28 08:54:36</t>
         </is>
       </c>
     </row>
@@ -4645,7 +4645,7 @@
       </c>
       <c r="R70" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:31</t>
+          <t>2026-05-28 08:54:36</t>
         </is>
       </c>
     </row>
@@ -4705,7 +4705,7 @@
       </c>
       <c r="R71" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:31</t>
+          <t>2026-05-28 08:54:36</t>
         </is>
       </c>
     </row>
@@ -4765,7 +4765,7 @@
       </c>
       <c r="R72" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:31</t>
+          <t>2026-05-28 08:54:36</t>
         </is>
       </c>
     </row>
@@ -4825,7 +4825,7 @@
       </c>
       <c r="R73" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:31</t>
+          <t>2026-05-28 08:54:36</t>
         </is>
       </c>
     </row>
@@ -4885,7 +4885,7 @@
       </c>
       <c r="R74" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:31</t>
+          <t>2026-05-28 08:54:36</t>
         </is>
       </c>
     </row>
@@ -4945,7 +4945,7 @@
       </c>
       <c r="R75" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:31</t>
+          <t>2026-05-28 08:54:36</t>
         </is>
       </c>
     </row>

--- a/data/exports/optimization/uk49s_genetic_optimizer_results.xlsx
+++ b/data/exports/optimization/uk49s_genetic_optimizer_results.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R75"/>
+  <dimension ref="A1:R74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -532,7 +532,7 @@
         <v>49</v>
       </c>
       <c r="H2" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="I2" t="n">
         <v>148</v>
@@ -556,7 +556,7 @@
         <v>14.7051</v>
       </c>
       <c r="P2" t="n">
-        <v>201.2628</v>
+        <v>201.4628</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -565,7 +565,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:36</t>
+          <t>2026-05-28 17:22:42</t>
         </is>
       </c>
     </row>
@@ -592,7 +592,7 @@
         <v>49</v>
       </c>
       <c r="H3" t="n">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="I3" t="n">
         <v>148</v>
@@ -616,7 +616,7 @@
         <v>14.7051</v>
       </c>
       <c r="P3" t="n">
-        <v>201.2628</v>
+        <v>201.4628</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -625,7 +625,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:36</t>
+          <t>2026-05-28 17:22:42</t>
         </is>
       </c>
     </row>
@@ -652,7 +652,7 @@
         <v>49</v>
       </c>
       <c r="H4" t="n">
-        <v>29</v>
+        <v>10</v>
       </c>
       <c r="I4" t="n">
         <v>148</v>
@@ -676,7 +676,7 @@
         <v>14.7051</v>
       </c>
       <c r="P4" t="n">
-        <v>201.2628</v>
+        <v>201.4628</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -685,7 +685,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:36</t>
+          <t>2026-05-28 17:22:42</t>
         </is>
       </c>
     </row>
@@ -712,7 +712,7 @@
         <v>49</v>
       </c>
       <c r="H5" t="n">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="I5" t="n">
         <v>148</v>
@@ -736,7 +736,7 @@
         <v>14.7051</v>
       </c>
       <c r="P5" t="n">
-        <v>201.2628</v>
+        <v>201.4628</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -745,7 +745,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:36</t>
+          <t>2026-05-28 17:22:42</t>
         </is>
       </c>
     </row>
@@ -772,7 +772,7 @@
         <v>49</v>
       </c>
       <c r="H6" t="n">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="I6" t="n">
         <v>148</v>
@@ -796,7 +796,7 @@
         <v>14.7051</v>
       </c>
       <c r="P6" t="n">
-        <v>201.2628</v>
+        <v>201.4628</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -805,7 +805,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:36</t>
+          <t>2026-05-28 17:22:42</t>
         </is>
       </c>
     </row>
@@ -832,7 +832,7 @@
         <v>49</v>
       </c>
       <c r="H7" t="n">
-        <v>26</v>
+        <v>47</v>
       </c>
       <c r="I7" t="n">
         <v>148</v>
@@ -856,7 +856,7 @@
         <v>14.7051</v>
       </c>
       <c r="P7" t="n">
-        <v>201.2628</v>
+        <v>201.4628</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
@@ -865,7 +865,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:36</t>
+          <t>2026-05-28 17:22:42</t>
         </is>
       </c>
     </row>
@@ -892,7 +892,7 @@
         <v>49</v>
       </c>
       <c r="H8" t="n">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="I8" t="n">
         <v>148</v>
@@ -916,7 +916,7 @@
         <v>14.7051</v>
       </c>
       <c r="P8" t="n">
-        <v>201.2628</v>
+        <v>201.4628</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:36</t>
+          <t>2026-05-28 17:22:42</t>
         </is>
       </c>
     </row>
@@ -952,7 +952,7 @@
         <v>49</v>
       </c>
       <c r="H9" t="n">
-        <v>39</v>
+        <v>22</v>
       </c>
       <c r="I9" t="n">
         <v>148</v>
@@ -976,7 +976,7 @@
         <v>14.7051</v>
       </c>
       <c r="P9" t="n">
-        <v>201.2628</v>
+        <v>201.4628</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
@@ -985,7 +985,7 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:36</t>
+          <t>2026-05-28 17:22:42</t>
         </is>
       </c>
     </row>
@@ -1012,7 +1012,7 @@
         <v>49</v>
       </c>
       <c r="H10" t="n">
-        <v>48</v>
+        <v>31</v>
       </c>
       <c r="I10" t="n">
         <v>148</v>
@@ -1036,7 +1036,7 @@
         <v>14.7051</v>
       </c>
       <c r="P10" t="n">
-        <v>201.2628</v>
+        <v>201.4628</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
@@ -1045,7 +1045,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:36</t>
+          <t>2026-05-28 17:22:42</t>
         </is>
       </c>
     </row>
@@ -1072,7 +1072,7 @@
         <v>49</v>
       </c>
       <c r="H11" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="I11" t="n">
         <v>148</v>
@@ -1096,7 +1096,7 @@
         <v>14.7051</v>
       </c>
       <c r="P11" t="n">
-        <v>201.2628</v>
+        <v>201.4628</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
@@ -1105,7 +1105,7 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:36</t>
+          <t>2026-05-28 17:22:42</t>
         </is>
       </c>
     </row>
@@ -1132,7 +1132,7 @@
         <v>49</v>
       </c>
       <c r="H12" t="n">
-        <v>41</v>
+        <v>11</v>
       </c>
       <c r="I12" t="n">
         <v>148</v>
@@ -1156,7 +1156,7 @@
         <v>14.7051</v>
       </c>
       <c r="P12" t="n">
-        <v>201.2628</v>
+        <v>201.4628</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
@@ -1165,7 +1165,7 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:36</t>
+          <t>2026-05-28 17:22:42</t>
         </is>
       </c>
     </row>
@@ -1192,7 +1192,7 @@
         <v>49</v>
       </c>
       <c r="H13" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="I13" t="n">
         <v>148</v>
@@ -1216,7 +1216,7 @@
         <v>14.7051</v>
       </c>
       <c r="P13" t="n">
-        <v>201.2628</v>
+        <v>201.4628</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
@@ -1225,7 +1225,7 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:36</t>
+          <t>2026-05-28 17:22:42</t>
         </is>
       </c>
     </row>
@@ -1252,7 +1252,7 @@
         <v>49</v>
       </c>
       <c r="H14" t="n">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="I14" t="n">
         <v>148</v>
@@ -1276,7 +1276,7 @@
         <v>14.7051</v>
       </c>
       <c r="P14" t="n">
-        <v>201.2628</v>
+        <v>201.4628</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
@@ -1285,7 +1285,7 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:36</t>
+          <t>2026-05-28 17:22:42</t>
         </is>
       </c>
     </row>
@@ -1312,7 +1312,7 @@
         <v>49</v>
       </c>
       <c r="H15" t="n">
-        <v>43</v>
+        <v>16</v>
       </c>
       <c r="I15" t="n">
         <v>148</v>
@@ -1336,7 +1336,7 @@
         <v>14.7051</v>
       </c>
       <c r="P15" t="n">
-        <v>201.2628</v>
+        <v>201.4628</v>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
@@ -1345,7 +1345,7 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:36</t>
+          <t>2026-05-28 17:22:42</t>
         </is>
       </c>
     </row>
@@ -1372,7 +1372,7 @@
         <v>49</v>
       </c>
       <c r="H16" t="n">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="I16" t="n">
         <v>148</v>
@@ -1396,7 +1396,7 @@
         <v>14.7051</v>
       </c>
       <c r="P16" t="n">
-        <v>201.2628</v>
+        <v>201.4628</v>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
@@ -1405,7 +1405,7 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:36</t>
+          <t>2026-05-28 17:22:42</t>
         </is>
       </c>
     </row>
@@ -1432,7 +1432,7 @@
         <v>49</v>
       </c>
       <c r="H17" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="I17" t="n">
         <v>148</v>
@@ -1456,7 +1456,7 @@
         <v>14.7051</v>
       </c>
       <c r="P17" t="n">
-        <v>201.2628</v>
+        <v>201.4628</v>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
@@ -1465,7 +1465,7 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:36</t>
+          <t>2026-05-28 17:22:42</t>
         </is>
       </c>
     </row>
@@ -1492,7 +1492,7 @@
         <v>49</v>
       </c>
       <c r="H18" t="n">
-        <v>28</v>
+        <v>7</v>
       </c>
       <c r="I18" t="n">
         <v>148</v>
@@ -1516,7 +1516,7 @@
         <v>14.7051</v>
       </c>
       <c r="P18" t="n">
-        <v>201.2628</v>
+        <v>201.4628</v>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
@@ -1525,7 +1525,7 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:36</t>
+          <t>2026-05-28 17:22:42</t>
         </is>
       </c>
     </row>
@@ -1552,7 +1552,7 @@
         <v>49</v>
       </c>
       <c r="H19" t="n">
-        <v>10</v>
+        <v>38</v>
       </c>
       <c r="I19" t="n">
         <v>148</v>
@@ -1576,7 +1576,7 @@
         <v>14.7051</v>
       </c>
       <c r="P19" t="n">
-        <v>201.2628</v>
+        <v>201.4628</v>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
@@ -1585,7 +1585,7 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:36</t>
+          <t>2026-05-28 17:22:42</t>
         </is>
       </c>
     </row>
@@ -1612,7 +1612,7 @@
         <v>49</v>
       </c>
       <c r="H20" t="n">
-        <v>7</v>
+        <v>33</v>
       </c>
       <c r="I20" t="n">
         <v>148</v>
@@ -1636,7 +1636,7 @@
         <v>14.7051</v>
       </c>
       <c r="P20" t="n">
-        <v>201.2628</v>
+        <v>201.4628</v>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
@@ -1645,7 +1645,7 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:36</t>
+          <t>2026-05-28 17:22:42</t>
         </is>
       </c>
     </row>
@@ -1672,7 +1672,7 @@
         <v>49</v>
       </c>
       <c r="H21" t="n">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="I21" t="n">
         <v>148</v>
@@ -1696,7 +1696,7 @@
         <v>14.7051</v>
       </c>
       <c r="P21" t="n">
-        <v>201.2628</v>
+        <v>201.4628</v>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
@@ -1705,7 +1705,7 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:36</t>
+          <t>2026-05-28 17:22:42</t>
         </is>
       </c>
     </row>
@@ -1732,7 +1732,7 @@
         <v>49</v>
       </c>
       <c r="H22" t="n">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="I22" t="n">
         <v>148</v>
@@ -1756,7 +1756,7 @@
         <v>14.7051</v>
       </c>
       <c r="P22" t="n">
-        <v>201.2628</v>
+        <v>201.4628</v>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
@@ -1765,7 +1765,7 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:36</t>
+          <t>2026-05-28 17:22:42</t>
         </is>
       </c>
     </row>
@@ -1792,7 +1792,7 @@
         <v>49</v>
       </c>
       <c r="H23" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="I23" t="n">
         <v>148</v>
@@ -1816,7 +1816,7 @@
         <v>14.7051</v>
       </c>
       <c r="P23" t="n">
-        <v>201.2628</v>
+        <v>201.4628</v>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
@@ -1825,7 +1825,7 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:36</t>
+          <t>2026-05-28 17:22:42</t>
         </is>
       </c>
     </row>
@@ -1852,7 +1852,7 @@
         <v>49</v>
       </c>
       <c r="H24" t="n">
-        <v>31</v>
+        <v>14</v>
       </c>
       <c r="I24" t="n">
         <v>148</v>
@@ -1876,7 +1876,7 @@
         <v>14.7051</v>
       </c>
       <c r="P24" t="n">
-        <v>201.2628</v>
+        <v>201.4628</v>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
@@ -1885,7 +1885,7 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:36</t>
+          <t>2026-05-28 17:22:42</t>
         </is>
       </c>
     </row>
@@ -1912,7 +1912,7 @@
         <v>49</v>
       </c>
       <c r="H25" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="I25" t="n">
         <v>148</v>
@@ -1936,7 +1936,7 @@
         <v>14.7051</v>
       </c>
       <c r="P25" t="n">
-        <v>201.2628</v>
+        <v>201.4628</v>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
@@ -1945,7 +1945,7 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:36</t>
+          <t>2026-05-28 17:22:42</t>
         </is>
       </c>
     </row>
@@ -1972,7 +1972,7 @@
         <v>49</v>
       </c>
       <c r="H26" t="n">
-        <v>14</v>
+        <v>42</v>
       </c>
       <c r="I26" t="n">
         <v>148</v>
@@ -1996,7 +1996,7 @@
         <v>14.7051</v>
       </c>
       <c r="P26" t="n">
-        <v>201.2628</v>
+        <v>201.4628</v>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
@@ -2005,7 +2005,7 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:36</t>
+          <t>2026-05-28 17:22:42</t>
         </is>
       </c>
     </row>
@@ -2032,7 +2032,7 @@
         <v>49</v>
       </c>
       <c r="H27" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="I27" t="n">
         <v>148</v>
@@ -2056,7 +2056,7 @@
         <v>14.7051</v>
       </c>
       <c r="P27" t="n">
-        <v>201.2628</v>
+        <v>201.4628</v>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
@@ -2065,7 +2065,7 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:36</t>
+          <t>2026-05-28 17:22:42</t>
         </is>
       </c>
     </row>
@@ -2092,7 +2092,7 @@
         <v>49</v>
       </c>
       <c r="H28" t="n">
-        <v>42</v>
+        <v>23</v>
       </c>
       <c r="I28" t="n">
         <v>148</v>
@@ -2116,7 +2116,7 @@
         <v>14.7051</v>
       </c>
       <c r="P28" t="n">
-        <v>201.2628</v>
+        <v>201.4628</v>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
@@ -2125,7 +2125,7 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:36</t>
+          <t>2026-05-28 17:22:42</t>
         </is>
       </c>
     </row>
@@ -2152,7 +2152,7 @@
         <v>49</v>
       </c>
       <c r="H29" t="n">
-        <v>23</v>
+        <v>39</v>
       </c>
       <c r="I29" t="n">
         <v>148</v>
@@ -2176,7 +2176,7 @@
         <v>14.7051</v>
       </c>
       <c r="P29" t="n">
-        <v>201.2628</v>
+        <v>201.4628</v>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
@@ -2185,7 +2185,7 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:36</t>
+          <t>2026-05-28 17:22:42</t>
         </is>
       </c>
     </row>
@@ -2212,7 +2212,7 @@
         <v>49</v>
       </c>
       <c r="H30" t="n">
-        <v>22</v>
+        <v>2</v>
       </c>
       <c r="I30" t="n">
         <v>148</v>
@@ -2236,7 +2236,7 @@
         <v>14.7051</v>
       </c>
       <c r="P30" t="n">
-        <v>201.2628</v>
+        <v>201.4628</v>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
@@ -2245,7 +2245,7 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:36</t>
+          <t>2026-05-28 17:22:42</t>
         </is>
       </c>
     </row>
@@ -2257,10 +2257,10 @@
         <v>1</v>
       </c>
       <c r="C31" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D31" t="n">
-        <v>5</v>
+        <v>42</v>
       </c>
       <c r="E31" t="n">
         <v>44</v>
@@ -2272,31 +2272,31 @@
         <v>49</v>
       </c>
       <c r="H31" t="n">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="I31" t="n">
-        <v>148</v>
+        <v>187</v>
       </c>
       <c r="J31" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K31" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L31" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N31" t="n">
         <v>0</v>
       </c>
       <c r="O31" t="n">
-        <v>14.7051</v>
+        <v>13.7201</v>
       </c>
       <c r="P31" t="n">
-        <v>201.2628</v>
+        <v>198.2001</v>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
@@ -2305,7 +2305,7 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:36</t>
+          <t>2026-05-28 17:22:42</t>
         </is>
       </c>
     </row>
@@ -2314,7 +2314,7 @@
         <v>31</v>
       </c>
       <c r="B32" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C32" t="n">
         <v>3</v>
@@ -2332,10 +2332,10 @@
         <v>49</v>
       </c>
       <c r="H32" t="n">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="I32" t="n">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="J32" t="n">
         <v>3</v>
@@ -2344,19 +2344,19 @@
         <v>3</v>
       </c>
       <c r="L32" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M32" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O32" t="n">
-        <v>14.7051</v>
+        <v>14.8135</v>
       </c>
       <c r="P32" t="n">
-        <v>201.2628</v>
+        <v>197.6138</v>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
@@ -2365,7 +2365,7 @@
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:36</t>
+          <t>2026-05-28 17:22:42</t>
         </is>
       </c>
     </row>
@@ -2374,13 +2374,13 @@
         <v>32</v>
       </c>
       <c r="B33" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C33" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D33" t="n">
-        <v>42</v>
+        <v>5</v>
       </c>
       <c r="E33" t="n">
         <v>44</v>
@@ -2392,16 +2392,16 @@
         <v>49</v>
       </c>
       <c r="H33" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="I33" t="n">
-        <v>187</v>
+        <v>149</v>
       </c>
       <c r="J33" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K33" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L33" t="n">
         <v>3</v>
@@ -2410,13 +2410,13 @@
         <v>3</v>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O33" t="n">
-        <v>13.7201</v>
+        <v>14.8135</v>
       </c>
       <c r="P33" t="n">
-        <v>198.0001</v>
+        <v>197.6138</v>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
@@ -2425,7 +2425,7 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:36</t>
+          <t>2026-05-28 17:22:42</t>
         </is>
       </c>
     </row>
@@ -2434,13 +2434,13 @@
         <v>33</v>
       </c>
       <c r="B34" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C34" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D34" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E34" t="n">
         <v>44</v>
@@ -2452,10 +2452,10 @@
         <v>49</v>
       </c>
       <c r="H34" t="n">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="I34" t="n">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="J34" t="n">
         <v>3</v>
@@ -2473,10 +2473,10 @@
         <v>1</v>
       </c>
       <c r="O34" t="n">
-        <v>14.8135</v>
+        <v>14.4139</v>
       </c>
       <c r="P34" t="n">
-        <v>197.4138</v>
+        <v>197.4947</v>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
@@ -2485,7 +2485,7 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:36</t>
+          <t>2026-05-28 17:22:42</t>
         </is>
       </c>
     </row>
@@ -2494,49 +2494,49 @@
         <v>34</v>
       </c>
       <c r="B35" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C35" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D35" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E35" t="n">
-        <v>44</v>
+        <v>8</v>
       </c>
       <c r="F35" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="G35" t="n">
         <v>49</v>
       </c>
       <c r="H35" t="n">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="I35" t="n">
-        <v>153</v>
+        <v>110</v>
       </c>
       <c r="J35" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K35" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L35" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M35" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O35" t="n">
-        <v>14.4139</v>
+        <v>13.2454</v>
       </c>
       <c r="P35" t="n">
-        <v>197.0547</v>
+        <v>196.9934</v>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
@@ -2545,7 +2545,7 @@
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:36</t>
+          <t>2026-05-28 17:22:42</t>
         </is>
       </c>
     </row>
@@ -2560,28 +2560,28 @@
         <v>3</v>
       </c>
       <c r="D36" t="n">
-        <v>40</v>
+        <v>5</v>
       </c>
       <c r="E36" t="n">
-        <v>44</v>
+        <v>6</v>
       </c>
       <c r="F36" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="G36" t="n">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="H36" t="n">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="I36" t="n">
-        <v>183</v>
+        <v>105</v>
       </c>
       <c r="J36" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K36" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L36" t="n">
         <v>3</v>
@@ -2590,13 +2590,13 @@
         <v>3</v>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O36" t="n">
-        <v>13.7201</v>
+        <v>14.5052</v>
       </c>
       <c r="P36" t="n">
-        <v>196.8401</v>
+        <v>196.9229</v>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
@@ -2605,7 +2605,7 @@
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:36</t>
+          <t>2026-05-28 17:22:42</t>
         </is>
       </c>
     </row>
@@ -2623,7 +2623,7 @@
         <v>5</v>
       </c>
       <c r="E37" t="n">
-        <v>8</v>
+        <v>40</v>
       </c>
       <c r="F37" t="n">
         <v>44</v>
@@ -2632,16 +2632,16 @@
         <v>49</v>
       </c>
       <c r="H37" t="n">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="I37" t="n">
-        <v>110</v>
+        <v>142</v>
       </c>
       <c r="J37" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K37" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L37" t="n">
         <v>4</v>
@@ -2653,10 +2653,10 @@
         <v>0</v>
       </c>
       <c r="O37" t="n">
-        <v>13.2454</v>
+        <v>12.753</v>
       </c>
       <c r="P37" t="n">
-        <v>196.7934</v>
+        <v>196.8826</v>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
@@ -2665,7 +2665,7 @@
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:36</t>
+          <t>2026-05-28 17:22:42</t>
         </is>
       </c>
     </row>
@@ -2680,22 +2680,22 @@
         <v>3</v>
       </c>
       <c r="D38" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E38" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="F38" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="G38" t="n">
         <v>49</v>
       </c>
       <c r="H38" t="n">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="I38" t="n">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="J38" t="n">
         <v>3</v>
@@ -2704,19 +2704,19 @@
         <v>3</v>
       </c>
       <c r="L38" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M38" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O38" t="n">
-        <v>12.753</v>
+        <v>15.2132</v>
       </c>
       <c r="P38" t="n">
-        <v>196.5826</v>
+        <v>196.1929</v>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
@@ -2725,7 +2725,7 @@
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:36</t>
+          <t>2026-05-28 17:22:42</t>
         </is>
       </c>
     </row>
@@ -2743,7 +2743,7 @@
         <v>5</v>
       </c>
       <c r="E39" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F39" t="n">
         <v>44</v>
@@ -2752,10 +2752,10 @@
         <v>46</v>
       </c>
       <c r="H39" t="n">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="I39" t="n">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="J39" t="n">
         <v>2</v>
@@ -2764,19 +2764,19 @@
         <v>4</v>
       </c>
       <c r="L39" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M39" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O39" t="n">
-        <v>14.5052</v>
+        <v>13.0231</v>
       </c>
       <c r="P39" t="n">
-        <v>196.4829</v>
+        <v>195.6576</v>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
@@ -2785,7 +2785,7 @@
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:36</t>
+          <t>2026-05-28 17:22:42</t>
         </is>
       </c>
     </row>
@@ -2800,10 +2800,10 @@
         <v>3</v>
       </c>
       <c r="D40" t="n">
-        <v>4</v>
+        <v>44</v>
       </c>
       <c r="E40" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F40" t="n">
         <v>46</v>
@@ -2812,31 +2812,31 @@
         <v>49</v>
       </c>
       <c r="H40" t="n">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c r="I40" t="n">
-        <v>147</v>
+        <v>188</v>
       </c>
       <c r="J40" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K40" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L40" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M40" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N40" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O40" t="n">
-        <v>15.2132</v>
+        <v>15.7175</v>
       </c>
       <c r="P40" t="n">
-        <v>195.9929</v>
+        <v>195.5938</v>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
@@ -2845,7 +2845,7 @@
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:36</t>
+          <t>2026-05-28 17:22:42</t>
         </is>
       </c>
     </row>
@@ -2857,46 +2857,46 @@
         <v>1</v>
       </c>
       <c r="C41" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D41" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E41" t="n">
-        <v>9</v>
+        <v>44</v>
       </c>
       <c r="F41" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="G41" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="H41" t="n">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="I41" t="n">
-        <v>108</v>
+        <v>145</v>
       </c>
       <c r="J41" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K41" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L41" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M41" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O41" t="n">
-        <v>13.0231</v>
+        <v>15.7175</v>
       </c>
       <c r="P41" t="n">
-        <v>195.4576</v>
+        <v>195.5938</v>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
@@ -2905,7 +2905,7 @@
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:36</t>
+          <t>2026-05-28 17:22:42</t>
         </is>
       </c>
     </row>
@@ -2917,13 +2917,13 @@
         <v>1</v>
       </c>
       <c r="C42" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D42" t="n">
-        <v>44</v>
+        <v>9</v>
       </c>
       <c r="E42" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F42" t="n">
         <v>46</v>
@@ -2932,16 +2932,16 @@
         <v>49</v>
       </c>
       <c r="H42" t="n">
-        <v>32</v>
+        <v>6</v>
       </c>
       <c r="I42" t="n">
-        <v>188</v>
+        <v>154</v>
       </c>
       <c r="J42" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K42" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L42" t="n">
         <v>4</v>
@@ -2950,13 +2950,13 @@
         <v>2</v>
       </c>
       <c r="N42" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O42" t="n">
-        <v>15.7175</v>
+        <v>12.7216</v>
       </c>
       <c r="P42" t="n">
-        <v>195.3938</v>
+        <v>195.2841</v>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
@@ -2965,7 +2965,7 @@
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:36</t>
+          <t>2026-05-28 17:22:42</t>
         </is>
       </c>
     </row>
@@ -2977,25 +2977,25 @@
         <v>1</v>
       </c>
       <c r="C43" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D43" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E43" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F43" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="G43" t="n">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="H43" t="n">
         <v>32</v>
       </c>
       <c r="I43" t="n">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="J43" t="n">
         <v>3</v>
@@ -3004,19 +3004,19 @@
         <v>3</v>
       </c>
       <c r="L43" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M43" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N43" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O43" t="n">
-        <v>15.7175</v>
+        <v>14.5052</v>
       </c>
       <c r="P43" t="n">
-        <v>195.3938</v>
+        <v>195.1629</v>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
@@ -3025,7 +3025,7 @@
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:36</t>
+          <t>2026-05-28 17:22:42</t>
         </is>
       </c>
     </row>
@@ -3040,7 +3040,7 @@
         <v>5</v>
       </c>
       <c r="D44" t="n">
-        <v>9</v>
+        <v>43</v>
       </c>
       <c r="E44" t="n">
         <v>44</v>
@@ -3052,16 +3052,16 @@
         <v>49</v>
       </c>
       <c r="H44" t="n">
-        <v>6</v>
+        <v>47</v>
       </c>
       <c r="I44" t="n">
-        <v>154</v>
+        <v>188</v>
       </c>
       <c r="J44" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K44" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L44" t="n">
         <v>4</v>
@@ -3070,13 +3070,13 @@
         <v>2</v>
       </c>
       <c r="N44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O44" t="n">
-        <v>12.7216</v>
+        <v>14.2352</v>
       </c>
       <c r="P44" t="n">
-        <v>195.0841</v>
+        <v>194.5479</v>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
@@ -3085,7 +3085,7 @@
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:36</t>
+          <t>2026-05-28 17:22:42</t>
         </is>
       </c>
     </row>
@@ -3094,28 +3094,28 @@
         <v>44</v>
       </c>
       <c r="B45" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C45" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D45" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E45" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F45" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="G45" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="H45" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="I45" t="n">
-        <v>142</v>
+        <v>157</v>
       </c>
       <c r="J45" t="n">
         <v>3</v>
@@ -3124,19 +3124,19 @@
         <v>3</v>
       </c>
       <c r="L45" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M45" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O45" t="n">
-        <v>14.5052</v>
+        <v>12.4483</v>
       </c>
       <c r="P45" t="n">
-        <v>194.8229</v>
+        <v>193.8207</v>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
@@ -3145,7 +3145,7 @@
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:36</t>
+          <t>2026-05-28 17:22:42</t>
         </is>
       </c>
     </row>
@@ -3157,46 +3157,46 @@
         <v>1</v>
       </c>
       <c r="C46" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D46" t="n">
-        <v>43</v>
+        <v>5</v>
       </c>
       <c r="E46" t="n">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="F46" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="G46" t="n">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="H46" t="n">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="I46" t="n">
-        <v>188</v>
+        <v>137</v>
       </c>
       <c r="J46" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K46" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L46" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M46" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O46" t="n">
-        <v>14.2352</v>
+        <v>12.0996</v>
       </c>
       <c r="P46" t="n">
-        <v>194.2079</v>
+        <v>193.509</v>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
@@ -3205,7 +3205,7 @@
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:36</t>
+          <t>2026-05-28 17:22:42</t>
         </is>
       </c>
     </row>
@@ -3214,34 +3214,34 @@
         <v>46</v>
       </c>
       <c r="B47" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C47" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D47" t="n">
+        <v>5</v>
+      </c>
+      <c r="E47" t="n">
         <v>10</v>
       </c>
-      <c r="E47" t="n">
-        <v>44</v>
-      </c>
       <c r="F47" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="G47" t="n">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="H47" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="I47" t="n">
-        <v>157</v>
+        <v>109</v>
       </c>
       <c r="J47" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K47" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L47" t="n">
         <v>3</v>
@@ -3253,10 +3253,10 @@
         <v>0</v>
       </c>
       <c r="O47" t="n">
-        <v>12.4483</v>
+        <v>12.5539</v>
       </c>
       <c r="P47" t="n">
-        <v>193.6207</v>
+        <v>193.3647</v>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
@@ -3265,7 +3265,7 @@
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:36</t>
+          <t>2026-05-28 17:22:42</t>
         </is>
       </c>
     </row>
@@ -3277,46 +3277,46 @@
         <v>1</v>
       </c>
       <c r="C48" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D48" t="n">
-        <v>5</v>
+        <v>39</v>
       </c>
       <c r="E48" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="F48" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="G48" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="H48" t="n">
         <v>29</v>
       </c>
       <c r="I48" t="n">
-        <v>137</v>
+        <v>184</v>
       </c>
       <c r="J48" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K48" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L48" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M48" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N48" t="n">
         <v>0</v>
       </c>
       <c r="O48" t="n">
-        <v>12.0996</v>
+        <v>12.2409</v>
       </c>
       <c r="P48" t="n">
-        <v>193.309</v>
+        <v>193.2223</v>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
@@ -3325,7 +3325,7 @@
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:36</t>
+          <t>2026-05-28 17:22:42</t>
         </is>
       </c>
     </row>
@@ -3343,19 +3343,19 @@
         <v>5</v>
       </c>
       <c r="E49" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F49" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="G49" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="H49" t="n">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="I49" t="n">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="J49" t="n">
         <v>2</v>
@@ -3364,19 +3364,19 @@
         <v>4</v>
       </c>
       <c r="L49" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M49" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N49" t="n">
         <v>0</v>
       </c>
       <c r="O49" t="n">
-        <v>12.5539</v>
+        <v>12.3386</v>
       </c>
       <c r="P49" t="n">
-        <v>193.1647</v>
+        <v>193.1464</v>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
@@ -3385,7 +3385,7 @@
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:36</t>
+          <t>2026-05-28 17:22:42</t>
         </is>
       </c>
     </row>
@@ -3400,10 +3400,10 @@
         <v>3</v>
       </c>
       <c r="D50" t="n">
-        <v>5</v>
+        <v>37</v>
       </c>
       <c r="E50" t="n">
-        <v>12</v>
+        <v>44</v>
       </c>
       <c r="F50" t="n">
         <v>46</v>
@@ -3412,16 +3412,16 @@
         <v>49</v>
       </c>
       <c r="H50" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="I50" t="n">
-        <v>116</v>
+        <v>180</v>
       </c>
       <c r="J50" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K50" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L50" t="n">
         <v>4</v>
@@ -3436,7 +3436,7 @@
         <v>12.3386</v>
       </c>
       <c r="P50" t="n">
-        <v>193.1464</v>
+        <v>192.9864</v>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
@@ -3445,7 +3445,7 @@
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:36</t>
+          <t>2026-05-28 17:22:42</t>
         </is>
       </c>
     </row>
@@ -3460,7 +3460,7 @@
         <v>5</v>
       </c>
       <c r="D51" t="n">
-        <v>39</v>
+        <v>10</v>
       </c>
       <c r="E51" t="n">
         <v>44</v>
@@ -3475,19 +3475,19 @@
         <v>32</v>
       </c>
       <c r="I51" t="n">
-        <v>184</v>
+        <v>155</v>
       </c>
       <c r="J51" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K51" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L51" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M51" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N51" t="n">
         <v>0</v>
@@ -3496,7 +3496,7 @@
         <v>12.2409</v>
       </c>
       <c r="P51" t="n">
-        <v>193.0223</v>
+        <v>192.4823</v>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
@@ -3505,7 +3505,7 @@
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:36</t>
+          <t>2026-05-28 17:22:42</t>
         </is>
       </c>
     </row>
@@ -3520,28 +3520,28 @@
         <v>3</v>
       </c>
       <c r="D52" t="n">
-        <v>37</v>
+        <v>5</v>
       </c>
       <c r="E52" t="n">
-        <v>44</v>
+        <v>14</v>
       </c>
       <c r="F52" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="G52" t="n">
         <v>49</v>
       </c>
       <c r="H52" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="I52" t="n">
-        <v>180</v>
+        <v>116</v>
       </c>
       <c r="J52" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K52" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L52" t="n">
         <v>4</v>
@@ -3553,10 +3553,10 @@
         <v>0</v>
       </c>
       <c r="O52" t="n">
-        <v>12.3386</v>
+        <v>10.5186</v>
       </c>
       <c r="P52" t="n">
-        <v>192.6864</v>
+        <v>192.3364</v>
       </c>
       <c r="Q52" t="inlineStr">
         <is>
@@ -3565,7 +3565,7 @@
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:36</t>
+          <t>2026-05-28 17:22:42</t>
         </is>
       </c>
     </row>
@@ -3577,25 +3577,25 @@
         <v>1</v>
       </c>
       <c r="C53" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D53" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E53" t="n">
         <v>44</v>
       </c>
       <c r="F53" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G53" t="n">
         <v>49</v>
       </c>
       <c r="H53" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="I53" t="n">
-        <v>155</v>
+        <v>147</v>
       </c>
       <c r="J53" t="n">
         <v>3</v>
@@ -3604,19 +3604,19 @@
         <v>3</v>
       </c>
       <c r="L53" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M53" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O53" t="n">
-        <v>12.2409</v>
+        <v>14.7323</v>
       </c>
       <c r="P53" t="n">
-        <v>192.2823</v>
+        <v>192.1707</v>
       </c>
       <c r="Q53" t="inlineStr">
         <is>
@@ -3625,7 +3625,7 @@
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:36</t>
+          <t>2026-05-28 17:22:42</t>
         </is>
       </c>
     </row>
@@ -3643,7 +3643,7 @@
         <v>5</v>
       </c>
       <c r="E54" t="n">
-        <v>14</v>
+        <v>34</v>
       </c>
       <c r="F54" t="n">
         <v>44</v>
@@ -3652,16 +3652,16 @@
         <v>49</v>
       </c>
       <c r="H54" t="n">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="I54" t="n">
-        <v>116</v>
+        <v>136</v>
       </c>
       <c r="J54" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K54" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L54" t="n">
         <v>4</v>
@@ -3673,10 +3673,10 @@
         <v>0</v>
       </c>
       <c r="O54" t="n">
-        <v>10.5186</v>
+        <v>10.1311</v>
       </c>
       <c r="P54" t="n">
-        <v>192.1364</v>
+        <v>192.0079</v>
       </c>
       <c r="Q54" t="inlineStr">
         <is>
@@ -3685,7 +3685,7 @@
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:36</t>
+          <t>2026-05-28 17:22:42</t>
         </is>
       </c>
     </row>
@@ -3703,19 +3703,19 @@
         <v>5</v>
       </c>
       <c r="E55" t="n">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="F55" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="G55" t="n">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="H55" t="n">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="I55" t="n">
-        <v>147</v>
+        <v>136</v>
       </c>
       <c r="J55" t="n">
         <v>3</v>
@@ -3724,19 +3724,19 @@
         <v>3</v>
       </c>
       <c r="L55" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M55" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O55" t="n">
-        <v>14.7323</v>
+        <v>11.6619</v>
       </c>
       <c r="P55" t="n">
-        <v>191.9707</v>
+        <v>190.6548</v>
       </c>
       <c r="Q55" t="inlineStr">
         <is>
@@ -3745,7 +3745,7 @@
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:36</t>
+          <t>2026-05-28 17:22:42</t>
         </is>
       </c>
     </row>
@@ -3760,28 +3760,28 @@
         <v>3</v>
       </c>
       <c r="D56" t="n">
-        <v>5</v>
+        <v>31</v>
       </c>
       <c r="E56" t="n">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="F56" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="G56" t="n">
         <v>49</v>
       </c>
       <c r="H56" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="I56" t="n">
-        <v>136</v>
+        <v>174</v>
       </c>
       <c r="J56" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K56" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L56" t="n">
         <v>4</v>
@@ -3793,10 +3793,10 @@
         <v>0</v>
       </c>
       <c r="O56" t="n">
-        <v>10.1311</v>
+        <v>10.0916</v>
       </c>
       <c r="P56" t="n">
-        <v>191.6679</v>
+        <v>190.089</v>
       </c>
       <c r="Q56" t="inlineStr">
         <is>
@@ -3805,7 +3805,7 @@
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:36</t>
+          <t>2026-05-28 17:22:42</t>
         </is>
       </c>
     </row>
@@ -3823,7 +3823,7 @@
         <v>5</v>
       </c>
       <c r="E57" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F57" t="n">
         <v>44</v>
@@ -3832,10 +3832,10 @@
         <v>46</v>
       </c>
       <c r="H57" t="n">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="I57" t="n">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="J57" t="n">
         <v>3</v>
@@ -3844,19 +3844,19 @@
         <v>3</v>
       </c>
       <c r="L57" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M57" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N57" t="n">
         <v>0</v>
       </c>
       <c r="O57" t="n">
-        <v>11.6619</v>
+        <v>11.2428</v>
       </c>
       <c r="P57" t="n">
-        <v>190.3548</v>
+        <v>189.2269</v>
       </c>
       <c r="Q57" t="inlineStr">
         <is>
@@ -3865,7 +3865,7 @@
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:36</t>
+          <t>2026-05-28 17:22:42</t>
         </is>
       </c>
     </row>
@@ -3880,10 +3880,10 @@
         <v>3</v>
       </c>
       <c r="D58" t="n">
-        <v>31</v>
+        <v>5</v>
       </c>
       <c r="E58" t="n">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="F58" t="n">
         <v>46</v>
@@ -3892,16 +3892,16 @@
         <v>49</v>
       </c>
       <c r="H58" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="I58" t="n">
-        <v>174</v>
+        <v>136</v>
       </c>
       <c r="J58" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K58" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L58" t="n">
         <v>4</v>
@@ -3913,10 +3913,10 @@
         <v>0</v>
       </c>
       <c r="O58" t="n">
-        <v>10.0916</v>
+        <v>9.8102</v>
       </c>
       <c r="P58" t="n">
-        <v>189.649</v>
+        <v>188.6255</v>
       </c>
       <c r="Q58" t="inlineStr">
         <is>
@@ -3925,7 +3925,7 @@
       </c>
       <c r="R58" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:36</t>
+          <t>2026-05-28 17:22:42</t>
         </is>
       </c>
     </row>
@@ -3940,43 +3940,43 @@
         <v>3</v>
       </c>
       <c r="D59" t="n">
-        <v>5</v>
+        <v>33</v>
       </c>
       <c r="E59" t="n">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="F59" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="G59" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="H59" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="I59" t="n">
-        <v>135</v>
+        <v>176</v>
       </c>
       <c r="J59" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K59" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L59" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M59" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N59" t="n">
         <v>0</v>
       </c>
       <c r="O59" t="n">
-        <v>11.2428</v>
+        <v>10.7443</v>
       </c>
       <c r="P59" t="n">
-        <v>188.8869</v>
+        <v>188.4808</v>
       </c>
       <c r="Q59" t="inlineStr">
         <is>
@@ -3985,7 +3985,7 @@
       </c>
       <c r="R59" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:36</t>
+          <t>2026-05-28 17:22:42</t>
         </is>
       </c>
     </row>
@@ -4003,19 +4003,19 @@
         <v>5</v>
       </c>
       <c r="E60" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="F60" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="G60" t="n">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="H60" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="I60" t="n">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="J60" t="n">
         <v>3</v>
@@ -4033,10 +4033,10 @@
         <v>0</v>
       </c>
       <c r="O60" t="n">
-        <v>9.8102</v>
+        <v>10.8444</v>
       </c>
       <c r="P60" t="n">
-        <v>188.6255</v>
+        <v>187.8309</v>
       </c>
       <c r="Q60" t="inlineStr">
         <is>
@@ -4045,7 +4045,7 @@
       </c>
       <c r="R60" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:36</t>
+          <t>2026-05-28 17:22:42</t>
         </is>
       </c>
     </row>
@@ -4054,16 +4054,16 @@
         <v>60</v>
       </c>
       <c r="B61" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C61" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D61" t="n">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="E61" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F61" t="n">
         <v>46</v>
@@ -4072,10 +4072,10 @@
         <v>49</v>
       </c>
       <c r="H61" t="n">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="I61" t="n">
-        <v>176</v>
+        <v>192</v>
       </c>
       <c r="J61" t="n">
         <v>4</v>
@@ -4090,13 +4090,13 @@
         <v>2</v>
       </c>
       <c r="N61" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O61" t="n">
-        <v>10.7443</v>
+        <v>14.9184</v>
       </c>
       <c r="P61" t="n">
-        <v>188.2808</v>
+        <v>187.7961</v>
       </c>
       <c r="Q61" t="inlineStr">
         <is>
@@ -4105,7 +4105,7 @@
       </c>
       <c r="R61" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:36</t>
+          <t>2026-05-28 17:22:42</t>
         </is>
       </c>
     </row>
@@ -4114,16 +4114,16 @@
         <v>61</v>
       </c>
       <c r="B62" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C62" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D62" t="n">
-        <v>44</v>
+        <v>5</v>
       </c>
       <c r="E62" t="n">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="F62" t="n">
         <v>46</v>
@@ -4135,28 +4135,28 @@
         <v>32</v>
       </c>
       <c r="I62" t="n">
-        <v>192</v>
+        <v>143</v>
       </c>
       <c r="J62" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K62" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L62" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M62" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N62" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O62" t="n">
-        <v>14.9184</v>
+        <v>12.3386</v>
       </c>
       <c r="P62" t="n">
-        <v>187.5961</v>
+        <v>187.5264</v>
       </c>
       <c r="Q62" t="inlineStr">
         <is>
@@ -4165,7 +4165,7 @@
       </c>
       <c r="R62" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:36</t>
+          <t>2026-05-28 17:22:42</t>
         </is>
       </c>
     </row>
@@ -4183,40 +4183,40 @@
         <v>5</v>
       </c>
       <c r="E63" t="n">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="F63" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="G63" t="n">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="H63" t="n">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="I63" t="n">
-        <v>143</v>
+        <v>123</v>
       </c>
       <c r="J63" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K63" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L63" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M63" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N63" t="n">
         <v>0</v>
       </c>
       <c r="O63" t="n">
-        <v>12.3386</v>
+        <v>8.579000000000001</v>
       </c>
       <c r="P63" t="n">
-        <v>187.5264</v>
+        <v>186.8876</v>
       </c>
       <c r="Q63" t="inlineStr">
         <is>
@@ -4225,7 +4225,7 @@
       </c>
       <c r="R63" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:36</t>
+          <t>2026-05-28 17:22:42</t>
         </is>
       </c>
     </row>
@@ -4234,28 +4234,28 @@
         <v>63</v>
       </c>
       <c r="B64" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C64" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D64" t="n">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="E64" t="n">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="F64" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="G64" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="H64" t="n">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="I64" t="n">
-        <v>134</v>
+        <v>168</v>
       </c>
       <c r="J64" t="n">
         <v>3</v>
@@ -4273,10 +4273,10 @@
         <v>0</v>
       </c>
       <c r="O64" t="n">
-        <v>10.8444</v>
+        <v>8.704000000000001</v>
       </c>
       <c r="P64" t="n">
-        <v>187.4909</v>
+        <v>185.4401</v>
       </c>
       <c r="Q64" t="inlineStr">
         <is>
@@ -4285,7 +4285,7 @@
       </c>
       <c r="R64" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:36</t>
+          <t>2026-05-28 17:22:42</t>
         </is>
       </c>
     </row>
@@ -4303,7 +4303,7 @@
         <v>5</v>
       </c>
       <c r="E65" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F65" t="n">
         <v>44</v>
@@ -4312,10 +4312,10 @@
         <v>46</v>
       </c>
       <c r="H65" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I65" t="n">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="J65" t="n">
         <v>2</v>
@@ -4324,19 +4324,19 @@
         <v>4</v>
       </c>
       <c r="L65" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M65" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N65" t="n">
         <v>0</v>
       </c>
       <c r="O65" t="n">
-        <v>8.579000000000001</v>
+        <v>8.8544</v>
       </c>
       <c r="P65" t="n">
-        <v>186.6876</v>
+        <v>185.0559</v>
       </c>
       <c r="Q65" t="inlineStr">
         <is>
@@ -4345,7 +4345,7 @@
       </c>
       <c r="R65" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:36</t>
+          <t>2026-05-28 17:22:42</t>
         </is>
       </c>
     </row>
@@ -4360,7 +4360,7 @@
         <v>5</v>
       </c>
       <c r="D66" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="E66" t="n">
         <v>44</v>
@@ -4372,22 +4372,22 @@
         <v>49</v>
       </c>
       <c r="H66" t="n">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="I66" t="n">
-        <v>168</v>
+        <v>175</v>
       </c>
       <c r="J66" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K66" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L66" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M66" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N66" t="n">
         <v>0</v>
@@ -4396,7 +4396,7 @@
         <v>8.704000000000001</v>
       </c>
       <c r="P66" t="n">
-        <v>185.1401</v>
+        <v>184.8001</v>
       </c>
       <c r="Q66" t="inlineStr">
         <is>
@@ -4405,7 +4405,7 @@
       </c>
       <c r="R66" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:36</t>
+          <t>2026-05-28 17:22:42</t>
         </is>
       </c>
     </row>
@@ -4417,46 +4417,46 @@
         <v>1</v>
       </c>
       <c r="C67" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D67" t="n">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="E67" t="n">
-        <v>21</v>
+        <v>44</v>
       </c>
       <c r="F67" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="G67" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="H67" t="n">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="I67" t="n">
-        <v>120</v>
+        <v>175</v>
       </c>
       <c r="J67" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K67" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L67" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M67" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N67" t="n">
         <v>0</v>
       </c>
       <c r="O67" t="n">
-        <v>8.8544</v>
+        <v>8.822699999999999</v>
       </c>
       <c r="P67" t="n">
-        <v>184.7559</v>
+        <v>184.4567</v>
       </c>
       <c r="Q67" t="inlineStr">
         <is>
@@ -4465,7 +4465,7 @@
       </c>
       <c r="R67" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:36</t>
+          <t>2026-05-28 17:22:42</t>
         </is>
       </c>
     </row>
@@ -4474,34 +4474,34 @@
         <v>67</v>
       </c>
       <c r="B68" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C68" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D68" t="n">
+        <v>5</v>
+      </c>
+      <c r="E68" t="n">
         <v>28</v>
       </c>
-      <c r="E68" t="n">
-        <v>44</v>
-      </c>
       <c r="F68" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="G68" t="n">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="H68" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="I68" t="n">
-        <v>175</v>
+        <v>127</v>
       </c>
       <c r="J68" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K68" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L68" t="n">
         <v>3</v>
@@ -4513,10 +4513,10 @@
         <v>0</v>
       </c>
       <c r="O68" t="n">
-        <v>8.704000000000001</v>
+        <v>8.8544</v>
       </c>
       <c r="P68" t="n">
-        <v>184.6001</v>
+        <v>184.3359</v>
       </c>
       <c r="Q68" t="inlineStr">
         <is>
@@ -4525,7 +4525,7 @@
       </c>
       <c r="R68" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:36</t>
+          <t>2026-05-28 17:22:42</t>
         </is>
       </c>
     </row>
@@ -4540,7 +4540,7 @@
         <v>5</v>
       </c>
       <c r="D69" t="n">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="E69" t="n">
         <v>44</v>
@@ -4552,31 +4552,31 @@
         <v>49</v>
       </c>
       <c r="H69" t="n">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="I69" t="n">
-        <v>175</v>
+        <v>166</v>
       </c>
       <c r="J69" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K69" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L69" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M69" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N69" t="n">
         <v>0</v>
       </c>
       <c r="O69" t="n">
-        <v>8.822699999999999</v>
+        <v>8.4048</v>
       </c>
       <c r="P69" t="n">
-        <v>184.2567</v>
+        <v>183.9119</v>
       </c>
       <c r="Q69" t="inlineStr">
         <is>
@@ -4585,7 +4585,7 @@
       </c>
       <c r="R69" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:36</t>
+          <t>2026-05-28 17:22:42</t>
         </is>
       </c>
     </row>
@@ -4603,7 +4603,7 @@
         <v>5</v>
       </c>
       <c r="E70" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F70" t="n">
         <v>44</v>
@@ -4612,10 +4612,10 @@
         <v>46</v>
       </c>
       <c r="H70" t="n">
-        <v>49</v>
+        <v>25</v>
       </c>
       <c r="I70" t="n">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="J70" t="n">
         <v>3</v>
@@ -4624,19 +4624,19 @@
         <v>3</v>
       </c>
       <c r="L70" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M70" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N70" t="n">
         <v>0</v>
       </c>
       <c r="O70" t="n">
-        <v>8.8544</v>
+        <v>8.7178</v>
       </c>
       <c r="P70" t="n">
-        <v>184.1359</v>
+        <v>182.0945</v>
       </c>
       <c r="Q70" t="inlineStr">
         <is>
@@ -4645,7 +4645,7 @@
       </c>
       <c r="R70" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:36</t>
+          <t>2026-05-28 17:22:42</t>
         </is>
       </c>
     </row>
@@ -4660,7 +4660,7 @@
         <v>5</v>
       </c>
       <c r="D71" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E71" t="n">
         <v>44</v>
@@ -4672,16 +4672,16 @@
         <v>49</v>
       </c>
       <c r="H71" t="n">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="I71" t="n">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="J71" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K71" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L71" t="n">
         <v>4</v>
@@ -4693,10 +4693,10 @@
         <v>0</v>
       </c>
       <c r="O71" t="n">
-        <v>8.4048</v>
+        <v>8.1142</v>
       </c>
       <c r="P71" t="n">
-        <v>183.6119</v>
+        <v>182.0855</v>
       </c>
       <c r="Q71" t="inlineStr">
         <is>
@@ -4705,7 +4705,7 @@
       </c>
       <c r="R71" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:36</t>
+          <t>2026-05-28 17:22:42</t>
         </is>
       </c>
     </row>
@@ -4723,19 +4723,19 @@
         <v>5</v>
       </c>
       <c r="E72" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="F72" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="G72" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="H72" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="I72" t="n">
-        <v>126</v>
+        <v>135</v>
       </c>
       <c r="J72" t="n">
         <v>3</v>
@@ -4744,19 +4744,19 @@
         <v>3</v>
       </c>
       <c r="L72" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M72" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N72" t="n">
         <v>0</v>
       </c>
       <c r="O72" t="n">
-        <v>8.7178</v>
+        <v>9.5624</v>
       </c>
       <c r="P72" t="n">
-        <v>181.8945</v>
+        <v>181.9661</v>
       </c>
       <c r="Q72" t="inlineStr">
         <is>
@@ -4765,7 +4765,7 @@
       </c>
       <c r="R72" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:36</t>
+          <t>2026-05-28 17:22:42</t>
         </is>
       </c>
     </row>
@@ -4780,7 +4780,7 @@
         <v>5</v>
       </c>
       <c r="D73" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E73" t="n">
         <v>44</v>
@@ -4792,10 +4792,10 @@
         <v>49</v>
       </c>
       <c r="H73" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="I73" t="n">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="J73" t="n">
         <v>4</v>
@@ -4813,10 +4813,10 @@
         <v>0</v>
       </c>
       <c r="O73" t="n">
-        <v>8.1142</v>
+        <v>8.2608</v>
       </c>
       <c r="P73" t="n">
-        <v>181.7855</v>
+        <v>180.7719</v>
       </c>
       <c r="Q73" t="inlineStr">
         <is>
@@ -4825,7 +4825,7 @@
       </c>
       <c r="R73" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:36</t>
+          <t>2026-05-28 17:22:42</t>
         </is>
       </c>
     </row>
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="C74" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D74" t="n">
-        <v>27</v>
+        <v>5</v>
       </c>
       <c r="E74" t="n">
-        <v>44</v>
+        <v>23</v>
       </c>
       <c r="F74" t="n">
         <v>46</v>
@@ -4852,31 +4852,31 @@
         <v>49</v>
       </c>
       <c r="H74" t="n">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="I74" t="n">
-        <v>172</v>
+        <v>127</v>
       </c>
       <c r="J74" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K74" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L74" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M74" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N74" t="n">
         <v>0</v>
       </c>
       <c r="O74" t="n">
-        <v>8.2608</v>
+        <v>9.0465</v>
       </c>
       <c r="P74" t="n">
-        <v>180.5719</v>
+        <v>178.3364</v>
       </c>
       <c r="Q74" t="inlineStr">
         <is>
@@ -4885,67 +4885,7 @@
       </c>
       <c r="R74" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:36</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="n">
-        <v>74</v>
-      </c>
-      <c r="B75" t="n">
-        <v>1</v>
-      </c>
-      <c r="C75" t="n">
-        <v>3</v>
-      </c>
-      <c r="D75" t="n">
-        <v>5</v>
-      </c>
-      <c r="E75" t="n">
-        <v>23</v>
-      </c>
-      <c r="F75" t="n">
-        <v>46</v>
-      </c>
-      <c r="G75" t="n">
-        <v>49</v>
-      </c>
-      <c r="H75" t="n">
-        <v>34</v>
-      </c>
-      <c r="I75" t="n">
-        <v>127</v>
-      </c>
-      <c r="J75" t="n">
-        <v>2</v>
-      </c>
-      <c r="K75" t="n">
-        <v>4</v>
-      </c>
-      <c r="L75" t="n">
-        <v>5</v>
-      </c>
-      <c r="M75" t="n">
-        <v>1</v>
-      </c>
-      <c r="N75" t="n">
-        <v>0</v>
-      </c>
-      <c r="O75" t="n">
-        <v>9.0465</v>
-      </c>
-      <c r="P75" t="n">
-        <v>178.3364</v>
-      </c>
-      <c r="Q75" t="inlineStr">
-        <is>
-          <t>UK49sGeneticOptimizer_v1</t>
-        </is>
-      </c>
-      <c r="R75" t="inlineStr">
-        <is>
-          <t>2026-05-28 08:54:36</t>
+          <t>2026-05-28 17:22:42</t>
         </is>
       </c>
     </row>
@@ -4985,10 +4925,10 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>187.9364</v>
+        <v>188.1364</v>
       </c>
       <c r="C2" t="n">
-        <v>163.9126</v>
+        <v>164.1532</v>
       </c>
     </row>
     <row r="3">
@@ -4996,10 +4936,10 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>190.279</v>
+        <v>190.757</v>
       </c>
       <c r="C3" t="n">
-        <v>173.0252</v>
+        <v>172.4511</v>
       </c>
     </row>
     <row r="4">
@@ -5007,10 +4947,10 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>195.2433</v>
+        <v>191.8747</v>
       </c>
       <c r="C4" t="n">
-        <v>177.8129</v>
+        <v>178.421</v>
       </c>
     </row>
     <row r="5">
@@ -5018,10 +4958,10 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>198.0129</v>
+        <v>198.8035</v>
       </c>
       <c r="C5" t="n">
-        <v>183.5204</v>
+        <v>182.7949</v>
       </c>
     </row>
     <row r="6">
@@ -5029,10 +4969,10 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>199.4529</v>
+        <v>201.4628</v>
       </c>
       <c r="C6" t="n">
-        <v>187.1388</v>
+        <v>186.3106</v>
       </c>
     </row>
     <row r="7">
@@ -5040,10 +4980,10 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>201.2628</v>
+        <v>201.4628</v>
       </c>
       <c r="C7" t="n">
-        <v>188.0443</v>
+        <v>190.1832</v>
       </c>
     </row>
     <row r="8">
@@ -5051,10 +4991,10 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>201.2628</v>
+        <v>201.4628</v>
       </c>
       <c r="C8" t="n">
-        <v>191.3488</v>
+        <v>192.063</v>
       </c>
     </row>
     <row r="9">
@@ -5062,10 +5002,10 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>201.2628</v>
+        <v>201.4628</v>
       </c>
       <c r="C9" t="n">
-        <v>195.9746</v>
+        <v>194.8474</v>
       </c>
     </row>
     <row r="10">
@@ -5073,10 +5013,10 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>201.2628</v>
+        <v>201.4628</v>
       </c>
       <c r="C10" t="n">
-        <v>198.8773</v>
+        <v>197.6609</v>
       </c>
     </row>
     <row r="11">
@@ -5084,10 +5024,10 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>201.2628</v>
+        <v>201.4628</v>
       </c>
       <c r="C11" t="n">
-        <v>199.6751</v>
+        <v>200.2226</v>
       </c>
     </row>
     <row r="12">
@@ -5095,10 +5035,10 @@
         <v>11</v>
       </c>
       <c r="B12" t="n">
-        <v>201.2628</v>
+        <v>201.4628</v>
       </c>
       <c r="C12" t="n">
-        <v>199.0778</v>
+        <v>199.2173</v>
       </c>
     </row>
     <row r="13">
@@ -5106,10 +5046,10 @@
         <v>12</v>
       </c>
       <c r="B13" t="n">
-        <v>201.2628</v>
+        <v>201.4628</v>
       </c>
       <c r="C13" t="n">
-        <v>199.0502</v>
+        <v>199.3566</v>
       </c>
     </row>
     <row r="14">
@@ -5117,10 +5057,10 @@
         <v>13</v>
       </c>
       <c r="B14" t="n">
-        <v>201.2628</v>
+        <v>201.4628</v>
       </c>
       <c r="C14" t="n">
-        <v>198.9393</v>
+        <v>199.2215</v>
       </c>
     </row>
     <row r="15">
@@ -5128,10 +5068,10 @@
         <v>14</v>
       </c>
       <c r="B15" t="n">
-        <v>201.2628</v>
+        <v>201.4628</v>
       </c>
       <c r="C15" t="n">
-        <v>199.586</v>
+        <v>199.7837</v>
       </c>
     </row>
     <row r="16">
@@ -5139,10 +5079,10 @@
         <v>15</v>
       </c>
       <c r="B16" t="n">
-        <v>201.2628</v>
+        <v>201.4628</v>
       </c>
       <c r="C16" t="n">
-        <v>199.5192</v>
+        <v>199.5698</v>
       </c>
     </row>
     <row r="17">
@@ -5150,10 +5090,10 @@
         <v>16</v>
       </c>
       <c r="B17" t="n">
-        <v>201.2628</v>
+        <v>201.4628</v>
       </c>
       <c r="C17" t="n">
-        <v>199.4018</v>
+        <v>199.7518</v>
       </c>
     </row>
     <row r="18">
@@ -5161,10 +5101,10 @@
         <v>17</v>
       </c>
       <c r="B18" t="n">
-        <v>201.2628</v>
+        <v>201.4628</v>
       </c>
       <c r="C18" t="n">
-        <v>199.7751</v>
+        <v>199.9424</v>
       </c>
     </row>
     <row r="19">
@@ -5172,10 +5112,10 @@
         <v>18</v>
       </c>
       <c r="B19" t="n">
-        <v>201.2628</v>
+        <v>201.4628</v>
       </c>
       <c r="C19" t="n">
-        <v>199.2204</v>
+        <v>199.4548</v>
       </c>
     </row>
     <row r="20">
@@ -5183,10 +5123,10 @@
         <v>19</v>
       </c>
       <c r="B20" t="n">
-        <v>201.2628</v>
+        <v>201.4628</v>
       </c>
       <c r="C20" t="n">
-        <v>198.9298</v>
+        <v>199.1152</v>
       </c>
     </row>
     <row r="21">
@@ -5194,10 +5134,10 @@
         <v>20</v>
       </c>
       <c r="B21" t="n">
-        <v>201.2628</v>
+        <v>201.4628</v>
       </c>
       <c r="C21" t="n">
-        <v>199.6809</v>
+        <v>199.8118</v>
       </c>
     </row>
     <row r="22">
@@ -5205,10 +5145,10 @@
         <v>21</v>
       </c>
       <c r="B22" t="n">
-        <v>201.2628</v>
+        <v>201.4628</v>
       </c>
       <c r="C22" t="n">
-        <v>199.9409</v>
+        <v>200.1211</v>
       </c>
     </row>
     <row r="23">
@@ -5216,10 +5156,10 @@
         <v>22</v>
       </c>
       <c r="B23" t="n">
-        <v>201.2628</v>
+        <v>201.4628</v>
       </c>
       <c r="C23" t="n">
-        <v>199.3572</v>
+        <v>199.6624</v>
       </c>
     </row>
     <row r="24">
@@ -5227,10 +5167,10 @@
         <v>23</v>
       </c>
       <c r="B24" t="n">
-        <v>201.2628</v>
+        <v>201.4628</v>
       </c>
       <c r="C24" t="n">
-        <v>199.6378</v>
+        <v>199.8429</v>
       </c>
     </row>
     <row r="25">
@@ -5238,10 +5178,10 @@
         <v>24</v>
       </c>
       <c r="B25" t="n">
-        <v>201.2628</v>
+        <v>201.4628</v>
       </c>
       <c r="C25" t="n">
-        <v>199.824</v>
+        <v>199.8423</v>
       </c>
     </row>
     <row r="26">
@@ -5249,10 +5189,10 @@
         <v>25</v>
       </c>
       <c r="B26" t="n">
-        <v>201.2628</v>
+        <v>201.4628</v>
       </c>
       <c r="C26" t="n">
-        <v>199.3356</v>
+        <v>199.7013</v>
       </c>
     </row>
     <row r="27">
@@ -5260,10 +5200,10 @@
         <v>26</v>
       </c>
       <c r="B27" t="n">
-        <v>201.2628</v>
+        <v>201.4628</v>
       </c>
       <c r="C27" t="n">
-        <v>199.5197</v>
+        <v>199.6496</v>
       </c>
     </row>
     <row r="28">
@@ -5271,10 +5211,10 @@
         <v>27</v>
       </c>
       <c r="B28" t="n">
-        <v>201.2628</v>
+        <v>201.4628</v>
       </c>
       <c r="C28" t="n">
-        <v>199.5661</v>
+        <v>199.7296</v>
       </c>
     </row>
     <row r="29">
@@ -5282,10 +5222,10 @@
         <v>28</v>
       </c>
       <c r="B29" t="n">
-        <v>201.2628</v>
+        <v>201.4628</v>
       </c>
       <c r="C29" t="n">
-        <v>199.4347</v>
+        <v>199.7513</v>
       </c>
     </row>
     <row r="30">
@@ -5293,10 +5233,10 @@
         <v>29</v>
       </c>
       <c r="B30" t="n">
-        <v>201.2628</v>
+        <v>201.4628</v>
       </c>
       <c r="C30" t="n">
-        <v>199.863</v>
+        <v>200.01</v>
       </c>
     </row>
     <row r="31">
@@ -5304,10 +5244,10 @@
         <v>30</v>
       </c>
       <c r="B31" t="n">
-        <v>201.2628</v>
+        <v>201.4628</v>
       </c>
       <c r="C31" t="n">
-        <v>199.2455</v>
+        <v>199.4141</v>
       </c>
     </row>
     <row r="32">
@@ -5315,10 +5255,10 @@
         <v>31</v>
       </c>
       <c r="B32" t="n">
-        <v>201.2628</v>
+        <v>201.4628</v>
       </c>
       <c r="C32" t="n">
-        <v>199.5549</v>
+        <v>199.8706</v>
       </c>
     </row>
     <row r="33">
@@ -5326,10 +5266,10 @@
         <v>32</v>
       </c>
       <c r="B33" t="n">
-        <v>201.2628</v>
+        <v>201.4628</v>
       </c>
       <c r="C33" t="n">
-        <v>199.3385</v>
+        <v>199.4753</v>
       </c>
     </row>
     <row r="34">
@@ -5337,10 +5277,10 @@
         <v>33</v>
       </c>
       <c r="B34" t="n">
-        <v>201.2628</v>
+        <v>201.4628</v>
       </c>
       <c r="C34" t="n">
-        <v>199.04</v>
+        <v>199.2367</v>
       </c>
     </row>
     <row r="35">
@@ -5348,10 +5288,10 @@
         <v>34</v>
       </c>
       <c r="B35" t="n">
-        <v>201.2628</v>
+        <v>201.4628</v>
       </c>
       <c r="C35" t="n">
-        <v>199.6269</v>
+        <v>199.8759</v>
       </c>
     </row>
     <row r="36">
@@ -5359,10 +5299,10 @@
         <v>35</v>
       </c>
       <c r="B36" t="n">
-        <v>201.2628</v>
+        <v>201.4628</v>
       </c>
       <c r="C36" t="n">
-        <v>199.1968</v>
+        <v>199.3048</v>
       </c>
     </row>
     <row r="37">
@@ -5370,10 +5310,10 @@
         <v>36</v>
       </c>
       <c r="B37" t="n">
-        <v>201.2628</v>
+        <v>201.4628</v>
       </c>
       <c r="C37" t="n">
-        <v>198.9083</v>
+        <v>199.1853</v>
       </c>
     </row>
     <row r="38">
@@ -5381,10 +5321,10 @@
         <v>37</v>
       </c>
       <c r="B38" t="n">
-        <v>201.2628</v>
+        <v>201.4628</v>
       </c>
       <c r="C38" t="n">
-        <v>199.4188</v>
+        <v>199.6691</v>
       </c>
     </row>
     <row r="39">
@@ -5392,10 +5332,10 @@
         <v>38</v>
       </c>
       <c r="B39" t="n">
-        <v>201.2628</v>
+        <v>201.4628</v>
       </c>
       <c r="C39" t="n">
-        <v>199.5879</v>
+        <v>199.6962</v>
       </c>
     </row>
     <row r="40">
@@ -5403,10 +5343,10 @@
         <v>39</v>
       </c>
       <c r="B40" t="n">
-        <v>201.2628</v>
+        <v>201.4628</v>
       </c>
       <c r="C40" t="n">
-        <v>199.0694</v>
+        <v>199.3616</v>
       </c>
     </row>
     <row r="41">
@@ -5414,10 +5354,10 @@
         <v>40</v>
       </c>
       <c r="B41" t="n">
-        <v>201.2628</v>
+        <v>201.4628</v>
       </c>
       <c r="C41" t="n">
-        <v>199.9921</v>
+        <v>200.0995</v>
       </c>
     </row>
     <row r="42">
@@ -5425,10 +5365,10 @@
         <v>41</v>
       </c>
       <c r="B42" t="n">
-        <v>201.2628</v>
+        <v>201.4628</v>
       </c>
       <c r="C42" t="n">
-        <v>198.8261</v>
+        <v>199.1244</v>
       </c>
     </row>
     <row r="43">
@@ -5436,10 +5376,10 @@
         <v>42</v>
       </c>
       <c r="B43" t="n">
-        <v>201.2628</v>
+        <v>201.4628</v>
       </c>
       <c r="C43" t="n">
-        <v>199.4449</v>
+        <v>199.579</v>
       </c>
     </row>
     <row r="44">
@@ -5447,10 +5387,10 @@
         <v>43</v>
       </c>
       <c r="B44" t="n">
-        <v>201.2628</v>
+        <v>201.4628</v>
       </c>
       <c r="C44" t="n">
-        <v>200.0567</v>
+        <v>200.209</v>
       </c>
     </row>
     <row r="45">
@@ -5458,10 +5398,10 @@
         <v>44</v>
       </c>
       <c r="B45" t="n">
-        <v>201.2628</v>
+        <v>201.4628</v>
       </c>
       <c r="C45" t="n">
-        <v>199.9009</v>
+        <v>200.225</v>
       </c>
     </row>
     <row r="46">
@@ -5469,10 +5409,10 @@
         <v>45</v>
       </c>
       <c r="B46" t="n">
-        <v>201.2628</v>
+        <v>201.4628</v>
       </c>
       <c r="C46" t="n">
-        <v>199.5761</v>
+        <v>199.7713</v>
       </c>
     </row>
     <row r="47">
@@ -5480,10 +5420,10 @@
         <v>46</v>
       </c>
       <c r="B47" t="n">
-        <v>201.2628</v>
+        <v>201.4628</v>
       </c>
       <c r="C47" t="n">
-        <v>199.4746</v>
+        <v>199.6028</v>
       </c>
     </row>
     <row r="48">
@@ -5491,10 +5431,10 @@
         <v>47</v>
       </c>
       <c r="B48" t="n">
-        <v>201.2628</v>
+        <v>201.4628</v>
       </c>
       <c r="C48" t="n">
-        <v>199.0522</v>
+        <v>199.3327</v>
       </c>
     </row>
     <row r="49">
@@ -5502,10 +5442,10 @@
         <v>48</v>
       </c>
       <c r="B49" t="n">
-        <v>201.2628</v>
+        <v>201.4628</v>
       </c>
       <c r="C49" t="n">
-        <v>199.2388</v>
+        <v>199.3836</v>
       </c>
     </row>
     <row r="50">
@@ -5513,10 +5453,10 @@
         <v>49</v>
       </c>
       <c r="B50" t="n">
-        <v>201.2628</v>
+        <v>201.4628</v>
       </c>
       <c r="C50" t="n">
-        <v>198.8852</v>
+        <v>199.1296</v>
       </c>
     </row>
     <row r="51">
@@ -5524,10 +5464,10 @@
         <v>50</v>
       </c>
       <c r="B51" t="n">
-        <v>201.2628</v>
+        <v>201.4628</v>
       </c>
       <c r="C51" t="n">
-        <v>199.5056</v>
+        <v>199.6918</v>
       </c>
     </row>
     <row r="52">
@@ -5535,10 +5475,10 @@
         <v>51</v>
       </c>
       <c r="B52" t="n">
-        <v>201.2628</v>
+        <v>201.4628</v>
       </c>
       <c r="C52" t="n">
-        <v>200.0238</v>
+        <v>200.2178</v>
       </c>
     </row>
     <row r="53">
@@ -5546,10 +5486,10 @@
         <v>52</v>
       </c>
       <c r="B53" t="n">
-        <v>201.2628</v>
+        <v>201.4628</v>
       </c>
       <c r="C53" t="n">
-        <v>199.6758</v>
+        <v>199.8814</v>
       </c>
     </row>
     <row r="54">
@@ -5557,10 +5497,10 @@
         <v>53</v>
       </c>
       <c r="B54" t="n">
-        <v>201.2628</v>
+        <v>201.4628</v>
       </c>
       <c r="C54" t="n">
-        <v>199.2359</v>
+        <v>199.4796</v>
       </c>
     </row>
     <row r="55">
@@ -5568,10 +5508,10 @@
         <v>54</v>
       </c>
       <c r="B55" t="n">
-        <v>201.2628</v>
+        <v>201.4628</v>
       </c>
       <c r="C55" t="n">
-        <v>199.3715</v>
+        <v>199.4889</v>
       </c>
     </row>
     <row r="56">
@@ -5579,10 +5519,10 @@
         <v>55</v>
       </c>
       <c r="B56" t="n">
-        <v>201.2628</v>
+        <v>201.4628</v>
       </c>
       <c r="C56" t="n">
-        <v>199.5646</v>
+        <v>199.8266</v>
       </c>
     </row>
     <row r="57">
@@ -5590,10 +5530,10 @@
         <v>56</v>
       </c>
       <c r="B57" t="n">
-        <v>201.2628</v>
+        <v>201.4628</v>
       </c>
       <c r="C57" t="n">
-        <v>199.8436</v>
+        <v>200.0617</v>
       </c>
     </row>
     <row r="58">
@@ -5601,10 +5541,10 @@
         <v>57</v>
       </c>
       <c r="B58" t="n">
-        <v>201.2628</v>
+        <v>201.4628</v>
       </c>
       <c r="C58" t="n">
-        <v>199.2067</v>
+        <v>199.3243</v>
       </c>
     </row>
     <row r="59">
@@ -5612,10 +5552,10 @@
         <v>58</v>
       </c>
       <c r="B59" t="n">
-        <v>201.2628</v>
+        <v>201.4628</v>
       </c>
       <c r="C59" t="n">
-        <v>199.5053</v>
+        <v>199.5709</v>
       </c>
     </row>
     <row r="60">
@@ -5623,10 +5563,10 @@
         <v>59</v>
       </c>
       <c r="B60" t="n">
-        <v>201.2628</v>
+        <v>201.4628</v>
       </c>
       <c r="C60" t="n">
-        <v>198.8133</v>
+        <v>199.1128</v>
       </c>
     </row>
     <row r="61">
@@ -5634,10 +5574,10 @@
         <v>60</v>
       </c>
       <c r="B61" t="n">
-        <v>201.2628</v>
+        <v>201.4628</v>
       </c>
       <c r="C61" t="n">
-        <v>199.3326</v>
+        <v>199.6416</v>
       </c>
     </row>
   </sheetData>

--- a/data/exports/optimization/uk49s_genetic_optimizer_results.xlsx
+++ b/data/exports/optimization/uk49s_genetic_optimizer_results.xlsx
@@ -565,7 +565,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:42</t>
+          <t>2026-05-28 19:50:03</t>
         </is>
       </c>
     </row>
@@ -625,7 +625,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:42</t>
+          <t>2026-05-28 19:50:03</t>
         </is>
       </c>
     </row>
@@ -685,7 +685,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:42</t>
+          <t>2026-05-28 19:50:03</t>
         </is>
       </c>
     </row>
@@ -745,7 +745,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:42</t>
+          <t>2026-05-28 19:50:03</t>
         </is>
       </c>
     </row>
@@ -805,7 +805,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:42</t>
+          <t>2026-05-28 19:50:03</t>
         </is>
       </c>
     </row>
@@ -865,7 +865,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:42</t>
+          <t>2026-05-28 19:50:03</t>
         </is>
       </c>
     </row>
@@ -925,7 +925,7 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:42</t>
+          <t>2026-05-28 19:50:03</t>
         </is>
       </c>
     </row>
@@ -985,7 +985,7 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:42</t>
+          <t>2026-05-28 19:50:03</t>
         </is>
       </c>
     </row>
@@ -1045,7 +1045,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:42</t>
+          <t>2026-05-28 19:50:03</t>
         </is>
       </c>
     </row>
@@ -1105,7 +1105,7 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:42</t>
+          <t>2026-05-28 19:50:03</t>
         </is>
       </c>
     </row>
@@ -1165,7 +1165,7 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:42</t>
+          <t>2026-05-28 19:50:03</t>
         </is>
       </c>
     </row>
@@ -1225,7 +1225,7 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:42</t>
+          <t>2026-05-28 19:50:03</t>
         </is>
       </c>
     </row>
@@ -1285,7 +1285,7 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:42</t>
+          <t>2026-05-28 19:50:03</t>
         </is>
       </c>
     </row>
@@ -1345,7 +1345,7 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:42</t>
+          <t>2026-05-28 19:50:03</t>
         </is>
       </c>
     </row>
@@ -1405,7 +1405,7 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:42</t>
+          <t>2026-05-28 19:50:03</t>
         </is>
       </c>
     </row>
@@ -1465,7 +1465,7 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:42</t>
+          <t>2026-05-28 19:50:03</t>
         </is>
       </c>
     </row>
@@ -1525,7 +1525,7 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:42</t>
+          <t>2026-05-28 19:50:03</t>
         </is>
       </c>
     </row>
@@ -1585,7 +1585,7 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:42</t>
+          <t>2026-05-28 19:50:03</t>
         </is>
       </c>
     </row>
@@ -1645,7 +1645,7 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:42</t>
+          <t>2026-05-28 19:50:03</t>
         </is>
       </c>
     </row>
@@ -1705,7 +1705,7 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:42</t>
+          <t>2026-05-28 19:50:03</t>
         </is>
       </c>
     </row>
@@ -1765,7 +1765,7 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:42</t>
+          <t>2026-05-28 19:50:03</t>
         </is>
       </c>
     </row>
@@ -1825,7 +1825,7 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:42</t>
+          <t>2026-05-28 19:50:03</t>
         </is>
       </c>
     </row>
@@ -1885,7 +1885,7 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:42</t>
+          <t>2026-05-28 19:50:03</t>
         </is>
       </c>
     </row>
@@ -1945,7 +1945,7 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:42</t>
+          <t>2026-05-28 19:50:03</t>
         </is>
       </c>
     </row>
@@ -2005,7 +2005,7 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:42</t>
+          <t>2026-05-28 19:50:03</t>
         </is>
       </c>
     </row>
@@ -2065,7 +2065,7 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:42</t>
+          <t>2026-05-28 19:50:03</t>
         </is>
       </c>
     </row>
@@ -2125,7 +2125,7 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:42</t>
+          <t>2026-05-28 19:50:03</t>
         </is>
       </c>
     </row>
@@ -2185,7 +2185,7 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:42</t>
+          <t>2026-05-28 19:50:03</t>
         </is>
       </c>
     </row>
@@ -2245,7 +2245,7 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:42</t>
+          <t>2026-05-28 19:50:03</t>
         </is>
       </c>
     </row>
@@ -2305,7 +2305,7 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:42</t>
+          <t>2026-05-28 19:50:03</t>
         </is>
       </c>
     </row>
@@ -2365,7 +2365,7 @@
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:42</t>
+          <t>2026-05-28 19:50:03</t>
         </is>
       </c>
     </row>
@@ -2425,7 +2425,7 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:42</t>
+          <t>2026-05-28 19:50:03</t>
         </is>
       </c>
     </row>
@@ -2485,7 +2485,7 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:42</t>
+          <t>2026-05-28 19:50:03</t>
         </is>
       </c>
     </row>
@@ -2545,7 +2545,7 @@
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:42</t>
+          <t>2026-05-28 19:50:03</t>
         </is>
       </c>
     </row>
@@ -2605,7 +2605,7 @@
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:42</t>
+          <t>2026-05-28 19:50:03</t>
         </is>
       </c>
     </row>
@@ -2665,7 +2665,7 @@
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:42</t>
+          <t>2026-05-28 19:50:03</t>
         </is>
       </c>
     </row>
@@ -2725,7 +2725,7 @@
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:42</t>
+          <t>2026-05-28 19:50:03</t>
         </is>
       </c>
     </row>
@@ -2785,7 +2785,7 @@
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:42</t>
+          <t>2026-05-28 19:50:03</t>
         </is>
       </c>
     </row>
@@ -2845,7 +2845,7 @@
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:42</t>
+          <t>2026-05-28 19:50:03</t>
         </is>
       </c>
     </row>
@@ -2905,7 +2905,7 @@
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:42</t>
+          <t>2026-05-28 19:50:03</t>
         </is>
       </c>
     </row>
@@ -2965,7 +2965,7 @@
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:42</t>
+          <t>2026-05-28 19:50:03</t>
         </is>
       </c>
     </row>
@@ -3025,7 +3025,7 @@
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:42</t>
+          <t>2026-05-28 19:50:03</t>
         </is>
       </c>
     </row>
@@ -3085,7 +3085,7 @@
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:42</t>
+          <t>2026-05-28 19:50:03</t>
         </is>
       </c>
     </row>
@@ -3145,7 +3145,7 @@
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:42</t>
+          <t>2026-05-28 19:50:03</t>
         </is>
       </c>
     </row>
@@ -3205,7 +3205,7 @@
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:42</t>
+          <t>2026-05-28 19:50:03</t>
         </is>
       </c>
     </row>
@@ -3265,7 +3265,7 @@
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:42</t>
+          <t>2026-05-28 19:50:03</t>
         </is>
       </c>
     </row>
@@ -3325,7 +3325,7 @@
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:42</t>
+          <t>2026-05-28 19:50:03</t>
         </is>
       </c>
     </row>
@@ -3385,7 +3385,7 @@
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:42</t>
+          <t>2026-05-28 19:50:03</t>
         </is>
       </c>
     </row>
@@ -3445,7 +3445,7 @@
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:42</t>
+          <t>2026-05-28 19:50:03</t>
         </is>
       </c>
     </row>
@@ -3505,7 +3505,7 @@
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:42</t>
+          <t>2026-05-28 19:50:03</t>
         </is>
       </c>
     </row>
@@ -3565,7 +3565,7 @@
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:42</t>
+          <t>2026-05-28 19:50:03</t>
         </is>
       </c>
     </row>
@@ -3625,7 +3625,7 @@
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:42</t>
+          <t>2026-05-28 19:50:03</t>
         </is>
       </c>
     </row>
@@ -3685,7 +3685,7 @@
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:42</t>
+          <t>2026-05-28 19:50:03</t>
         </is>
       </c>
     </row>
@@ -3745,7 +3745,7 @@
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:42</t>
+          <t>2026-05-28 19:50:03</t>
         </is>
       </c>
     </row>
@@ -3805,7 +3805,7 @@
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:42</t>
+          <t>2026-05-28 19:50:03</t>
         </is>
       </c>
     </row>
@@ -3865,7 +3865,7 @@
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:42</t>
+          <t>2026-05-28 19:50:03</t>
         </is>
       </c>
     </row>
@@ -3925,7 +3925,7 @@
       </c>
       <c r="R58" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:42</t>
+          <t>2026-05-28 19:50:03</t>
         </is>
       </c>
     </row>
@@ -3985,7 +3985,7 @@
       </c>
       <c r="R59" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:42</t>
+          <t>2026-05-28 19:50:03</t>
         </is>
       </c>
     </row>
@@ -4045,7 +4045,7 @@
       </c>
       <c r="R60" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:42</t>
+          <t>2026-05-28 19:50:03</t>
         </is>
       </c>
     </row>
@@ -4105,7 +4105,7 @@
       </c>
       <c r="R61" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:42</t>
+          <t>2026-05-28 19:50:03</t>
         </is>
       </c>
     </row>
@@ -4165,7 +4165,7 @@
       </c>
       <c r="R62" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:42</t>
+          <t>2026-05-28 19:50:03</t>
         </is>
       </c>
     </row>
@@ -4225,7 +4225,7 @@
       </c>
       <c r="R63" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:42</t>
+          <t>2026-05-28 19:50:03</t>
         </is>
       </c>
     </row>
@@ -4285,7 +4285,7 @@
       </c>
       <c r="R64" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:42</t>
+          <t>2026-05-28 19:50:03</t>
         </is>
       </c>
     </row>
@@ -4345,7 +4345,7 @@
       </c>
       <c r="R65" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:42</t>
+          <t>2026-05-28 19:50:03</t>
         </is>
       </c>
     </row>
@@ -4405,7 +4405,7 @@
       </c>
       <c r="R66" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:42</t>
+          <t>2026-05-28 19:50:03</t>
         </is>
       </c>
     </row>
@@ -4465,7 +4465,7 @@
       </c>
       <c r="R67" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:42</t>
+          <t>2026-05-28 19:50:03</t>
         </is>
       </c>
     </row>
@@ -4525,7 +4525,7 @@
       </c>
       <c r="R68" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:42</t>
+          <t>2026-05-28 19:50:03</t>
         </is>
       </c>
     </row>
@@ -4585,7 +4585,7 @@
       </c>
       <c r="R69" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:42</t>
+          <t>2026-05-28 19:50:03</t>
         </is>
       </c>
     </row>
@@ -4645,7 +4645,7 @@
       </c>
       <c r="R70" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:42</t>
+          <t>2026-05-28 19:50:03</t>
         </is>
       </c>
     </row>
@@ -4705,7 +4705,7 @@
       </c>
       <c r="R71" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:42</t>
+          <t>2026-05-28 19:50:03</t>
         </is>
       </c>
     </row>
@@ -4765,7 +4765,7 @@
       </c>
       <c r="R72" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:42</t>
+          <t>2026-05-28 19:50:03</t>
         </is>
       </c>
     </row>
@@ -4825,7 +4825,7 @@
       </c>
       <c r="R73" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:42</t>
+          <t>2026-05-28 19:50:03</t>
         </is>
       </c>
     </row>
@@ -4885,7 +4885,7 @@
       </c>
       <c r="R74" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:42</t>
+          <t>2026-05-28 19:50:03</t>
         </is>
       </c>
     </row>
